--- a/flora.xlsx
+++ b/flora.xlsx
@@ -1,21 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\User\Documents\bioConservaPY\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C539395A-6324-43CB-824E-8055E4C44028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr/>
 </workbook>
 </file>
 
@@ -76,16 +67,16 @@
     <t>Acalypha godseffiana</t>
   </si>
   <si>
+    <t>Exótica</t>
+  </si>
+  <si>
+    <t>No Evaluado (NE)</t>
+  </si>
+  <si>
     <t>Copia de Ficha registro flora y fauna (FLORA 1).pdf</t>
   </si>
   <si>
     <t>Acalypha hispida</t>
-  </si>
-  <si>
-    <t>Exótica</t>
-  </si>
-  <si>
-    <t>No Evaluado (NE)</t>
   </si>
   <si>
     <t>FLO-20260609_34.pdf</t>
@@ -2062,64 +2053,58 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <sz val="11.0"/>
+      <color/>
+      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font/>
   </fonts>
   <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
   </fills>
   <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -2275,7 +2260,7 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln cap="flat" cmpd="sng" w="9525" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -2284,13 +2269,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln cap="flat" cmpd="sng" w="25400" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln cap="flat" cmpd="sng" w="38100" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -2300,7 +2285,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="40000" rotWithShape="0" dir="5400000" dist="20000">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -2309,7 +2294,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="40000" rotWithShape="0" dir="5400000" dist="23000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -2318,7 +2303,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="40000" rotWithShape="0" dir="5400000" dist="23000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -2328,12 +2313,12 @@
             <a:camera prst="orthographicFront">
               <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig rig="threePt" dir="t">
+            <a:lightRig dir="t" rig="threePt">
               <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
+            <a:bevelT h="25400" w="63500"/>
           </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
@@ -2364,7 +2349,7 @@
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+            <a:fillToRect b="180000" l="50000" r="50000" t="-80000"/>
           </a:path>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
@@ -2383,7 +2368,7 @@
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+            <a:fillToRect b="50000" l="50000" r="50000" t="50000"/>
           </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
@@ -2395,23 +2380,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K258"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="50.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="26.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="27" bestFit="1" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="50.71"/>
+    <col customWidth="1" min="2" max="2" width="13.29"/>
+    <col customWidth="1" min="3" max="3" width="13.43"/>
+    <col customWidth="1" min="4" max="4" width="12.71"/>
+    <col customWidth="1" min="5" max="5" width="15.0"/>
+    <col customWidth="1" min="6" max="6" width="18.43"/>
+    <col customWidth="1" min="7" max="7" width="26.71"/>
+    <col customWidth="1" min="8" max="9" width="11.71"/>
+    <col customWidth="1" min="10" max="10" width="7.0"/>
+    <col customWidth="1" min="11" max="11" width="27.0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" ht="14.25" customHeight="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2446,7 +2433,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" ht="14.25" customHeight="1">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -2469,21 +2456,21 @@
         <v>17</v>
       </c>
       <c r="H2">
-        <v>-12054126</v>
+        <v>-1.2054126E7</v>
       </c>
       <c r="I2">
-        <v>-77084847</v>
+        <v>-7.7084847E7</v>
       </c>
       <c r="J2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" ht="14.25" customHeight="1">
+      <c r="A3" t="s">
         <v>20</v>
-      </c>
-      <c r="K2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>18</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -2501,22 +2488,22 @@
         <v>16</v>
       </c>
       <c r="G3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H3">
-        <v>-1205694058</v>
+        <v>-1.205694058E9</v>
       </c>
       <c r="I3">
-        <v>-7708641878</v>
+        <v>-7.708641878E9</v>
       </c>
       <c r="J3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" ht="14.25" customHeight="1">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -2536,22 +2523,22 @@
         <v>16</v>
       </c>
       <c r="G4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H4">
-        <v>-12060857</v>
+        <v>-1.2060857E7</v>
       </c>
       <c r="I4">
-        <v>-77084882</v>
+        <v>-7.7084882E7</v>
       </c>
       <c r="J4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" ht="14.25" customHeight="1">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -2574,19 +2561,19 @@
         <v>24</v>
       </c>
       <c r="H5">
-        <v>-12059189</v>
+        <v>-1.2059189E7</v>
       </c>
       <c r="I5">
-        <v>-770833987</v>
+        <v>-7.70833987E8</v>
       </c>
       <c r="J5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" ht="14.25" customHeight="1">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -2609,19 +2596,19 @@
         <v>30</v>
       </c>
       <c r="H6">
-        <v>-12058464</v>
+        <v>-1.2058464E7</v>
       </c>
       <c r="I6">
-        <v>-77079628</v>
+        <v>-7.7079628E7</v>
       </c>
       <c r="J6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K6" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" ht="14.25" customHeight="1">
       <c r="A7" t="s">
         <v>32</v>
       </c>
@@ -2644,19 +2631,19 @@
         <v>34</v>
       </c>
       <c r="H7">
-        <v>-12059339</v>
+        <v>-1.2059339E7</v>
       </c>
       <c r="I7">
-        <v>-77087202</v>
+        <v>-7.7087202E7</v>
       </c>
       <c r="J7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" ht="14.25" customHeight="1">
       <c r="A8" t="s">
         <v>35</v>
       </c>
@@ -2679,19 +2666,19 @@
         <v>36</v>
       </c>
       <c r="H8">
-        <v>-1205614319</v>
+        <v>-1.205614319E9</v>
       </c>
       <c r="I8">
-        <v>-7708652797</v>
+        <v>-7.708652797E9</v>
       </c>
       <c r="J8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K8" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" ht="14.25" customHeight="1">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -2714,19 +2701,19 @@
         <v>37</v>
       </c>
       <c r="H9">
-        <v>-12057781</v>
+        <v>-1.2057781E7</v>
       </c>
       <c r="I9">
-        <v>-77080035</v>
+        <v>-7.7080035E7</v>
       </c>
       <c r="J9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K9" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" ht="14.25" customHeight="1">
       <c r="A10" t="s">
         <v>38</v>
       </c>
@@ -2749,19 +2736,19 @@
         <v>39</v>
       </c>
       <c r="H10">
-        <v>-12058044</v>
+        <v>-1.2058044E7</v>
       </c>
       <c r="I10">
-        <v>-7708053</v>
+        <v>-7708053.0</v>
       </c>
       <c r="J10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" ht="14.25" customHeight="1">
       <c r="A11" t="s">
         <v>40</v>
       </c>
@@ -2784,19 +2771,19 @@
         <v>44</v>
       </c>
       <c r="H11">
-        <v>-1205744928</v>
+        <v>-1.205744928E9</v>
       </c>
       <c r="I11">
-        <v>-7708568678</v>
+        <v>-7.708568678E9</v>
       </c>
       <c r="J11" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" ht="14.25" customHeight="1">
       <c r="A12" t="s">
         <v>45</v>
       </c>
@@ -2819,19 +2806,19 @@
         <v>48</v>
       </c>
       <c r="H12">
-        <v>-12059866</v>
+        <v>-1.2059866E7</v>
       </c>
       <c r="I12">
-        <v>-77081176</v>
+        <v>-7.7081176E7</v>
       </c>
       <c r="J12" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" ht="14.25" customHeight="1">
       <c r="A13" t="s">
         <v>49</v>
       </c>
@@ -2854,19 +2841,19 @@
         <v>50</v>
       </c>
       <c r="H13">
-        <v>-1205744058</v>
+        <v>-1.205744058E9</v>
       </c>
       <c r="I13">
-        <v>-7708600328</v>
+        <v>-7.708600328E9</v>
       </c>
       <c r="J13" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K13" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" ht="14.25" customHeight="1">
       <c r="A14" t="s">
         <v>51</v>
       </c>
@@ -2889,19 +2876,19 @@
         <v>52</v>
       </c>
       <c r="H14">
-        <v>-120543636</v>
+        <v>-1.20543636E8</v>
       </c>
       <c r="I14">
-        <v>-770844448</v>
+        <v>-7.70844448E8</v>
       </c>
       <c r="J14" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K14" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" ht="14.25" customHeight="1">
       <c r="A15" t="s">
         <v>53</v>
       </c>
@@ -2924,19 +2911,19 @@
         <v>54</v>
       </c>
       <c r="H15">
-        <v>-12058254</v>
+        <v>-1.2058254E7</v>
       </c>
       <c r="I15">
-        <v>-77080432</v>
+        <v>-7.7080432E7</v>
       </c>
       <c r="J15" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K15" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" ht="14.25" customHeight="1">
       <c r="A16" t="s">
         <v>55</v>
       </c>
@@ -2959,19 +2946,19 @@
         <v>56</v>
       </c>
       <c r="H16">
-        <v>-12060189</v>
+        <v>-1.2060189E7</v>
       </c>
       <c r="I16">
-        <v>-77080977</v>
+        <v>-7.7080977E7</v>
       </c>
       <c r="J16" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K16" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" ht="14.25" customHeight="1">
       <c r="A17" t="s">
         <v>57</v>
       </c>
@@ -2994,19 +2981,19 @@
         <v>61</v>
       </c>
       <c r="H17">
-        <v>-1205956993</v>
+        <v>-1.205956993E9</v>
       </c>
       <c r="I17">
-        <v>-7708088735</v>
+        <v>-7.708088735E9</v>
       </c>
       <c r="J17" t="s">
         <v>62</v>
       </c>
       <c r="K17" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" ht="14.25" customHeight="1">
       <c r="A18" t="s">
         <v>53</v>
       </c>
@@ -3029,19 +3016,19 @@
         <v>66</v>
       </c>
       <c r="H18">
-        <v>-12058444</v>
+        <v>-1.2058444E7</v>
       </c>
       <c r="I18">
-        <v>-77080372</v>
+        <v>-7.7080372E7</v>
       </c>
       <c r="J18" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K18" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" ht="14.25" customHeight="1">
       <c r="A19" t="s">
         <v>67</v>
       </c>
@@ -3064,19 +3051,19 @@
         <v>71</v>
       </c>
       <c r="H19">
-        <v>-12054729</v>
+        <v>-1.2054729E7</v>
       </c>
       <c r="I19">
-        <v>-77085504</v>
+        <v>-7.7085504E7</v>
       </c>
       <c r="J19" t="s">
         <v>62</v>
       </c>
       <c r="K19" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" ht="14.25" customHeight="1">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -3099,19 +3086,19 @@
         <v>72</v>
       </c>
       <c r="H20">
-        <v>-12058446</v>
+        <v>-1.2058446E7</v>
       </c>
       <c r="I20">
-        <v>-77079712</v>
+        <v>-7.7079712E7</v>
       </c>
       <c r="J20" t="s">
         <v>62</v>
       </c>
       <c r="K20" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" ht="14.25" customHeight="1">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -3134,19 +3121,19 @@
         <v>74</v>
       </c>
       <c r="H21">
-        <v>-12057977</v>
+        <v>-1.2057977E7</v>
       </c>
       <c r="I21">
-        <v>-77079822</v>
+        <v>-7.7079822E7</v>
       </c>
       <c r="J21" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K21" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" ht="14.25" customHeight="1">
       <c r="A22" t="s">
         <v>75</v>
       </c>
@@ -3169,19 +3156,19 @@
         <v>77</v>
       </c>
       <c r="H22">
-        <v>-120601022</v>
+        <v>-1.20601022E8</v>
       </c>
       <c r="I22">
-        <v>-770812073</v>
+        <v>-7.70812073E8</v>
       </c>
       <c r="J22" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K22" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" ht="14.25" customHeight="1">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -3204,19 +3191,19 @@
         <v>78</v>
       </c>
       <c r="H23">
-        <v>-12058392</v>
+        <v>-1.2058392E7</v>
       </c>
       <c r="I23">
-        <v>-77080974</v>
+        <v>-7.7080974E7</v>
       </c>
       <c r="J23" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K23" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" ht="14.25" customHeight="1">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -3239,19 +3226,19 @@
         <v>81</v>
       </c>
       <c r="H24">
-        <v>-12058012</v>
+        <v>-1.2058012E7</v>
       </c>
       <c r="I24">
-        <v>-77079983</v>
+        <v>-7.7079983E7</v>
       </c>
       <c r="J24" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K24" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" ht="14.25" customHeight="1">
       <c r="A25" t="s">
         <v>82</v>
       </c>
@@ -3274,10 +3261,10 @@
         <v>86</v>
       </c>
       <c r="H25">
-        <v>-12059339</v>
+        <v>-1.2059339E7</v>
       </c>
       <c r="I25">
-        <v>-77087202</v>
+        <v>-7.7087202E7</v>
       </c>
       <c r="J25" t="s">
         <v>62</v>
@@ -3286,7 +3273,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" ht="14.25" customHeight="1">
       <c r="A26" t="s">
         <v>87</v>
       </c>
@@ -3309,10 +3296,10 @@
         <v>88</v>
       </c>
       <c r="H26">
-        <v>-12054079</v>
+        <v>-1.2054079E7</v>
       </c>
       <c r="I26">
-        <v>-77085772</v>
+        <v>-7.7085772E7</v>
       </c>
       <c r="J26" t="s">
         <v>62</v>
@@ -3321,7 +3308,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" ht="14.25" customHeight="1">
       <c r="A27" t="s">
         <v>89</v>
       </c>
@@ -3344,10 +3331,10 @@
         <v>90</v>
       </c>
       <c r="H27">
-        <v>-12060689</v>
+        <v>-1.2060689E7</v>
       </c>
       <c r="I27">
-        <v>-77082967</v>
+        <v>-7.7082967E7</v>
       </c>
       <c r="J27" t="s">
         <v>62</v>
@@ -3356,7 +3343,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" ht="14.25" customHeight="1">
       <c r="A28" t="s">
         <v>91</v>
       </c>
@@ -3379,10 +3366,10 @@
         <v>92</v>
       </c>
       <c r="H28">
-        <v>-12060636</v>
+        <v>-1.2060636E7</v>
       </c>
       <c r="I28">
-        <v>-77082914</v>
+        <v>-7.7082914E7</v>
       </c>
       <c r="J28" t="s">
         <v>62</v>
@@ -3391,7 +3378,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" ht="14.25" customHeight="1">
       <c r="A29" t="s">
         <v>93</v>
       </c>
@@ -3414,19 +3401,19 @@
         <v>99</v>
       </c>
       <c r="H29">
-        <v>-1205938467</v>
+        <v>-1.205938467E9</v>
       </c>
       <c r="I29">
-        <v>-7708157858</v>
+        <v>-7.708157858E9</v>
       </c>
       <c r="J29" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K29" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" ht="14.25" customHeight="1">
       <c r="A30" t="s">
         <v>100</v>
       </c>
@@ -3449,19 +3436,19 @@
         <v>104</v>
       </c>
       <c r="H30">
-        <v>-120603064</v>
+        <v>-1.20603064E8</v>
       </c>
       <c r="I30">
-        <v>-770811865</v>
+        <v>-7.70811865E8</v>
       </c>
       <c r="J30" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K30" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31" ht="14.25" customHeight="1">
       <c r="A31" t="s">
         <v>105</v>
       </c>
@@ -3484,19 +3471,19 @@
         <v>107</v>
       </c>
       <c r="H31">
-        <v>-12060747</v>
+        <v>-1.2060747E7</v>
       </c>
       <c r="I31">
-        <v>-7708427</v>
+        <v>-7708427.0</v>
       </c>
       <c r="J31" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K31" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="32" ht="14.25" customHeight="1">
       <c r="A32" t="s">
         <v>108</v>
       </c>
@@ -3519,19 +3506,19 @@
         <v>112</v>
       </c>
       <c r="H32">
-        <v>-12054079</v>
+        <v>-1.2054079E7</v>
       </c>
       <c r="I32">
-        <v>-77085772</v>
+        <v>-7.7085772E7</v>
       </c>
       <c r="J32" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K32" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="33" ht="14.25" customHeight="1">
       <c r="A33" t="s">
         <v>113</v>
       </c>
@@ -3554,19 +3541,19 @@
         <v>115</v>
       </c>
       <c r="H33">
-        <v>-12055022</v>
+        <v>-1.2055022E7</v>
       </c>
       <c r="I33">
-        <v>-77085872</v>
+        <v>-7.7085872E7</v>
       </c>
       <c r="J33" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K33" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="34" ht="14.25" customHeight="1">
       <c r="A34" t="s">
         <v>116</v>
       </c>
@@ -3589,19 +3576,19 @@
         <v>118</v>
       </c>
       <c r="H34">
-        <v>-1206006375</v>
+        <v>-1.206006375E9</v>
       </c>
       <c r="I34">
-        <v>-7708105692</v>
+        <v>-7.708105692E9</v>
       </c>
       <c r="J34" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K34" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35" ht="14.25" customHeight="1">
       <c r="A35" t="s">
         <v>119</v>
       </c>
@@ -3624,19 +3611,19 @@
         <v>121</v>
       </c>
       <c r="H35">
-        <v>-1205555</v>
+        <v>-1205555.0</v>
       </c>
       <c r="I35">
-        <v>-77082396</v>
+        <v>-7.7082396E7</v>
       </c>
       <c r="J35" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K35" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36" ht="14.25" customHeight="1">
       <c r="A36" t="s">
         <v>122</v>
       </c>
@@ -3659,19 +3646,19 @@
         <v>121</v>
       </c>
       <c r="H36">
-        <v>-12054731</v>
+        <v>-1.2054731E7</v>
       </c>
       <c r="I36">
-        <v>-77085502</v>
+        <v>-7.7085502E7</v>
       </c>
       <c r="J36" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K36" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37" ht="14.25" customHeight="1">
       <c r="A37" t="s">
         <v>25</v>
       </c>
@@ -3694,19 +3681,19 @@
         <v>125</v>
       </c>
       <c r="H37">
-        <v>-12058223</v>
+        <v>-1.2058223E7</v>
       </c>
       <c r="I37">
-        <v>-77079791</v>
+        <v>-7.7079791E7</v>
       </c>
       <c r="J37" t="s">
         <v>62</v>
       </c>
       <c r="K37" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="38" ht="14.25" customHeight="1">
       <c r="A38" t="s">
         <v>126</v>
       </c>
@@ -3729,19 +3716,19 @@
         <v>128</v>
       </c>
       <c r="H38">
-        <v>-120596026</v>
+        <v>-1.20596026E8</v>
       </c>
       <c r="I38">
-        <v>-7708200161</v>
+        <v>-7.708200161E9</v>
       </c>
       <c r="J38" t="s">
         <v>62</v>
       </c>
       <c r="K38" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="39" ht="14.25" customHeight="1">
       <c r="A39" t="s">
         <v>129</v>
       </c>
@@ -3764,19 +3751,19 @@
         <v>130</v>
       </c>
       <c r="H39">
-        <v>-12055507</v>
+        <v>-1.2055507E7</v>
       </c>
       <c r="I39">
-        <v>-77086982</v>
+        <v>-7.7086982E7</v>
       </c>
       <c r="J39" t="s">
         <v>62</v>
       </c>
       <c r="K39" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="40" ht="14.25" customHeight="1">
       <c r="A40" t="s">
         <v>131</v>
       </c>
@@ -3799,19 +3786,19 @@
         <v>132</v>
       </c>
       <c r="H40">
-        <v>-12059339</v>
+        <v>-1.2059339E7</v>
       </c>
       <c r="I40">
-        <v>-77087202</v>
+        <v>-7.7087202E7</v>
       </c>
       <c r="J40" t="s">
         <v>62</v>
       </c>
       <c r="K40" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="41" ht="14.25" customHeight="1">
       <c r="A41" t="s">
         <v>25</v>
       </c>
@@ -3834,19 +3821,19 @@
         <v>136</v>
       </c>
       <c r="H41">
-        <v>-12058293</v>
+        <v>-1.2058293E7</v>
       </c>
       <c r="I41">
-        <v>-77079951</v>
+        <v>-7.7079951E7</v>
       </c>
       <c r="J41" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K41" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="42" ht="14.25" customHeight="1">
       <c r="A42" t="s">
         <v>137</v>
       </c>
@@ -3869,10 +3856,10 @@
         <v>141</v>
       </c>
       <c r="H42">
-        <v>-12056378</v>
+        <v>-1.2056378E7</v>
       </c>
       <c r="I42">
-        <v>-77082083</v>
+        <v>-7.7082083E7</v>
       </c>
       <c r="J42" t="s">
         <v>62</v>
@@ -3881,7 +3868,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="43" ht="14.25" customHeight="1">
       <c r="A43" t="s">
         <v>143</v>
       </c>
@@ -3904,10 +3891,10 @@
         <v>144</v>
       </c>
       <c r="H43">
-        <v>-12056669</v>
+        <v>-1.2056669E7</v>
       </c>
       <c r="I43">
-        <v>-77085002</v>
+        <v>-7.7085002E7</v>
       </c>
       <c r="J43" t="s">
         <v>62</v>
@@ -3916,7 +3903,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="44" ht="14.25" customHeight="1">
       <c r="A44" t="s">
         <v>23</v>
       </c>
@@ -3939,10 +3926,10 @@
         <v>145</v>
       </c>
       <c r="H44">
-        <v>-120582519</v>
+        <v>-1.20582519E8</v>
       </c>
       <c r="I44">
-        <v>-770854067</v>
+        <v>-7.70854067E8</v>
       </c>
       <c r="J44" t="s">
         <v>62</v>
@@ -3951,7 +3938,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="45" ht="14.25" customHeight="1">
       <c r="A45" t="s">
         <v>146</v>
       </c>
@@ -3974,10 +3961,10 @@
         <v>150</v>
       </c>
       <c r="H45">
-        <v>-12059339</v>
+        <v>-1.2059339E7</v>
       </c>
       <c r="I45">
-        <v>-77087202</v>
+        <v>-7.7087202E7</v>
       </c>
       <c r="J45" t="s">
         <v>62</v>
@@ -3986,7 +3973,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="46" ht="14.25" customHeight="1">
       <c r="A46" t="s">
         <v>151</v>
       </c>
@@ -4009,19 +3996,19 @@
         <v>155</v>
       </c>
       <c r="H46">
-        <v>-12053123</v>
+        <v>-1.2053123E7</v>
       </c>
       <c r="I46">
-        <v>-77087656</v>
+        <v>-7.7087656E7</v>
       </c>
       <c r="J46" t="s">
         <v>62</v>
       </c>
       <c r="K46" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47" ht="14.25" customHeight="1">
       <c r="A47" t="s">
         <v>137</v>
       </c>
@@ -4044,19 +4031,19 @@
         <v>158</v>
       </c>
       <c r="H47">
-        <v>-12056669</v>
+        <v>-1.2056669E7</v>
       </c>
       <c r="I47">
-        <v>-77082056</v>
+        <v>-7.7082056E7</v>
       </c>
       <c r="J47" t="s">
         <v>62</v>
       </c>
       <c r="K47" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="48" ht="14.25" customHeight="1">
       <c r="A48" t="s">
         <v>25</v>
       </c>
@@ -4079,19 +4066,19 @@
         <v>162</v>
       </c>
       <c r="H48">
-        <v>-12058495</v>
+        <v>-1.2058495E7</v>
       </c>
       <c r="I48">
-        <v>-77079711</v>
+        <v>-7.7079711E7</v>
       </c>
       <c r="J48" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K48" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="49" ht="14.25" customHeight="1">
       <c r="A49" t="s">
         <v>163</v>
       </c>
@@ -4114,19 +4101,19 @@
         <v>162</v>
       </c>
       <c r="H49">
-        <v>-12058495</v>
+        <v>-1.2058495E7</v>
       </c>
       <c r="I49">
-        <v>-77079711</v>
+        <v>-7.7079711E7</v>
       </c>
       <c r="J49" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K49" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="50" ht="14.25" customHeight="1">
       <c r="A50" t="s">
         <v>164</v>
       </c>
@@ -4149,19 +4136,19 @@
         <v>168</v>
       </c>
       <c r="H50">
-        <v>-12059164</v>
+        <v>-1.2059164E7</v>
       </c>
       <c r="I50">
-        <v>-77082569</v>
+        <v>-7.7082569E7</v>
       </c>
       <c r="J50" t="s">
         <v>62</v>
       </c>
       <c r="K50" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="51" ht="14.25" customHeight="1">
       <c r="A51" t="s">
         <v>169</v>
       </c>
@@ -4184,19 +4171,19 @@
         <v>173</v>
       </c>
       <c r="H51">
-        <v>-12054729</v>
+        <v>-1.2054729E7</v>
       </c>
       <c r="I51">
-        <v>-77085504</v>
+        <v>-7.7085504E7</v>
       </c>
       <c r="J51" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K51" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="52" ht="14.25" customHeight="1">
       <c r="A52" t="s">
         <v>25</v>
       </c>
@@ -4219,19 +4206,19 @@
         <v>175</v>
       </c>
       <c r="H52">
-        <v>-12058372</v>
+        <v>-1.2058372E7</v>
       </c>
       <c r="I52">
-        <v>-77079835</v>
+        <v>-7.7079835E7</v>
       </c>
       <c r="J52" t="s">
         <v>62</v>
       </c>
       <c r="K52" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="53" ht="14.25" customHeight="1">
       <c r="A53" t="s">
         <v>163</v>
       </c>
@@ -4254,19 +4241,19 @@
         <v>175</v>
       </c>
       <c r="H53">
-        <v>-12058372</v>
+        <v>-1.2058372E7</v>
       </c>
       <c r="I53">
-        <v>-77079835</v>
+        <v>-7.7079835E7</v>
       </c>
       <c r="J53" t="s">
         <v>62</v>
       </c>
       <c r="K53" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="54" ht="14.25" customHeight="1">
       <c r="A54" t="s">
         <v>176</v>
       </c>
@@ -4289,19 +4276,19 @@
         <v>178</v>
       </c>
       <c r="H54">
-        <v>-12059876</v>
+        <v>-1.2059876E7</v>
       </c>
       <c r="I54">
-        <v>-77080387</v>
+        <v>-7.7080387E7</v>
       </c>
       <c r="J54" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K54" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="55" ht="14.25" customHeight="1">
       <c r="A55" t="s">
         <v>179</v>
       </c>
@@ -4324,19 +4311,19 @@
         <v>181</v>
       </c>
       <c r="H55">
-        <v>-12059676</v>
+        <v>-1.2059676E7</v>
       </c>
       <c r="I55">
-        <v>-77079776</v>
+        <v>-7.7079776E7</v>
       </c>
       <c r="J55" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K55" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="56" ht="14.25" customHeight="1">
       <c r="A56" t="s">
         <v>38</v>
       </c>
@@ -4359,19 +4346,19 @@
         <v>184</v>
       </c>
       <c r="H56">
-        <v>-12058044</v>
+        <v>-1.2058044E7</v>
       </c>
       <c r="I56">
-        <v>-7708196112</v>
+        <v>-7.708196112E9</v>
       </c>
       <c r="J56" t="s">
         <v>62</v>
       </c>
       <c r="K56" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="57" ht="14.25" customHeight="1">
       <c r="A57" t="s">
         <v>53</v>
       </c>
@@ -4394,19 +4381,19 @@
         <v>186</v>
       </c>
       <c r="H57">
-        <v>-12058455</v>
+        <v>-1.2058455E7</v>
       </c>
       <c r="I57">
-        <v>-77080218</v>
+        <v>-7.7080218E7</v>
       </c>
       <c r="J57" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K57" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="58" ht="14.25" customHeight="1">
       <c r="A58" t="s">
         <v>187</v>
       </c>
@@ -4429,19 +4416,19 @@
         <v>191</v>
       </c>
       <c r="H58">
-        <v>-1205636519</v>
+        <v>-1.205636519E9</v>
       </c>
       <c r="I58">
-        <v>-7708688828</v>
+        <v>-7.708688828E9</v>
       </c>
       <c r="J58" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K58" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="59" ht="14.25" customHeight="1">
       <c r="A59" t="s">
         <v>53</v>
       </c>
@@ -4464,19 +4451,19 @@
         <v>195</v>
       </c>
       <c r="H59">
-        <v>-12058392</v>
+        <v>-1.2058392E7</v>
       </c>
       <c r="I59">
-        <v>-77080974</v>
+        <v>-7.7080974E7</v>
       </c>
       <c r="J59" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K59" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="60" ht="14.25" customHeight="1">
       <c r="A60" t="s">
         <v>196</v>
       </c>
@@ -4499,19 +4486,19 @@
         <v>199</v>
       </c>
       <c r="H60">
-        <v>-1205982207</v>
+        <v>-1.205982207E9</v>
       </c>
       <c r="I60">
-        <v>-7708130564</v>
+        <v>-7.708130564E9</v>
       </c>
       <c r="J60" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K60" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="61" ht="14.25" customHeight="1">
       <c r="A61" t="s">
         <v>200</v>
       </c>
@@ -4534,19 +4521,19 @@
         <v>201</v>
       </c>
       <c r="H61">
-        <v>-12059339</v>
+        <v>-1.2059339E7</v>
       </c>
       <c r="I61">
-        <v>-77087202</v>
+        <v>-7.7087202E7</v>
       </c>
       <c r="J61" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K61" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="62" ht="14.25" customHeight="1">
       <c r="A62" t="s">
         <v>53</v>
       </c>
@@ -4569,19 +4556,19 @@
         <v>202</v>
       </c>
       <c r="H62">
-        <v>-12058258</v>
+        <v>-1.2058258E7</v>
       </c>
       <c r="I62">
-        <v>-77080569</v>
+        <v>-7.7080569E7</v>
       </c>
       <c r="J62" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K62" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="63" ht="14.25" customHeight="1">
       <c r="A63" t="s">
         <v>25</v>
       </c>
@@ -4604,19 +4591,19 @@
         <v>204</v>
       </c>
       <c r="H63">
-        <v>-12058487</v>
+        <v>-1.2058487E7</v>
       </c>
       <c r="I63">
-        <v>-77079881</v>
+        <v>-7.7079881E7</v>
       </c>
       <c r="J63" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K63" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="64" ht="14.25" customHeight="1">
       <c r="A64" t="s">
         <v>163</v>
       </c>
@@ -4639,19 +4626,19 @@
         <v>204</v>
       </c>
       <c r="H64">
-        <v>-12058487</v>
+        <v>-1.2058487E7</v>
       </c>
       <c r="I64">
-        <v>-77079881</v>
+        <v>-7.7079881E7</v>
       </c>
       <c r="J64" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K64" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="65" ht="14.25" customHeight="1">
       <c r="A65" t="s">
         <v>25</v>
       </c>
@@ -4674,19 +4661,19 @@
         <v>206</v>
       </c>
       <c r="H65">
-        <v>-12058078</v>
+        <v>-1.2058078E7</v>
       </c>
       <c r="I65">
-        <v>-77079772</v>
+        <v>-7.7079772E7</v>
       </c>
       <c r="J65" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K65" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="66" ht="14.25" customHeight="1">
       <c r="A66" t="s">
         <v>137</v>
       </c>
@@ -4709,19 +4696,19 @@
         <v>208</v>
       </c>
       <c r="H66">
-        <v>-12056444</v>
+        <v>-1.2056444E7</v>
       </c>
       <c r="I66">
-        <v>-77081023</v>
+        <v>-7.7081023E7</v>
       </c>
       <c r="J66" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K66" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="67" ht="14.25" customHeight="1">
       <c r="A67" t="s">
         <v>209</v>
       </c>
@@ -4744,19 +4731,19 @@
         <v>213</v>
       </c>
       <c r="H67">
-        <v>-12060774</v>
+        <v>-1.2060774E7</v>
       </c>
       <c r="I67">
-        <v>-77084292</v>
+        <v>-7.7084292E7</v>
       </c>
       <c r="J67" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K67" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="68" ht="14.25" customHeight="1">
       <c r="A68" t="s">
         <v>214</v>
       </c>
@@ -4779,19 +4766,19 @@
         <v>217</v>
       </c>
       <c r="H68">
-        <v>-1205973372</v>
+        <v>-1.205973372E9</v>
       </c>
       <c r="I68">
-        <v>-7708081745</v>
+        <v>-7.708081745E9</v>
       </c>
       <c r="J68" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K68" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="69" ht="14.25" customHeight="1">
       <c r="A69" t="s">
         <v>218</v>
       </c>
@@ -4814,19 +4801,19 @@
         <v>220</v>
       </c>
       <c r="H69">
-        <v>-120577</v>
+        <v>-120577.0</v>
       </c>
       <c r="I69">
-        <v>-770816994</v>
+        <v>-7.70816994E8</v>
       </c>
       <c r="J69" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K69" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="70" ht="14.25" customHeight="1">
       <c r="A70" t="s">
         <v>221</v>
       </c>
@@ -4849,19 +4836,19 @@
         <v>227</v>
       </c>
       <c r="H70">
-        <v>-12061726</v>
+        <v>-1.20551446E8</v>
       </c>
       <c r="I70">
-        <v>-77082736</v>
+        <v>-7.7082736E7</v>
       </c>
       <c r="J70" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K70" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="71" ht="14.25" customHeight="1">
       <c r="A71" t="s">
         <v>23</v>
       </c>
@@ -4884,19 +4871,19 @@
         <v>230</v>
       </c>
       <c r="H71">
-        <v>-120551446</v>
+        <v>-1.20551446E8</v>
       </c>
       <c r="I71">
-        <v>-7708471</v>
+        <v>-7708471.0</v>
       </c>
       <c r="J71" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K71" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="72" ht="14.25" customHeight="1">
       <c r="A72" t="s">
         <v>231</v>
       </c>
@@ -4919,19 +4906,19 @@
         <v>233</v>
       </c>
       <c r="H72">
-        <v>-1205957777</v>
+        <v>-1.205957777E9</v>
       </c>
       <c r="I72">
-        <v>-770808874</v>
+        <v>-7.70808874E8</v>
       </c>
       <c r="J72" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K72" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="73" ht="14.25" customHeight="1">
       <c r="A73" t="s">
         <v>234</v>
       </c>
@@ -4954,19 +4941,19 @@
         <v>236</v>
       </c>
       <c r="H73">
-        <v>-12055507</v>
+        <v>-1.2055507E7</v>
       </c>
       <c r="I73">
-        <v>-77086982</v>
+        <v>-7.7086982E7</v>
       </c>
       <c r="J73" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K73" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="74" ht="14.25" customHeight="1">
       <c r="A74" t="s">
         <v>25</v>
       </c>
@@ -4989,19 +4976,19 @@
         <v>237</v>
       </c>
       <c r="H74">
-        <v>-12058386</v>
+        <v>-1.2058386E7</v>
       </c>
       <c r="I74">
-        <v>-77079987</v>
+        <v>-7.7079987E7</v>
       </c>
       <c r="J74" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K74" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="75" ht="14.25" customHeight="1">
       <c r="A75" t="s">
         <v>53</v>
       </c>
@@ -5024,19 +5011,19 @@
         <v>240</v>
       </c>
       <c r="H75">
-        <v>-12058352</v>
+        <v>-1.2058352E7</v>
       </c>
       <c r="I75">
-        <v>-77080834</v>
+        <v>-7.7080834E7</v>
       </c>
       <c r="J75" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K75" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="76" ht="14.25" customHeight="1">
       <c r="A76" t="s">
         <v>241</v>
       </c>
@@ -5059,19 +5046,19 @@
         <v>242</v>
       </c>
       <c r="H76">
-        <v>-120567</v>
+        <v>-120567.0</v>
       </c>
       <c r="I76">
-        <v>-77085</v>
+        <v>-77085.0</v>
       </c>
       <c r="J76" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K76" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="77" ht="14.25" customHeight="1">
       <c r="A77" t="s">
         <v>243</v>
       </c>
@@ -5094,19 +5081,19 @@
         <v>244</v>
       </c>
       <c r="H77">
-        <v>-12059236</v>
+        <v>-1.2059236E7</v>
       </c>
       <c r="I77">
-        <v>-77081608</v>
+        <v>-7.7081608E7</v>
       </c>
       <c r="J77" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K77" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="78" ht="14.25" customHeight="1">
       <c r="A78" t="s">
         <v>245</v>
       </c>
@@ -5129,19 +5116,19 @@
         <v>247</v>
       </c>
       <c r="H78">
-        <v>-1205791189</v>
+        <v>-1.205791189E9</v>
       </c>
       <c r="I78">
-        <v>-7708579389</v>
+        <v>-7.708579389E9</v>
       </c>
       <c r="J78" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K78" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="79" ht="14.25" customHeight="1">
       <c r="A79" t="s">
         <v>248</v>
       </c>
@@ -5164,19 +5151,19 @@
         <v>250</v>
       </c>
       <c r="H79">
-        <v>-12053856</v>
+        <v>-1.2053856E7</v>
       </c>
       <c r="I79">
-        <v>-77086632</v>
+        <v>-7.7086632E7</v>
       </c>
       <c r="J79" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K79" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="80" ht="14.25" customHeight="1">
       <c r="A80" t="s">
         <v>251</v>
       </c>
@@ -5199,19 +5186,19 @@
         <v>253</v>
       </c>
       <c r="H80">
-        <v>-1205922</v>
+        <v>-1205922.0</v>
       </c>
       <c r="I80">
-        <v>-77079594</v>
+        <v>-7.7079594E7</v>
       </c>
       <c r="J80" t="s">
         <v>62</v>
       </c>
       <c r="K80" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="81" ht="14.25" customHeight="1">
       <c r="A81" t="s">
         <v>254</v>
       </c>
@@ -5234,19 +5221,19 @@
         <v>255</v>
       </c>
       <c r="H81">
-        <v>-1205974253</v>
+        <v>-1.205974253E9</v>
       </c>
       <c r="I81">
-        <v>-7708080566</v>
+        <v>-7.708080566E9</v>
       </c>
       <c r="J81" t="s">
         <v>62</v>
       </c>
       <c r="K81" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="82" ht="14.25" customHeight="1">
       <c r="A82" t="s">
         <v>25</v>
       </c>
@@ -5269,19 +5256,19 @@
         <v>256</v>
       </c>
       <c r="H82">
-        <v>-12058576</v>
+        <v>-1.2058576E7</v>
       </c>
       <c r="I82">
-        <v>-77079769</v>
+        <v>-7.7079769E7</v>
       </c>
       <c r="J82" t="s">
         <v>62</v>
       </c>
       <c r="K82" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="83" ht="14.25" customHeight="1">
       <c r="A83" t="s">
         <v>163</v>
       </c>
@@ -5304,19 +5291,19 @@
         <v>256</v>
       </c>
       <c r="H83">
-        <v>-12058576</v>
+        <v>-1.2058576E7</v>
       </c>
       <c r="I83">
-        <v>-77079769</v>
+        <v>-7.7079769E7</v>
       </c>
       <c r="J83" t="s">
         <v>62</v>
       </c>
       <c r="K83" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="84" ht="14.25" customHeight="1">
       <c r="A84" t="s">
         <v>25</v>
       </c>
@@ -5339,19 +5326,19 @@
         <v>259</v>
       </c>
       <c r="H84">
-        <v>-12058012</v>
+        <v>-1.2058012E7</v>
       </c>
       <c r="I84">
-        <v>-77079983</v>
+        <v>-7.7079983E7</v>
       </c>
       <c r="J84" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K84" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="85" ht="14.25" customHeight="1">
       <c r="A85" t="s">
         <v>163</v>
       </c>
@@ -5374,19 +5361,19 @@
         <v>259</v>
       </c>
       <c r="H85">
-        <v>-12058012</v>
+        <v>-1.2058012E7</v>
       </c>
       <c r="I85">
-        <v>-77079983</v>
+        <v>-7.7079983E7</v>
       </c>
       <c r="J85" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K85" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="86" ht="14.25" customHeight="1">
       <c r="A86" t="s">
         <v>260</v>
       </c>
@@ -5409,19 +5396,19 @@
         <v>262</v>
       </c>
       <c r="H86">
-        <v>-12055613</v>
+        <v>-1.2055613E7</v>
       </c>
       <c r="I86">
-        <v>-77087195</v>
+        <v>-7.7087195E7</v>
       </c>
       <c r="J86" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K86" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="87" ht="14.25" customHeight="1">
       <c r="A87" t="s">
         <v>263</v>
       </c>
@@ -5444,19 +5431,19 @@
         <v>265</v>
       </c>
       <c r="H87">
-        <v>-12056613</v>
+        <v>-1.2056613E7</v>
       </c>
       <c r="I87">
-        <v>-77086961</v>
+        <v>-7.7086961E7</v>
       </c>
       <c r="J87" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K87" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="88" ht="14.25" customHeight="1">
       <c r="A88" t="s">
         <v>53</v>
       </c>
@@ -5479,19 +5466,19 @@
         <v>267</v>
       </c>
       <c r="H88">
-        <v>-12058254</v>
+        <v>-1.2058254E7</v>
       </c>
       <c r="I88">
-        <v>-77080432</v>
+        <v>-7.7080432E7</v>
       </c>
       <c r="J88" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K88" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="89" ht="14.25" customHeight="1">
       <c r="A89" t="s">
         <v>268</v>
       </c>
@@ -5514,19 +5501,19 @@
         <v>269</v>
       </c>
       <c r="H89">
-        <v>-12059274</v>
+        <v>-1.2059274E7</v>
       </c>
       <c r="I89">
-        <v>-770808</v>
+        <v>-770808.0</v>
       </c>
       <c r="J89" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K89" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="90" ht="14.25" customHeight="1">
       <c r="A90" t="s">
         <v>53</v>
       </c>
@@ -5549,19 +5536,19 @@
         <v>270</v>
       </c>
       <c r="H90">
-        <v>-12058254</v>
+        <v>-1.2058254E7</v>
       </c>
       <c r="I90">
-        <v>-77080432</v>
+        <v>-7.7080432E7</v>
       </c>
       <c r="J90" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K90" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="91" ht="14.25" customHeight="1">
       <c r="A91" t="s">
         <v>271</v>
       </c>
@@ -5584,19 +5571,19 @@
         <v>272</v>
       </c>
       <c r="H91">
-        <v>-1205671728</v>
+        <v>-1.205671728E9</v>
       </c>
       <c r="I91">
-        <v>-7708682219</v>
+        <v>-7.708682219E9</v>
       </c>
       <c r="J91" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K91" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="92" ht="14.25" customHeight="1">
       <c r="A92" t="s">
         <v>273</v>
       </c>
@@ -5619,19 +5606,19 @@
         <v>275</v>
       </c>
       <c r="H92">
-        <v>-12054019</v>
+        <v>-1.2054019E7</v>
       </c>
       <c r="I92">
-        <v>-77085599</v>
+        <v>-7.7085599E7</v>
       </c>
       <c r="J92" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K92" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="93" ht="14.25" customHeight="1">
       <c r="A93" t="s">
         <v>53</v>
       </c>
@@ -5654,19 +5641,19 @@
         <v>276</v>
       </c>
       <c r="H93">
-        <v>-12058552</v>
+        <v>-1.2058552E7</v>
       </c>
       <c r="I93">
-        <v>-77080920</v>
+        <v>-7.708092E7</v>
       </c>
       <c r="J93" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K93" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="94" ht="14.25" customHeight="1">
       <c r="A94" t="s">
         <v>38</v>
       </c>
@@ -5689,19 +5676,19 @@
         <v>278</v>
       </c>
       <c r="H94">
-        <v>-1205796644</v>
+        <v>-1.205796644E9</v>
       </c>
       <c r="I94">
-        <v>-7708147904</v>
+        <v>-7.708147904E9</v>
       </c>
       <c r="J94" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K94" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="95" ht="14.25" customHeight="1">
       <c r="A95" t="s">
         <v>25</v>
       </c>
@@ -5724,19 +5711,19 @@
         <v>279</v>
       </c>
       <c r="H95">
-        <v>-12057968</v>
+        <v>-1.2057968E7</v>
       </c>
       <c r="I95">
-        <v>-77079862</v>
+        <v>-7.7079862E7</v>
       </c>
       <c r="J95" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K95" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="96" ht="14.25" customHeight="1">
       <c r="A96" t="s">
         <v>280</v>
       </c>
@@ -5759,10 +5746,10 @@
         <v>282</v>
       </c>
       <c r="H96">
-        <v>-12059339</v>
+        <v>-1.2059339E7</v>
       </c>
       <c r="I96">
-        <v>-77087202</v>
+        <v>-7.7087202E7</v>
       </c>
       <c r="J96" t="s">
         <v>62</v>
@@ -5771,7 +5758,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="97" ht="14.25" customHeight="1">
       <c r="A97" t="s">
         <v>53</v>
       </c>
@@ -5794,19 +5781,19 @@
         <v>284</v>
       </c>
       <c r="H97">
-        <v>-12058455</v>
+        <v>-1.2058455E7</v>
       </c>
       <c r="I97">
-        <v>-77080218</v>
+        <v>-7.7080218E7</v>
       </c>
       <c r="J97" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K97" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="98" ht="14.25" customHeight="1">
       <c r="A98" t="s">
         <v>25</v>
       </c>
@@ -5829,19 +5816,19 @@
         <v>286</v>
       </c>
       <c r="H98">
-        <v>-12058223</v>
+        <v>-1.2058223E7</v>
       </c>
       <c r="I98">
-        <v>-77079791</v>
+        <v>-7.7079791E7</v>
       </c>
       <c r="J98" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K98" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="99" ht="14.25" customHeight="1">
       <c r="A99" t="s">
         <v>287</v>
       </c>
@@ -5864,19 +5851,19 @@
         <v>289</v>
       </c>
       <c r="H99">
-        <v>-1205992081</v>
+        <v>-1.205992081E9</v>
       </c>
       <c r="I99">
-        <v>-7708127214</v>
+        <v>-7.708127214E9</v>
       </c>
       <c r="J99" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K99" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="100" ht="14.25" customHeight="1">
       <c r="A100" t="s">
         <v>290</v>
       </c>
@@ -5899,19 +5886,19 @@
         <v>292</v>
       </c>
       <c r="H100">
-        <v>-12054729</v>
+        <v>-1.2054729E7</v>
       </c>
       <c r="I100">
-        <v>-77085504</v>
+        <v>-7.7085504E7</v>
       </c>
       <c r="J100" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K100" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="101" ht="14.25" customHeight="1">
       <c r="A101" t="s">
         <v>293</v>
       </c>
@@ -5934,19 +5921,19 @@
         <v>295</v>
       </c>
       <c r="H101">
-        <v>-12055623</v>
+        <v>-1.2055623E7</v>
       </c>
       <c r="I101">
-        <v>-77087197</v>
+        <v>-7.7087197E7</v>
       </c>
       <c r="J101" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K101" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="102" ht="14.25" customHeight="1">
       <c r="A102" t="s">
         <v>25</v>
       </c>
@@ -5969,19 +5956,19 @@
         <v>296</v>
       </c>
       <c r="H102">
-        <v>-12058521</v>
+        <v>-1.2058521E7</v>
       </c>
       <c r="I102">
-        <v>-77079742</v>
+        <v>-7.7079742E7</v>
       </c>
       <c r="J102" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K102" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="103" ht="14.25" customHeight="1">
       <c r="A103" t="s">
         <v>297</v>
       </c>
@@ -6004,19 +5991,19 @@
         <v>299</v>
       </c>
       <c r="H103">
-        <v>-1205393778</v>
+        <v>-1.205393778E9</v>
       </c>
       <c r="I103">
-        <v>-7708729878</v>
+        <v>-7.708729878E9</v>
       </c>
       <c r="J103" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K103" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="104" ht="14.25" customHeight="1">
       <c r="A104" t="s">
         <v>53</v>
       </c>
@@ -6039,19 +6026,19 @@
         <v>300</v>
       </c>
       <c r="H104">
-        <v>-12058258</v>
+        <v>-1.2058258E7</v>
       </c>
       <c r="I104">
-        <v>-77080569</v>
+        <v>-7.7080569E7</v>
       </c>
       <c r="J104" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K104" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="105" ht="14.25" customHeight="1">
       <c r="A105" t="s">
         <v>25</v>
       </c>
@@ -6074,19 +6061,19 @@
         <v>302</v>
       </c>
       <c r="H105">
-        <v>-12058521</v>
+        <v>-1.2058521E7</v>
       </c>
       <c r="I105">
-        <v>-77079742</v>
+        <v>-7.7079742E7</v>
       </c>
       <c r="J105" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K105" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="106" ht="14.25" customHeight="1">
       <c r="A106" t="s">
         <v>303</v>
       </c>
@@ -6109,19 +6096,19 @@
         <v>304</v>
       </c>
       <c r="H106">
-        <v>-1205940176</v>
+        <v>-1.205940176E9</v>
       </c>
       <c r="I106">
-        <v>-7708161868</v>
+        <v>-7.708161868E9</v>
       </c>
       <c r="J106" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K106" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="107" ht="14.25" customHeight="1">
       <c r="A107" t="s">
         <v>305</v>
       </c>
@@ -6144,19 +6131,19 @@
         <v>307</v>
       </c>
       <c r="H107">
-        <v>-1205744058</v>
+        <v>-1.205744058E9</v>
       </c>
       <c r="I107">
-        <v>-7708600328</v>
+        <v>-7.708600328E9</v>
       </c>
       <c r="J107" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K107" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="108" ht="14.25" customHeight="1">
       <c r="A108" t="s">
         <v>308</v>
       </c>
@@ -6179,19 +6166,19 @@
         <v>310</v>
       </c>
       <c r="H108">
-        <v>-12060812</v>
+        <v>-1.2060812E7</v>
       </c>
       <c r="I108">
-        <v>-77084473</v>
+        <v>-7.7084473E7</v>
       </c>
       <c r="J108" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K108" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="109" ht="14.25" customHeight="1">
       <c r="A109" t="s">
         <v>311</v>
       </c>
@@ -6214,19 +6201,19 @@
         <v>312</v>
       </c>
       <c r="H109">
-        <v>-1205791189</v>
+        <v>-1.205791189E9</v>
       </c>
       <c r="I109">
-        <v>-7708579389</v>
+        <v>-7.708579389E9</v>
       </c>
       <c r="J109" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K109" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="110" ht="14.25" customHeight="1">
       <c r="A110" t="s">
         <v>53</v>
       </c>
@@ -6249,19 +6236,19 @@
         <v>313</v>
       </c>
       <c r="H110">
-        <v>-12058455</v>
+        <v>-1.2058455E7</v>
       </c>
       <c r="I110">
-        <v>-77080218</v>
+        <v>-7.7080218E7</v>
       </c>
       <c r="J110" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K110" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="111" ht="14.25" customHeight="1">
       <c r="A111" t="s">
         <v>314</v>
       </c>
@@ -6284,19 +6271,19 @@
         <v>315</v>
       </c>
       <c r="H111">
-        <v>-12059857</v>
+        <v>-1.2059857E7</v>
       </c>
       <c r="I111">
-        <v>-77081168</v>
+        <v>-7.7081168E7</v>
       </c>
       <c r="J111" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K111" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="112" ht="14.25" customHeight="1">
       <c r="A112" t="s">
         <v>25</v>
       </c>
@@ -6319,19 +6306,19 @@
         <v>316</v>
       </c>
       <c r="H112">
-        <v>-12058446</v>
+        <v>-1.2058446E7</v>
       </c>
       <c r="I112">
-        <v>-77079712</v>
+        <v>-7.7079712E7</v>
       </c>
       <c r="J112" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K112" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="113" ht="14.25" customHeight="1">
       <c r="A113" t="s">
         <v>25</v>
       </c>
@@ -6354,19 +6341,19 @@
         <v>317</v>
       </c>
       <c r="H113">
-        <v>-12058357</v>
+        <v>-1.2058357E7</v>
       </c>
       <c r="I113">
-        <v>-77079686</v>
+        <v>-7.7079686E7</v>
       </c>
       <c r="J113" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K113" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="114" ht="14.25" customHeight="1">
       <c r="A114" t="s">
         <v>53</v>
       </c>
@@ -6389,19 +6376,19 @@
         <v>318</v>
       </c>
       <c r="H114">
-        <v>-12058378</v>
+        <v>-1.2058378E7</v>
       </c>
       <c r="I114">
-        <v>-77080139</v>
+        <v>-7.7080139E7</v>
       </c>
       <c r="J114" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K114" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="115" ht="14.25" customHeight="1">
       <c r="A115" t="s">
         <v>319</v>
       </c>
@@ -6424,19 +6411,19 @@
         <v>320</v>
       </c>
       <c r="H115">
-        <v>-12059204</v>
+        <v>-1.2059204E7</v>
       </c>
       <c r="I115">
-        <v>-77079622</v>
+        <v>-7.7079622E7</v>
       </c>
       <c r="J115" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K115" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="116" ht="14.25" customHeight="1">
       <c r="A116" t="s">
         <v>321</v>
       </c>
@@ -6459,19 +6446,19 @@
         <v>323</v>
       </c>
       <c r="H116">
-        <v>-120599869</v>
+        <v>-1.20599869E8</v>
       </c>
       <c r="I116">
-        <v>-7708184206</v>
+        <v>-7.708184206E9</v>
       </c>
       <c r="J116" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K116" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="117" ht="14.25" customHeight="1">
       <c r="A117" t="s">
         <v>324</v>
       </c>
@@ -6494,19 +6481,19 @@
         <v>325</v>
       </c>
       <c r="H117">
-        <v>-1205704639</v>
+        <v>-1.205704639E9</v>
       </c>
       <c r="I117">
-        <v>-7708647347</v>
+        <v>-7.708647347E9</v>
       </c>
       <c r="J117" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K117" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="118" ht="14.25" customHeight="1">
       <c r="A118" t="s">
         <v>326</v>
       </c>
@@ -6529,19 +6516,19 @@
         <v>327</v>
       </c>
       <c r="H118">
-        <v>-12057855</v>
+        <v>-1.2057855E7</v>
       </c>
       <c r="I118">
-        <v>-77080801</v>
+        <v>-7.7080801E7</v>
       </c>
       <c r="J118" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K118" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="119" ht="14.25" customHeight="1">
       <c r="A119" t="s">
         <v>38</v>
       </c>
@@ -6564,19 +6551,19 @@
         <v>328</v>
       </c>
       <c r="H119">
-        <v>-12058044</v>
+        <v>-1.2058044E7</v>
       </c>
       <c r="I119">
-        <v>-7708053</v>
+        <v>-7708053.0</v>
       </c>
       <c r="J119" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K119" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="120" ht="14.25" customHeight="1">
       <c r="A120" t="s">
         <v>53</v>
       </c>
@@ -6599,19 +6586,19 @@
         <v>329</v>
       </c>
       <c r="H120">
-        <v>-12058552</v>
+        <v>-1.2058552E7</v>
       </c>
       <c r="I120">
-        <v>-77080920</v>
+        <v>-7.708092E7</v>
       </c>
       <c r="J120" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K120" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="121" ht="14.25" customHeight="1">
       <c r="A121" t="s">
         <v>330</v>
       </c>
@@ -6634,19 +6621,19 @@
         <v>331</v>
       </c>
       <c r="H121">
-        <v>-12059274</v>
+        <v>-1.2059274E7</v>
       </c>
       <c r="I121">
-        <v>-770808</v>
+        <v>-770808.0</v>
       </c>
       <c r="J121" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K121" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="122" ht="14.25" customHeight="1">
       <c r="A122" t="s">
         <v>332</v>
       </c>
@@ -6669,19 +6656,19 @@
         <v>336</v>
       </c>
       <c r="H122">
-        <v>-12055491</v>
+        <v>-1.2055491E7</v>
       </c>
       <c r="I122">
-        <v>-77087924</v>
+        <v>-7.7087924E7</v>
       </c>
       <c r="J122" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K122" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="123" ht="14.25" customHeight="1">
       <c r="A123" t="s">
         <v>337</v>
       </c>
@@ -6704,19 +6691,19 @@
         <v>340</v>
       </c>
       <c r="H123">
-        <v>-12053839</v>
+        <v>-1.2053839E7</v>
       </c>
       <c r="I123">
-        <v>-77086625</v>
+        <v>-7.7086625E7</v>
       </c>
       <c r="J123" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K123" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="124" ht="14.25" customHeight="1">
       <c r="A124" t="s">
         <v>341</v>
       </c>
@@ -6739,19 +6726,19 @@
         <v>343</v>
       </c>
       <c r="H124">
-        <v>-1205651</v>
+        <v>-1205651.0</v>
       </c>
       <c r="I124">
-        <v>-77087056</v>
+        <v>-7.7087056E7</v>
       </c>
       <c r="J124" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K124" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="125" ht="14.25" customHeight="1">
       <c r="A125" t="s">
         <v>344</v>
       </c>
@@ -6774,19 +6761,19 @@
         <v>348</v>
       </c>
       <c r="H125">
-        <v>-120560768</v>
+        <v>-1.20560768E8</v>
       </c>
       <c r="I125">
-        <v>-770822742</v>
+        <v>-7.70822742E8</v>
       </c>
       <c r="J125" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K125" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="126" ht="14.25" customHeight="1">
       <c r="A126" t="s">
         <v>38</v>
       </c>
@@ -6809,19 +6796,19 @@
         <v>349</v>
       </c>
       <c r="H126">
-        <v>-1205792004</v>
+        <v>-1.205792004E9</v>
       </c>
       <c r="I126">
-        <v>-7708145421</v>
+        <v>-7.708145421E9</v>
       </c>
       <c r="J126" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K126" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="127" ht="14.25" customHeight="1">
       <c r="A127" t="s">
         <v>137</v>
       </c>
@@ -6844,19 +6831,19 @@
         <v>351</v>
       </c>
       <c r="H127">
-        <v>-12056342</v>
+        <v>-1.2056342E7</v>
       </c>
       <c r="I127">
-        <v>-77080938</v>
+        <v>-7.7080938E7</v>
       </c>
       <c r="J127" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K127" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="128" ht="14.25" customHeight="1">
       <c r="A128" t="s">
         <v>352</v>
       </c>
@@ -6879,19 +6866,19 @@
         <v>354</v>
       </c>
       <c r="H128">
-        <v>-12059581</v>
+        <v>-1.2059581E7</v>
       </c>
       <c r="I128">
-        <v>-77080704</v>
+        <v>-7.7080704E7</v>
       </c>
       <c r="J128" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K128" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="129" ht="14.25" customHeight="1">
       <c r="A129" t="s">
         <v>355</v>
       </c>
@@ -6914,19 +6901,19 @@
         <v>356</v>
       </c>
       <c r="H129">
-        <v>-12057104</v>
+        <v>-1.2057104E7</v>
       </c>
       <c r="I129">
-        <v>-77086707</v>
+        <v>-7.7086707E7</v>
       </c>
       <c r="J129" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K129" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="130" ht="14.25" customHeight="1">
       <c r="A130" t="s">
         <v>53</v>
       </c>
@@ -6949,19 +6936,19 @@
         <v>360</v>
       </c>
       <c r="H130">
-        <v>-12058392</v>
+        <v>-1.2058392E7</v>
       </c>
       <c r="I130">
-        <v>-77080974</v>
+        <v>-7.7080974E7</v>
       </c>
       <c r="J130" t="s">
         <v>62</v>
       </c>
       <c r="K130" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="131" ht="14.25" customHeight="1">
       <c r="A131" t="s">
         <v>361</v>
       </c>
@@ -6984,19 +6971,19 @@
         <v>364</v>
       </c>
       <c r="H131">
-        <v>-1205735758</v>
+        <v>-1.205735758E9</v>
       </c>
       <c r="I131">
-        <v>-7708610558</v>
+        <v>-7.708610558E9</v>
       </c>
       <c r="J131" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K131" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="132" ht="14.25" customHeight="1">
       <c r="A132" t="s">
         <v>25</v>
       </c>
@@ -7019,19 +7006,19 @@
         <v>365</v>
       </c>
       <c r="H132">
-        <v>-12058555</v>
+        <v>-1.2058555E7</v>
       </c>
       <c r="I132">
-        <v>-77079716</v>
+        <v>-7.7079716E7</v>
       </c>
       <c r="J132" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K132" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="133" ht="14.25" customHeight="1">
       <c r="A133" t="s">
         <v>25</v>
       </c>
@@ -7054,19 +7041,19 @@
         <v>366</v>
       </c>
       <c r="H133">
-        <v>-12058503</v>
+        <v>-1.2058503E7</v>
       </c>
       <c r="I133">
-        <v>-77079896</v>
+        <v>-7.7079896E7</v>
       </c>
       <c r="J133" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K133" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="134" ht="14.25" customHeight="1">
       <c r="A134" t="s">
         <v>51</v>
       </c>
@@ -7089,19 +7076,19 @@
         <v>367</v>
       </c>
       <c r="H134">
-        <v>-120543072</v>
+        <v>-1.20543072E8</v>
       </c>
       <c r="I134">
-        <v>-770845118</v>
+        <v>-7.70845118E8</v>
       </c>
       <c r="J134" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K134" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="135" ht="14.25" customHeight="1">
       <c r="A135" t="s">
         <v>368</v>
       </c>
@@ -7124,19 +7111,19 @@
         <v>369</v>
       </c>
       <c r="H135">
-        <v>-12055931</v>
+        <v>-1.2055931E7</v>
       </c>
       <c r="I135">
-        <v>-77082624</v>
+        <v>-7.7082624E7</v>
       </c>
       <c r="J135" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K135" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="136" ht="14.25" customHeight="1">
       <c r="A136" t="s">
         <v>25</v>
       </c>
@@ -7159,19 +7146,19 @@
         <v>371</v>
       </c>
       <c r="H136">
-        <v>-12058558</v>
+        <v>-1.2058558E7</v>
       </c>
       <c r="I136">
-        <v>-77079863</v>
+        <v>-7.7079863E7</v>
       </c>
       <c r="J136" t="s">
         <v>62</v>
       </c>
       <c r="K136" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="137" ht="14.25" customHeight="1">
       <c r="A137" t="s">
         <v>372</v>
       </c>
@@ -7194,19 +7181,19 @@
         <v>373</v>
       </c>
       <c r="H137">
-        <v>-1205732</v>
+        <v>-1205732.0</v>
       </c>
       <c r="I137">
-        <v>-7708635</v>
+        <v>-7708635.0</v>
       </c>
       <c r="J137" t="s">
         <v>62</v>
       </c>
       <c r="K137" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="138" ht="14.25" customHeight="1">
       <c r="A138" t="s">
         <v>23</v>
       </c>
@@ -7229,19 +7216,19 @@
         <v>376</v>
       </c>
       <c r="H138">
-        <v>-120547328</v>
+        <v>-1.20547328E8</v>
       </c>
       <c r="I138">
-        <v>-770851167</v>
+        <v>-7.70851167E8</v>
       </c>
       <c r="J138" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K138" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="139" ht="14.25" customHeight="1">
       <c r="A139" t="s">
         <v>25</v>
       </c>
@@ -7264,19 +7251,19 @@
         <v>379</v>
       </c>
       <c r="H139">
-        <v>-12057859</v>
+        <v>-1.2057859E7</v>
       </c>
       <c r="I139">
-        <v>-77079771</v>
+        <v>-7.7079771E7</v>
       </c>
       <c r="J139" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K139" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="140" ht="14.25" customHeight="1">
       <c r="A140" t="s">
         <v>380</v>
       </c>
@@ -7299,19 +7286,19 @@
         <v>382</v>
       </c>
       <c r="H140">
-        <v>-12059856</v>
+        <v>-1.2059856E7</v>
       </c>
       <c r="I140">
-        <v>-77081167</v>
+        <v>-7.7081167E7</v>
       </c>
       <c r="J140" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K140" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="141" ht="14.25" customHeight="1">
       <c r="A141" t="s">
         <v>383</v>
       </c>
@@ -7334,19 +7321,19 @@
         <v>385</v>
       </c>
       <c r="H141">
-        <v>-12059339</v>
+        <v>-1.2059339E7</v>
       </c>
       <c r="I141">
-        <v>-77087202</v>
+        <v>-7.7087202E7</v>
       </c>
       <c r="J141" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K141" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="142" ht="14.25" customHeight="1">
       <c r="A142" t="s">
         <v>344</v>
       </c>
@@ -7369,19 +7356,19 @@
         <v>387</v>
       </c>
       <c r="H142">
-        <v>-12056708</v>
+        <v>-1.2056708E7</v>
       </c>
       <c r="I142">
-        <v>-770815916</v>
+        <v>-7.70815916E8</v>
       </c>
       <c r="J142" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K142" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="143" ht="14.25" customHeight="1">
       <c r="A143" t="s">
         <v>388</v>
       </c>
@@ -7404,10 +7391,10 @@
         <v>392</v>
       </c>
       <c r="H143">
-        <v>-12054079</v>
+        <v>-1.2054079E7</v>
       </c>
       <c r="I143">
-        <v>-77085772</v>
+        <v>-7.7085772E7</v>
       </c>
       <c r="J143" t="s">
         <v>62</v>
@@ -7416,7 +7403,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="144" ht="14.25" customHeight="1">
       <c r="A144" t="s">
         <v>394</v>
       </c>
@@ -7439,19 +7426,19 @@
         <v>397</v>
       </c>
       <c r="H144">
-        <v>-12060274</v>
+        <v>-1.2060274E7</v>
       </c>
       <c r="I144">
-        <v>-77084485</v>
+        <v>-7.7084485E7</v>
       </c>
       <c r="J144" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K144" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="145" ht="14.25" customHeight="1">
       <c r="A145" t="s">
         <v>398</v>
       </c>
@@ -7474,19 +7461,19 @@
         <v>400</v>
       </c>
       <c r="H145">
-        <v>-12060527</v>
+        <v>-1.2060527E7</v>
       </c>
       <c r="I145">
-        <v>-77084247</v>
+        <v>-7.7084247E7</v>
       </c>
       <c r="J145" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K145" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="146" ht="14.25" customHeight="1">
       <c r="A146" t="s">
         <v>401</v>
       </c>
@@ -7509,19 +7496,19 @@
         <v>403</v>
       </c>
       <c r="H146">
-        <v>-12053551</v>
+        <v>-1.2053551E7</v>
       </c>
       <c r="I146">
-        <v>-77086277</v>
+        <v>-7.7086277E7</v>
       </c>
       <c r="J146" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K146" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="147" ht="14.25" customHeight="1">
       <c r="A147" t="s">
         <v>404</v>
       </c>
@@ -7544,19 +7531,19 @@
         <v>406</v>
       </c>
       <c r="H147">
-        <v>-12054729</v>
+        <v>-1.2054729E7</v>
       </c>
       <c r="I147">
-        <v>-77085504</v>
+        <v>-7.7085504E7</v>
       </c>
       <c r="J147" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K147" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="148" ht="14.25" customHeight="1">
       <c r="A148" t="s">
         <v>151</v>
       </c>
@@ -7579,19 +7566,19 @@
         <v>407</v>
       </c>
       <c r="H148">
-        <v>-12053413</v>
+        <v>-1.2053413E7</v>
       </c>
       <c r="I148">
-        <v>-77086877</v>
+        <v>-7.7086877E7</v>
       </c>
       <c r="J148" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K148" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="149" ht="14.25" customHeight="1">
       <c r="A149" t="s">
         <v>53</v>
       </c>
@@ -7614,19 +7601,19 @@
         <v>408</v>
       </c>
       <c r="H149">
-        <v>-12058444</v>
+        <v>-1.2058444E7</v>
       </c>
       <c r="I149">
-        <v>-77080372</v>
+        <v>-7.7080372E7</v>
       </c>
       <c r="J149" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K149" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="150" ht="14.25" customHeight="1">
       <c r="A150" t="s">
         <v>53</v>
       </c>
@@ -7649,19 +7636,19 @@
         <v>411</v>
       </c>
       <c r="H150">
-        <v>-12058455</v>
+        <v>-1.2058455E7</v>
       </c>
       <c r="I150">
-        <v>-77080218</v>
+        <v>-7.7080218E7</v>
       </c>
       <c r="J150" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K150" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="151" ht="14.25" customHeight="1">
       <c r="A151" t="s">
         <v>25</v>
       </c>
@@ -7684,19 +7671,19 @@
         <v>413</v>
       </c>
       <c r="H151">
-        <v>-12058210</v>
+        <v>-1.205821E7</v>
       </c>
       <c r="I151">
-        <v>-77079859</v>
+        <v>-7.7079859E7</v>
       </c>
       <c r="J151" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K151" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="152" ht="14.25" customHeight="1">
       <c r="A152" t="s">
         <v>414</v>
       </c>
@@ -7719,19 +7706,19 @@
         <v>416</v>
       </c>
       <c r="H152">
-        <v>-12059274</v>
+        <v>-1.2059274E7</v>
       </c>
       <c r="I152">
-        <v>-770808</v>
+        <v>-770808.0</v>
       </c>
       <c r="J152" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K152" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="153" ht="14.25" customHeight="1">
       <c r="A153" t="s">
         <v>417</v>
       </c>
@@ -7754,19 +7741,19 @@
         <v>419</v>
       </c>
       <c r="H153">
-        <v>-1205732</v>
+        <v>-1205732.0</v>
       </c>
       <c r="I153">
-        <v>-7708635</v>
+        <v>-7708635.0</v>
       </c>
       <c r="J153" t="s">
         <v>62</v>
       </c>
       <c r="K153" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="154" ht="14.25" customHeight="1">
       <c r="A154" t="s">
         <v>420</v>
       </c>
@@ -7789,19 +7776,19 @@
         <v>423</v>
       </c>
       <c r="H154">
-        <v>-12059642</v>
+        <v>-1.2059642E7</v>
       </c>
       <c r="I154">
-        <v>-77080672</v>
+        <v>-7.7080672E7</v>
       </c>
       <c r="J154" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K154" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="155" ht="14.25" customHeight="1">
       <c r="A155" t="s">
         <v>424</v>
       </c>
@@ -7824,19 +7811,19 @@
         <v>426</v>
       </c>
       <c r="H155">
-        <v>-1206028675</v>
+        <v>-1.206028675E9</v>
       </c>
       <c r="I155">
-        <v>-770813027</v>
+        <v>-7.70813027E8</v>
       </c>
       <c r="J155" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K155" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="156" ht="14.25" customHeight="1">
       <c r="A156" t="s">
         <v>53</v>
       </c>
@@ -7859,19 +7846,19 @@
         <v>428</v>
       </c>
       <c r="H156">
-        <v>-12058378</v>
+        <v>-1.2058378E7</v>
       </c>
       <c r="I156">
-        <v>-77080139</v>
+        <v>-7.7080139E7</v>
       </c>
       <c r="J156" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K156" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="157" ht="14.25" customHeight="1">
       <c r="A157" t="s">
         <v>429</v>
       </c>
@@ -7894,19 +7881,19 @@
         <v>431</v>
       </c>
       <c r="H157">
-        <v>-1206024726</v>
+        <v>-1.206024726E9</v>
       </c>
       <c r="I157">
-        <v>-7708256338</v>
+        <v>-7.708256338E9</v>
       </c>
       <c r="J157" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K157" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="158" ht="14.25" customHeight="1">
       <c r="A158" t="s">
         <v>25</v>
       </c>
@@ -7929,19 +7916,19 @@
         <v>432</v>
       </c>
       <c r="H158">
-        <v>-12058012</v>
+        <v>-1.2058012E7</v>
       </c>
       <c r="I158">
-        <v>-77079983</v>
+        <v>-7.7079983E7</v>
       </c>
       <c r="J158" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K158" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="159" ht="14.25" customHeight="1">
       <c r="A159" t="s">
         <v>433</v>
       </c>
@@ -7964,19 +7951,19 @@
         <v>434</v>
       </c>
       <c r="H159">
-        <v>-12059274</v>
+        <v>-1.2059274E7</v>
       </c>
       <c r="I159">
-        <v>-770808</v>
+        <v>-770808.0</v>
       </c>
       <c r="J159" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K159" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="160" ht="14.25" customHeight="1">
       <c r="A160" t="s">
         <v>435</v>
       </c>
@@ -7999,19 +7986,19 @@
         <v>438</v>
       </c>
       <c r="H160">
-        <v>-120604022</v>
+        <v>-1.20604022E8</v>
       </c>
       <c r="I160">
-        <v>-770818246</v>
+        <v>-7.70818246E8</v>
       </c>
       <c r="J160" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K160" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="161" ht="14.25" customHeight="1">
       <c r="A161" t="s">
         <v>439</v>
       </c>
@@ -8034,19 +8021,19 @@
         <v>441</v>
       </c>
       <c r="H161">
-        <v>-12059274</v>
+        <v>-1.2059274E7</v>
       </c>
       <c r="I161">
-        <v>-770808</v>
+        <v>-770808.0</v>
       </c>
       <c r="J161" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K161" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="162" ht="14.25" customHeight="1">
       <c r="A162" t="s">
         <v>442</v>
       </c>
@@ -8069,19 +8056,19 @@
         <v>444</v>
       </c>
       <c r="H162">
-        <v>-12054079</v>
+        <v>-1.2054079E7</v>
       </c>
       <c r="I162">
-        <v>-77085772</v>
+        <v>-7.7085772E7</v>
       </c>
       <c r="J162" t="s">
         <v>62</v>
       </c>
       <c r="K162" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="163" ht="14.25" customHeight="1">
       <c r="A163" t="s">
         <v>445</v>
       </c>
@@ -8104,19 +8091,19 @@
         <v>448</v>
       </c>
       <c r="H163">
-        <v>-12060315</v>
+        <v>-1.2060315E7</v>
       </c>
       <c r="I163">
-        <v>-77084368</v>
+        <v>-7.7084368E7</v>
       </c>
       <c r="J163" t="s">
         <v>62</v>
       </c>
       <c r="K163" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="164" ht="14.25" customHeight="1">
       <c r="A164" t="s">
         <v>53</v>
       </c>
@@ -8139,19 +8126,19 @@
         <v>450</v>
       </c>
       <c r="H164">
-        <v>-12058378</v>
+        <v>-1.2058378E7</v>
       </c>
       <c r="I164">
-        <v>-77080139</v>
+        <v>-7.7080139E7</v>
       </c>
       <c r="J164" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K164" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="165" ht="14.25" customHeight="1">
       <c r="A165" t="s">
         <v>344</v>
       </c>
@@ -8174,19 +8161,19 @@
         <v>451</v>
       </c>
       <c r="H165">
-        <v>-120565319</v>
+        <v>-1.20565319E8</v>
       </c>
       <c r="I165">
-        <v>-770820465</v>
+        <v>-7.70820465E8</v>
       </c>
       <c r="J165" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K165" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="166" ht="14.25" customHeight="1">
       <c r="A166" t="s">
         <v>452</v>
       </c>
@@ -8209,19 +8196,19 @@
         <v>455</v>
       </c>
       <c r="H166">
-        <v>-12059218</v>
+        <v>-1.2059218E7</v>
       </c>
       <c r="I166">
-        <v>-77079587</v>
+        <v>-7.7079587E7</v>
       </c>
       <c r="J166" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K166" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="167" ht="14.25" customHeight="1">
       <c r="A167" t="s">
         <v>456</v>
       </c>
@@ -8244,19 +8231,19 @@
         <v>457</v>
       </c>
       <c r="H167">
-        <v>-12058299</v>
+        <v>-1.2058299E7</v>
       </c>
       <c r="I167">
-        <v>-77080642</v>
+        <v>-7.7080642E7</v>
       </c>
       <c r="J167" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K167" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="168" ht="14.25" customHeight="1">
       <c r="A168" t="s">
         <v>151</v>
       </c>
@@ -8279,19 +8266,19 @@
         <v>460</v>
       </c>
       <c r="H168">
-        <v>-12053404</v>
+        <v>-1.2053404E7</v>
       </c>
       <c r="I168">
-        <v>-77087545</v>
+        <v>-7.7087545E7</v>
       </c>
       <c r="J168" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K168" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="169" ht="14.25" customHeight="1">
       <c r="A169" t="s">
         <v>23</v>
       </c>
@@ -8314,19 +8301,19 @@
         <v>462</v>
       </c>
       <c r="H169">
-        <v>-120545941</v>
+        <v>-1.20545941E8</v>
       </c>
       <c r="I169">
-        <v>-770850302</v>
+        <v>-7.70850302E8</v>
       </c>
       <c r="J169" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K169" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="170" ht="14.25" customHeight="1">
       <c r="A170" t="s">
         <v>463</v>
       </c>
@@ -8349,19 +8336,19 @@
         <v>465</v>
       </c>
       <c r="H170">
-        <v>-12056773</v>
+        <v>-1.2056773E7</v>
       </c>
       <c r="I170">
-        <v>-77086538</v>
+        <v>-7.7086538E7</v>
       </c>
       <c r="J170" t="s">
         <v>62</v>
       </c>
       <c r="K170" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="171" ht="14.25" customHeight="1">
       <c r="A171" t="s">
         <v>466</v>
       </c>
@@ -8384,19 +8371,19 @@
         <v>468</v>
       </c>
       <c r="H171">
-        <v>-1205790019</v>
+        <v>-1.205790019E9</v>
       </c>
       <c r="I171">
-        <v>-7708584828</v>
+        <v>-7.708584828E9</v>
       </c>
       <c r="J171" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K171" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="172" ht="14.25" customHeight="1">
       <c r="A172" t="s">
         <v>137</v>
       </c>
@@ -8419,19 +8406,19 @@
         <v>471</v>
       </c>
       <c r="H172">
-        <v>-12056269</v>
+        <v>-1.2056269E7</v>
       </c>
       <c r="I172">
-        <v>-77081025</v>
+        <v>-7.7081025E7</v>
       </c>
       <c r="J172" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K172" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="173" ht="14.25" customHeight="1">
       <c r="A173" t="s">
         <v>472</v>
       </c>
@@ -8454,19 +8441,19 @@
         <v>474</v>
       </c>
       <c r="H173">
-        <v>-1205623</v>
+        <v>-1205623.0</v>
       </c>
       <c r="I173">
-        <v>-7708746</v>
+        <v>-7708746.0</v>
       </c>
       <c r="J173" t="s">
         <v>62</v>
       </c>
       <c r="K173" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="174" ht="14.25" customHeight="1">
       <c r="A174" t="s">
         <v>475</v>
       </c>
@@ -8489,19 +8476,19 @@
         <v>477</v>
       </c>
       <c r="H174">
-        <v>-12060636</v>
+        <v>-1.2060636E7</v>
       </c>
       <c r="I174">
-        <v>-77082914</v>
+        <v>-7.7082914E7</v>
       </c>
       <c r="J174" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K174" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="175" ht="14.25" customHeight="1">
       <c r="A175" t="s">
         <v>478</v>
       </c>
@@ -8523,20 +8510,20 @@
       <c r="G175" t="s">
         <v>482</v>
       </c>
-      <c r="H175">
-        <v>-1204513</v>
+      <c r="H175" s="1">
+        <v>-1205513.0</v>
       </c>
       <c r="I175">
-        <v>-7607812</v>
+        <v>-7.7080643E7</v>
       </c>
       <c r="J175" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K175" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="176" ht="14.25" customHeight="1">
       <c r="A176" t="s">
         <v>53</v>
       </c>
@@ -8559,19 +8546,19 @@
         <v>483</v>
       </c>
       <c r="H176">
-        <v>-12058300</v>
+        <v>-1.20583E7</v>
       </c>
       <c r="I176">
-        <v>-77080643</v>
+        <v>-7.7080643E7</v>
       </c>
       <c r="J176" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K176" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="177" ht="14.25" customHeight="1">
       <c r="A177" t="s">
         <v>25</v>
       </c>
@@ -8594,19 +8581,19 @@
         <v>484</v>
       </c>
       <c r="H177">
-        <v>-12058558</v>
+        <v>-1.2058558E7</v>
       </c>
       <c r="I177">
-        <v>-77079863</v>
+        <v>-7.7079863E7</v>
       </c>
       <c r="J177" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K177" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="178" ht="14.25" customHeight="1">
       <c r="A178" t="s">
         <v>485</v>
       </c>
@@ -8629,19 +8616,19 @@
         <v>487</v>
       </c>
       <c r="H178">
-        <v>-1205645147</v>
+        <v>-1.205645147E9</v>
       </c>
       <c r="I178">
-        <v>-7708684178</v>
+        <v>-7.708684178E9</v>
       </c>
       <c r="J178" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K178" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="179" ht="14.25" customHeight="1">
       <c r="A179" t="s">
         <v>25</v>
       </c>
@@ -8664,19 +8651,19 @@
         <v>489</v>
       </c>
       <c r="H179">
-        <v>-12058459</v>
+        <v>-1.2058459E7</v>
       </c>
       <c r="I179">
-        <v>-77079841</v>
+        <v>-7.7079841E7</v>
       </c>
       <c r="J179" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K179" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="180" ht="14.25" customHeight="1">
       <c r="A180" t="s">
         <v>25</v>
       </c>
@@ -8699,19 +8686,19 @@
         <v>490</v>
       </c>
       <c r="H180">
-        <v>-12058576</v>
+        <v>-1.2058576E7</v>
       </c>
       <c r="I180">
-        <v>-77079769</v>
+        <v>-7.7079769E7</v>
       </c>
       <c r="J180" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K180" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="181" ht="14.25" customHeight="1">
       <c r="A181" t="s">
         <v>491</v>
       </c>
@@ -8734,19 +8721,19 @@
         <v>493</v>
       </c>
       <c r="H181">
-        <v>-12060574</v>
+        <v>-1.2060574E7</v>
       </c>
       <c r="I181">
-        <v>-77082192</v>
+        <v>-7.7082192E7</v>
       </c>
       <c r="J181" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K181" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="182" ht="14.25" customHeight="1">
       <c r="A182" t="s">
         <v>137</v>
       </c>
@@ -8769,19 +8756,19 @@
         <v>494</v>
       </c>
       <c r="H182">
-        <v>-12056327</v>
+        <v>-1.2056327E7</v>
       </c>
       <c r="I182">
-        <v>-77080965</v>
+        <v>-7.7080965E7</v>
       </c>
       <c r="J182" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K182" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="183" ht="14.25" customHeight="1">
       <c r="A183" t="s">
         <v>53</v>
       </c>
@@ -8804,19 +8791,19 @@
         <v>495</v>
       </c>
       <c r="H183">
-        <v>-12058444</v>
+        <v>-1.2058444E7</v>
       </c>
       <c r="I183">
-        <v>-77080372</v>
+        <v>-7.7080372E7</v>
       </c>
       <c r="J183" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K183" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="184" ht="14.25" customHeight="1">
       <c r="A184" t="s">
         <v>496</v>
       </c>
@@ -8839,19 +8826,19 @@
         <v>502</v>
       </c>
       <c r="H184">
-        <v>-1205712839</v>
+        <v>-1.205712839E9</v>
       </c>
       <c r="I184">
-        <v>-7708622389</v>
+        <v>-7.708622389E9</v>
       </c>
       <c r="J184" t="s">
         <v>62</v>
       </c>
       <c r="K184" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="185" ht="14.25" customHeight="1">
       <c r="A185" t="s">
         <v>503</v>
       </c>
@@ -8874,19 +8861,19 @@
         <v>504</v>
       </c>
       <c r="H185">
-        <v>-12059339</v>
+        <v>-1.2059339E7</v>
       </c>
       <c r="I185">
-        <v>-77087202</v>
+        <v>-7.7087202E7</v>
       </c>
       <c r="J185" t="s">
         <v>62</v>
       </c>
       <c r="K185" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="186" ht="14.25" customHeight="1">
       <c r="A186" t="s">
         <v>53</v>
       </c>
@@ -8909,19 +8896,19 @@
         <v>508</v>
       </c>
       <c r="H186">
-        <v>-12058254</v>
+        <v>-1.2058254E7</v>
       </c>
       <c r="I186">
-        <v>-77080432</v>
+        <v>-7.7080432E7</v>
       </c>
       <c r="J186" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K186" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="187" ht="14.25" customHeight="1">
       <c r="A187" t="s">
         <v>53</v>
       </c>
@@ -8944,19 +8931,19 @@
         <v>509</v>
       </c>
       <c r="H187">
-        <v>-12058552</v>
+        <v>-1.2058552E7</v>
       </c>
       <c r="I187">
-        <v>-77080920</v>
+        <v>-7.708092E7</v>
       </c>
       <c r="J187" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K187" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="188" ht="14.25" customHeight="1">
       <c r="A188" t="s">
         <v>510</v>
       </c>
@@ -8979,19 +8966,19 @@
         <v>512</v>
       </c>
       <c r="H188">
-        <v>-12058944</v>
+        <v>-1.2058944E7</v>
       </c>
       <c r="I188">
-        <v>-77079397</v>
+        <v>-7.7079397E7</v>
       </c>
       <c r="J188" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K188" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="189" ht="14.25" customHeight="1">
       <c r="A189" t="s">
         <v>513</v>
       </c>
@@ -9014,19 +9001,19 @@
         <v>514</v>
       </c>
       <c r="H189">
-        <v>-12054729</v>
+        <v>-1.2054729E7</v>
       </c>
       <c r="I189">
-        <v>-77085504</v>
+        <v>-7.7085504E7</v>
       </c>
       <c r="J189" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K189" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="190" ht="14.25" customHeight="1">
       <c r="A190" t="s">
         <v>515</v>
       </c>
@@ -9049,19 +9036,19 @@
         <v>516</v>
       </c>
       <c r="H190">
-        <v>-120596026</v>
+        <v>-1.20596026E8</v>
       </c>
       <c r="I190">
-        <v>-7708201627</v>
+        <v>-7.708201627E9</v>
       </c>
       <c r="J190" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K190" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="191" ht="14.25" customHeight="1">
       <c r="A191" t="s">
         <v>25</v>
       </c>
@@ -9084,19 +9071,19 @@
         <v>518</v>
       </c>
       <c r="H191">
-        <v>-12058446</v>
+        <v>-1.2058446E7</v>
       </c>
       <c r="I191">
-        <v>-77079712</v>
+        <v>-7.7079712E7</v>
       </c>
       <c r="J191" t="s">
         <v>62</v>
       </c>
       <c r="K191" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="192" ht="14.25" customHeight="1">
       <c r="A192" t="s">
         <v>519</v>
       </c>
@@ -9119,19 +9106,19 @@
         <v>522</v>
       </c>
       <c r="H192">
-        <v>-12053929</v>
+        <v>-1.2053929E7</v>
       </c>
       <c r="I192">
-        <v>-77086401</v>
+        <v>-7.7086401E7</v>
       </c>
       <c r="J192" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K192" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="193" ht="14.25" customHeight="1">
       <c r="A193" t="s">
         <v>523</v>
       </c>
@@ -9154,19 +9141,19 @@
         <v>525</v>
       </c>
       <c r="H193">
-        <v>-12059411</v>
+        <v>-1.2059411E7</v>
       </c>
       <c r="I193">
-        <v>-77080058</v>
+        <v>-7.7080058E7</v>
       </c>
       <c r="J193" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K193" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="194" ht="14.25" customHeight="1">
       <c r="A194" t="s">
         <v>526</v>
       </c>
@@ -9189,19 +9176,19 @@
         <v>525</v>
       </c>
       <c r="H194">
-        <v>-12060887</v>
+        <v>-1.2060887E7</v>
       </c>
       <c r="I194">
-        <v>-77084615</v>
+        <v>-7.7084615E7</v>
       </c>
       <c r="J194" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K194" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="195" ht="14.25" customHeight="1">
       <c r="A195" t="s">
         <v>53</v>
       </c>
@@ -9224,19 +9211,19 @@
         <v>527</v>
       </c>
       <c r="H195">
-        <v>-12058300</v>
+        <v>-1.20583E7</v>
       </c>
       <c r="I195">
-        <v>-77080643</v>
+        <v>-7.7080643E7</v>
       </c>
       <c r="J195" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K195" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="196" ht="14.25" customHeight="1">
       <c r="A196" t="s">
         <v>528</v>
       </c>
@@ -9259,19 +9246,19 @@
         <v>532</v>
       </c>
       <c r="H196">
-        <v>-12056669</v>
+        <v>-1.2056669E7</v>
       </c>
       <c r="I196">
-        <v>-77085002</v>
+        <v>-7.7085002E7</v>
       </c>
       <c r="J196" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K196" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="197" ht="14.25" customHeight="1">
       <c r="A197" t="s">
         <v>533</v>
       </c>
@@ -9294,19 +9281,19 @@
         <v>536</v>
       </c>
       <c r="H197">
-        <v>-12057323</v>
+        <v>-1.2057323E7</v>
       </c>
       <c r="I197">
-        <v>-77085923</v>
+        <v>-7.7085923E7</v>
       </c>
       <c r="J197" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K197" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="198" ht="14.25" customHeight="1">
       <c r="A198" t="s">
         <v>53</v>
       </c>
@@ -9329,19 +9316,19 @@
         <v>537</v>
       </c>
       <c r="H198">
-        <v>-12058444</v>
+        <v>-1.2058444E7</v>
       </c>
       <c r="I198">
-        <v>-77080372</v>
+        <v>-7.7080372E7</v>
       </c>
       <c r="J198" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K198" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="199" ht="14.25" customHeight="1">
       <c r="A199" t="s">
         <v>53</v>
       </c>
@@ -9364,19 +9351,19 @@
         <v>538</v>
       </c>
       <c r="H199">
-        <v>-12058378</v>
+        <v>-1.2058378E7</v>
       </c>
       <c r="I199">
-        <v>-77080139</v>
+        <v>-7.7080139E7</v>
       </c>
       <c r="J199" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K199" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="200" ht="14.25" customHeight="1">
       <c r="A200" t="s">
         <v>539</v>
       </c>
@@ -9399,19 +9386,19 @@
         <v>541</v>
       </c>
       <c r="H200">
-        <v>-120573215</v>
+        <v>-1.20573215E8</v>
       </c>
       <c r="I200">
-        <v>-7708623939</v>
+        <v>-7.708623939E9</v>
       </c>
       <c r="J200" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K200" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="201" ht="14.25" customHeight="1">
       <c r="A201" t="s">
         <v>25</v>
       </c>
@@ -9434,19 +9421,19 @@
         <v>543</v>
       </c>
       <c r="H201">
-        <v>-12058555</v>
+        <v>-1.2058555E7</v>
       </c>
       <c r="I201">
-        <v>-77079716</v>
+        <v>-7.7079716E7</v>
       </c>
       <c r="J201" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K201" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="202" ht="14.25" customHeight="1">
       <c r="A202" t="s">
         <v>544</v>
       </c>
@@ -9469,19 +9456,19 @@
         <v>546</v>
       </c>
       <c r="H202">
-        <v>-12060606</v>
+        <v>-1.2060606E7</v>
       </c>
       <c r="I202">
-        <v>-77082258</v>
+        <v>-7.7082258E7</v>
       </c>
       <c r="J202" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K202" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="203" ht="14.25" customHeight="1">
       <c r="A203" t="s">
         <v>53</v>
       </c>
@@ -9504,19 +9491,19 @@
         <v>549</v>
       </c>
       <c r="H203">
-        <v>-12058455</v>
+        <v>-1.2058455E7</v>
       </c>
       <c r="I203">
-        <v>-77080218</v>
+        <v>-7.7080218E7</v>
       </c>
       <c r="J203" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K203" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="204" ht="14.25" customHeight="1">
       <c r="A204" t="s">
         <v>550</v>
       </c>
@@ -9539,10 +9526,10 @@
         <v>554</v>
       </c>
       <c r="H204">
-        <v>-13059507</v>
-      </c>
-      <c r="I204">
-        <v>-72087238</v>
+        <v>-1.2053551E7</v>
+      </c>
+      <c r="I204" s="1">
+        <v>-7.2085238E7</v>
       </c>
       <c r="J204" t="s">
         <v>62</v>
@@ -9551,7 +9538,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="205" ht="14.25" customHeight="1">
       <c r="A205" t="s">
         <v>555</v>
       </c>
@@ -9574,10 +9561,10 @@
         <v>557</v>
       </c>
       <c r="H205">
-        <v>-12053551</v>
+        <v>-1.2053551E7</v>
       </c>
       <c r="I205">
-        <v>-77086277</v>
+        <v>-7.7086277E7</v>
       </c>
       <c r="J205" t="s">
         <v>62</v>
@@ -9586,7 +9573,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="206" ht="14.25" customHeight="1">
       <c r="A206" t="s">
         <v>558</v>
       </c>
@@ -9609,19 +9596,19 @@
         <v>560</v>
       </c>
       <c r="H206">
-        <v>-12059274</v>
+        <v>-1.2059274E7</v>
       </c>
       <c r="I206">
-        <v>-770808</v>
+        <v>-770808.0</v>
       </c>
       <c r="J206" t="s">
         <v>62</v>
       </c>
       <c r="K206" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="207" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="207" ht="14.25" customHeight="1">
       <c r="A207" t="s">
         <v>561</v>
       </c>
@@ -9644,19 +9631,19 @@
         <v>564</v>
       </c>
       <c r="H207">
-        <v>-120602174</v>
+        <v>-1.20602174E8</v>
       </c>
       <c r="I207">
-        <v>-7708176537</v>
+        <v>-7.708176537E9</v>
       </c>
       <c r="J207" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K207" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="208" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="208" ht="14.25" customHeight="1">
       <c r="A208" t="s">
         <v>565</v>
       </c>
@@ -9679,19 +9666,19 @@
         <v>567</v>
       </c>
       <c r="H208">
-        <v>-15059507</v>
-      </c>
-      <c r="I208">
-        <v>-77087238</v>
+        <v>-1.2057333E7</v>
+      </c>
+      <c r="I208" s="1">
+        <v>-7.7085238E7</v>
       </c>
       <c r="J208" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K208" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="209" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="209" ht="14.25" customHeight="1">
       <c r="A209" t="s">
         <v>568</v>
       </c>
@@ -9714,19 +9701,19 @@
         <v>570</v>
       </c>
       <c r="H209">
-        <v>-12057333</v>
+        <v>-1.2057333E7</v>
       </c>
       <c r="I209">
-        <v>-77085928</v>
+        <v>-7.7085928E7</v>
       </c>
       <c r="J209" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K209" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="210" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="210" ht="14.25" customHeight="1">
       <c r="A210" t="s">
         <v>25</v>
       </c>
@@ -9749,19 +9736,19 @@
         <v>571</v>
       </c>
       <c r="H210">
-        <v>-12057968</v>
+        <v>-1.2057968E7</v>
       </c>
       <c r="I210">
-        <v>-77079862</v>
+        <v>-7.7079862E7</v>
       </c>
       <c r="J210" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K210" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="211" ht="14.25" customHeight="1">
       <c r="A211" t="s">
         <v>572</v>
       </c>
@@ -9784,19 +9771,19 @@
         <v>573</v>
       </c>
       <c r="H211">
-        <v>-12059106</v>
+        <v>-1.2059106E7</v>
       </c>
       <c r="I211">
-        <v>-77079643</v>
+        <v>-7.7079643E7</v>
       </c>
       <c r="J211" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K211" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="212" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="212" ht="14.25" customHeight="1">
       <c r="A212" t="s">
         <v>574</v>
       </c>
@@ -9819,19 +9806,19 @@
         <v>575</v>
       </c>
       <c r="H212">
-        <v>-12059106</v>
+        <v>-1.2059106E7</v>
       </c>
       <c r="I212">
-        <v>-77079643</v>
+        <v>-7.7079643E7</v>
       </c>
       <c r="J212" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K212" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="213" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="213" ht="14.25" customHeight="1">
       <c r="A213" t="s">
         <v>23</v>
       </c>
@@ -9854,19 +9841,19 @@
         <v>576</v>
       </c>
       <c r="H213">
-        <v>-120554125</v>
+        <v>-1.20554125E8</v>
       </c>
       <c r="I213">
-        <v>-770829659</v>
+        <v>-7.70829659E8</v>
       </c>
       <c r="J213" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K213" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="214" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="214" ht="14.25" customHeight="1">
       <c r="A214" t="s">
         <v>577</v>
       </c>
@@ -9889,19 +9876,19 @@
         <v>578</v>
       </c>
       <c r="H214">
-        <v>-12054729</v>
+        <v>-1.2054729E7</v>
       </c>
       <c r="I214">
-        <v>-77085504</v>
+        <v>-7.7085504E7</v>
       </c>
       <c r="J214" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K214" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="215" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="215" ht="14.25" customHeight="1">
       <c r="A215" t="s">
         <v>23</v>
       </c>
@@ -9924,19 +9911,19 @@
         <v>579</v>
       </c>
       <c r="H215">
-        <v>-120544912</v>
+        <v>-1.20544912E8</v>
       </c>
       <c r="I215">
-        <v>-770845148</v>
+        <v>-7.70845148E8</v>
       </c>
       <c r="J215" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K215" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="216" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="216" ht="14.25" customHeight="1">
       <c r="A216" t="s">
         <v>137</v>
       </c>
@@ -9959,19 +9946,19 @@
         <v>580</v>
       </c>
       <c r="H216">
-        <v>-12056125</v>
+        <v>-1.2056125E7</v>
       </c>
       <c r="I216">
-        <v>-77081382</v>
+        <v>-7.7081382E7</v>
       </c>
       <c r="J216" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K216" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="217" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="217" ht="14.25" customHeight="1">
       <c r="A217" t="s">
         <v>25</v>
       </c>
@@ -9994,19 +9981,19 @@
         <v>582</v>
       </c>
       <c r="H217">
-        <v>-12058414</v>
+        <v>-1.2058414E7</v>
       </c>
       <c r="I217">
-        <v>-77079889</v>
+        <v>-7.7079889E7</v>
       </c>
       <c r="J217" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K217" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="218" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="218" ht="14.25" customHeight="1">
       <c r="A218" t="s">
         <v>38</v>
       </c>
@@ -10029,19 +10016,19 @@
         <v>584</v>
       </c>
       <c r="H218">
-        <v>-120567</v>
+        <v>-120567.0</v>
       </c>
       <c r="I218">
-        <v>-77082</v>
+        <v>-77082.0</v>
       </c>
       <c r="J218" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K218" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="219" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="219" ht="14.25" customHeight="1">
       <c r="A219" t="s">
         <v>585</v>
       </c>
@@ -10064,19 +10051,19 @@
         <v>587</v>
       </c>
       <c r="H219">
-        <v>-12054804</v>
+        <v>-1.2054804E7</v>
       </c>
       <c r="I219">
-        <v>-77085347</v>
+        <v>-7.7085347E7</v>
       </c>
       <c r="J219" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K219" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="220" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="220" ht="14.25" customHeight="1">
       <c r="A220" t="s">
         <v>588</v>
       </c>
@@ -10099,19 +10086,19 @@
         <v>591</v>
       </c>
       <c r="H220">
-        <v>-1205955986</v>
+        <v>-1.205955986E9</v>
       </c>
       <c r="I220">
-        <v>-7708088826</v>
+        <v>-7.708088826E9</v>
       </c>
       <c r="J220" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K220" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="221" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="221" ht="14.25" customHeight="1">
       <c r="A221" t="s">
         <v>137</v>
       </c>
@@ -10134,19 +10121,19 @@
         <v>593</v>
       </c>
       <c r="H221">
-        <v>-12056545</v>
+        <v>-1.2056545E7</v>
       </c>
       <c r="I221">
-        <v>-7708216</v>
+        <v>-7708216.0</v>
       </c>
       <c r="J221" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K221" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="222" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="222" ht="14.25" customHeight="1">
       <c r="A222" t="s">
         <v>38</v>
       </c>
@@ -10169,19 +10156,19 @@
         <v>594</v>
       </c>
       <c r="H222">
-        <v>-1205697598</v>
+        <v>-1.205697598E9</v>
       </c>
       <c r="I222">
-        <v>-7708196071</v>
+        <v>-7.708196071E9</v>
       </c>
       <c r="J222" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K222" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="223" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="223" ht="14.25" customHeight="1">
       <c r="A223" t="s">
         <v>25</v>
       </c>
@@ -10204,10 +10191,10 @@
         <v>596</v>
       </c>
       <c r="H223">
-        <v>-12058534</v>
+        <v>-1.2058534E7</v>
       </c>
       <c r="I223">
-        <v>-77079864</v>
+        <v>-7.7079864E7</v>
       </c>
       <c r="J223" t="s">
         <v>62</v>
@@ -10216,7 +10203,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="224" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="224" ht="14.25" customHeight="1">
       <c r="A224" t="s">
         <v>25</v>
       </c>
@@ -10239,19 +10226,19 @@
         <v>597</v>
       </c>
       <c r="H224">
-        <v>-12057977</v>
+        <v>-1.2057977E7</v>
       </c>
       <c r="I224">
-        <v>-77079822</v>
+        <v>-7.7079822E7</v>
       </c>
       <c r="J224" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K224" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="225" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="225" ht="14.25" customHeight="1">
       <c r="A225" t="s">
         <v>53</v>
       </c>
@@ -10274,19 +10261,19 @@
         <v>599</v>
       </c>
       <c r="H225">
-        <v>-12058599</v>
+        <v>-1.2058599E7</v>
       </c>
       <c r="I225">
-        <v>-77081083</v>
+        <v>-7.7081083E7</v>
       </c>
       <c r="J225" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K225" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="226" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="226" ht="14.25" customHeight="1">
       <c r="A226" t="s">
         <v>25</v>
       </c>
@@ -10309,19 +10296,19 @@
         <v>601</v>
       </c>
       <c r="H226">
-        <v>-12058558</v>
+        <v>-1.2058558E7</v>
       </c>
       <c r="I226">
-        <v>-77079863</v>
+        <v>-7.7079863E7</v>
       </c>
       <c r="J226" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K226" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="227" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="227" ht="14.25" customHeight="1">
       <c r="A227" t="s">
         <v>25</v>
       </c>
@@ -10344,19 +10331,19 @@
         <v>602</v>
       </c>
       <c r="H227">
-        <v>-12058558</v>
+        <v>-1.2058558E7</v>
       </c>
       <c r="I227">
-        <v>-77079863</v>
+        <v>-7.7079863E7</v>
       </c>
       <c r="J227" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K227" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="228" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="228" ht="14.25" customHeight="1">
       <c r="A228" t="s">
         <v>25</v>
       </c>
@@ -10379,19 +10366,19 @@
         <v>604</v>
       </c>
       <c r="H228">
-        <v>-12058396</v>
+        <v>-1.2058396E7</v>
       </c>
       <c r="I228">
-        <v>-77079838</v>
+        <v>-7.7079838E7</v>
       </c>
       <c r="J228" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K228" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="229" ht="14.25" customHeight="1">
       <c r="A229" t="s">
         <v>25</v>
       </c>
@@ -10414,19 +10401,19 @@
         <v>605</v>
       </c>
       <c r="H229">
-        <v>-12058487</v>
+        <v>-1.2058487E7</v>
       </c>
       <c r="I229">
-        <v>-77079881</v>
+        <v>-7.7079881E7</v>
       </c>
       <c r="J229" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K229" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="230" ht="14.25" customHeight="1">
       <c r="A230" t="s">
         <v>11</v>
       </c>
@@ -10449,19 +10436,19 @@
         <v>607</v>
       </c>
       <c r="H230">
-        <v>-12054099</v>
+        <v>-1.2054099E7</v>
       </c>
       <c r="I230">
-        <v>-77085121</v>
+        <v>-7.7085121E7</v>
       </c>
       <c r="J230" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K230" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="231" ht="14.25" customHeight="1">
       <c r="A231" t="s">
         <v>608</v>
       </c>
@@ -10484,19 +10471,19 @@
         <v>610</v>
       </c>
       <c r="H231">
-        <v>-12059066</v>
+        <v>-1.2059066E7</v>
       </c>
       <c r="I231">
-        <v>-77088411</v>
+        <v>-7.7079712E7</v>
       </c>
       <c r="J231" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K231" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="232" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="232" ht="14.25" customHeight="1">
       <c r="A232" t="s">
         <v>25</v>
       </c>
@@ -10519,19 +10506,19 @@
         <v>611</v>
       </c>
       <c r="H232">
-        <v>-12058446</v>
+        <v>-1.2058446E7</v>
       </c>
       <c r="I232">
-        <v>-77079712</v>
+        <v>-7.7079712E7</v>
       </c>
       <c r="J232" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K232" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="233" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="233" ht="14.25" customHeight="1">
       <c r="A233" t="s">
         <v>53</v>
       </c>
@@ -10554,19 +10541,19 @@
         <v>612</v>
       </c>
       <c r="H233">
-        <v>-12058378</v>
+        <v>-1.2058378E7</v>
       </c>
       <c r="I233">
-        <v>-77080139</v>
+        <v>-7.7080139E7</v>
       </c>
       <c r="J233" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K233" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="234" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="234" ht="14.25" customHeight="1">
       <c r="A234" t="s">
         <v>218</v>
       </c>
@@ -10589,19 +10576,19 @@
         <v>615</v>
       </c>
       <c r="H234">
-        <v>-12057683</v>
+        <v>-1.2057683E7</v>
       </c>
       <c r="I234">
-        <v>-77081691</v>
+        <v>-7.7081691E7</v>
       </c>
       <c r="J234" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K234" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="235" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="235" ht="14.25" customHeight="1">
       <c r="A235" t="s">
         <v>616</v>
       </c>
@@ -10624,19 +10611,19 @@
         <v>617</v>
       </c>
       <c r="H235">
-        <v>-1205956104</v>
+        <v>-1.205956104E9</v>
       </c>
       <c r="I235">
-        <v>-7708225469</v>
+        <v>-7.708225469E9</v>
       </c>
       <c r="J235" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K235" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="236" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="236" ht="14.25" customHeight="1">
       <c r="A236" t="s">
         <v>618</v>
       </c>
@@ -10659,19 +10646,19 @@
         <v>620</v>
       </c>
       <c r="H236">
-        <v>-12060321</v>
+        <v>-1.2060321E7</v>
       </c>
       <c r="I236">
-        <v>-77082444</v>
+        <v>-7.7082444E7</v>
       </c>
       <c r="J236" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K236" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="237" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="237" ht="14.25" customHeight="1">
       <c r="A237" t="s">
         <v>621</v>
       </c>
@@ -10694,19 +10681,19 @@
         <v>623</v>
       </c>
       <c r="H237">
-        <v>-12060478</v>
+        <v>-1.2060478E7</v>
       </c>
       <c r="I237">
-        <v>-77081862</v>
+        <v>-7.7081862E7</v>
       </c>
       <c r="J237" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K237" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="238" ht="14.25" customHeight="1">
       <c r="A238" t="s">
         <v>624</v>
       </c>
@@ -10729,19 +10716,19 @@
         <v>626</v>
       </c>
       <c r="H238">
-        <v>-12057692</v>
+        <v>-1.2057692E7</v>
       </c>
       <c r="I238">
-        <v>-77079914</v>
+        <v>-7.7079914E7</v>
       </c>
       <c r="J238" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K238" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="239" ht="14.25" customHeight="1">
       <c r="A239" t="s">
         <v>627</v>
       </c>
@@ -10764,19 +10751,19 @@
         <v>628</v>
       </c>
       <c r="H239">
-        <v>-12055621</v>
+        <v>-1.2055621E7</v>
       </c>
       <c r="I239">
-        <v>-77087168</v>
+        <v>-7.7087168E7</v>
       </c>
       <c r="J239" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K239" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="240" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="240" ht="14.25" customHeight="1">
       <c r="A240" t="s">
         <v>629</v>
       </c>
@@ -10799,19 +10786,19 @@
         <v>631</v>
       </c>
       <c r="H240">
-        <v>-120598789</v>
+        <v>-1.20598789E8</v>
       </c>
       <c r="I240">
-        <v>-770812378</v>
+        <v>-7.70812378E8</v>
       </c>
       <c r="J240" t="s">
         <v>62</v>
       </c>
       <c r="K240" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="241" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="241" ht="14.25" customHeight="1">
       <c r="A241" t="s">
         <v>632</v>
       </c>
@@ -10834,19 +10821,19 @@
         <v>634</v>
       </c>
       <c r="H241">
-        <v>-1205794058</v>
+        <v>-1.205794058E9</v>
       </c>
       <c r="I241">
-        <v>-7708585978</v>
+        <v>-7.708585978E9</v>
       </c>
       <c r="J241" t="s">
         <v>62</v>
       </c>
       <c r="K241" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="242" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="242" ht="14.25" customHeight="1">
       <c r="A242" t="s">
         <v>635</v>
       </c>
@@ -10869,10 +10856,10 @@
         <v>637</v>
       </c>
       <c r="H242">
-        <v>-12054079</v>
+        <v>-1.2054079E7</v>
       </c>
       <c r="I242">
-        <v>-77085772</v>
+        <v>-7.7085772E7</v>
       </c>
       <c r="J242" t="s">
         <v>62</v>
@@ -10881,7 +10868,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="243" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="243" ht="14.25" customHeight="1">
       <c r="A243" t="s">
         <v>638</v>
       </c>
@@ -10904,19 +10891,19 @@
         <v>640</v>
       </c>
       <c r="H243">
-        <v>-1205486</v>
+        <v>-1205486.0</v>
       </c>
       <c r="I243">
-        <v>-7716547</v>
+        <v>-7.7085772E7</v>
       </c>
       <c r="J243" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K243" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="244" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="244" ht="14.25" customHeight="1">
       <c r="A244" t="s">
         <v>641</v>
       </c>
@@ -10939,19 +10926,19 @@
         <v>643</v>
       </c>
       <c r="H244">
-        <v>-1205574</v>
+        <v>-1205574.0</v>
       </c>
       <c r="I244">
-        <v>-7708559</v>
+        <v>-7708559.0</v>
       </c>
       <c r="J244" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K244" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="245" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="245" ht="14.25" customHeight="1">
       <c r="A245" t="s">
         <v>644</v>
       </c>
@@ -10974,19 +10961,19 @@
         <v>648</v>
       </c>
       <c r="H245">
-        <v>-120601022</v>
+        <v>-1.20601022E8</v>
       </c>
       <c r="I245">
-        <v>-770812073</v>
+        <v>-7.70812073E8</v>
       </c>
       <c r="J245" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K245" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="246" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="246" ht="14.25" customHeight="1">
       <c r="A246" t="s">
         <v>25</v>
       </c>
@@ -11009,19 +10996,19 @@
         <v>649</v>
       </c>
       <c r="H246">
-        <v>-12058280</v>
+        <v>-1.205828E7</v>
       </c>
       <c r="I246">
-        <v>-77079939</v>
+        <v>-7.7079939E7</v>
       </c>
       <c r="J246" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K246" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="247" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="247" ht="14.25" customHeight="1">
       <c r="A247" t="s">
         <v>53</v>
       </c>
@@ -11044,19 +11031,19 @@
         <v>650</v>
       </c>
       <c r="H247">
-        <v>-12058308</v>
+        <v>-1.2058308E7</v>
       </c>
       <c r="I247">
-        <v>-77080516</v>
+        <v>-7.7080516E7</v>
       </c>
       <c r="J247" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K247" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="248" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="248" ht="14.25" customHeight="1">
       <c r="A248" t="s">
         <v>651</v>
       </c>
@@ -11079,19 +11066,19 @@
         <v>654</v>
       </c>
       <c r="H248">
-        <v>-120603143</v>
+        <v>-1.20603143E8</v>
       </c>
       <c r="I248">
-        <v>-770814323</v>
+        <v>-7.70814323E8</v>
       </c>
       <c r="J248" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K248" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="249" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="249" ht="14.25" customHeight="1">
       <c r="A249" t="s">
         <v>25</v>
       </c>
@@ -11114,19 +11101,19 @@
         <v>656</v>
       </c>
       <c r="H249">
-        <v>-12058379</v>
+        <v>-1.2058379E7</v>
       </c>
       <c r="I249">
-        <v>-77079694</v>
+        <v>-7.7079694E7</v>
       </c>
       <c r="J249" t="s">
         <v>62</v>
       </c>
       <c r="K249" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="250" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="250" ht="14.25" customHeight="1">
       <c r="A250" t="s">
         <v>25</v>
       </c>
@@ -11149,19 +11136,19 @@
         <v>657</v>
       </c>
       <c r="H250">
-        <v>-12058576</v>
+        <v>-1.2058576E7</v>
       </c>
       <c r="I250">
-        <v>-77079769</v>
+        <v>-7.7079769E7</v>
       </c>
       <c r="J250" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K250" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="251" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="251" ht="14.25" customHeight="1">
       <c r="A251" t="s">
         <v>658</v>
       </c>
@@ -11184,19 +11171,19 @@
         <v>662</v>
       </c>
       <c r="H251">
-        <v>-12054079</v>
+        <v>-1.2054079E7</v>
       </c>
       <c r="I251">
-        <v>-77085772</v>
+        <v>-7.7085772E7</v>
       </c>
       <c r="J251" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K251" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="252" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="252" ht="14.25" customHeight="1">
       <c r="A252" t="s">
         <v>25</v>
       </c>
@@ -11219,19 +11206,19 @@
         <v>664</v>
       </c>
       <c r="H252">
-        <v>-12058225</v>
+        <v>-1.2058225E7</v>
       </c>
       <c r="I252">
-        <v>-77079769</v>
+        <v>-7.7079769E7</v>
       </c>
       <c r="J252" t="s">
         <v>62</v>
       </c>
       <c r="K252" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="253" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="253" ht="14.25" customHeight="1">
       <c r="A253" t="s">
         <v>665</v>
       </c>
@@ -11254,19 +11241,19 @@
         <v>666</v>
       </c>
       <c r="H253">
-        <v>-1205524619</v>
+        <v>-1.205524619E9</v>
       </c>
       <c r="I253">
-        <v>-7708674081</v>
+        <v>-7.708674081E9</v>
       </c>
       <c r="J253" t="s">
         <v>62</v>
       </c>
       <c r="K253" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="254" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="254" ht="14.25" customHeight="1">
       <c r="A254" t="s">
         <v>667</v>
       </c>
@@ -11289,19 +11276,19 @@
         <v>669</v>
       </c>
       <c r="H254">
-        <v>-120597677</v>
+        <v>-1.20597677E8</v>
       </c>
       <c r="I254">
-        <v>-77081146</v>
+        <v>-7.7081146E7</v>
       </c>
       <c r="J254" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K254" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="255" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="255" ht="14.25" customHeight="1">
       <c r="A255" t="s">
         <v>670</v>
       </c>
@@ -11324,19 +11311,19 @@
         <v>669</v>
       </c>
       <c r="H255">
-        <v>-120567</v>
+        <v>-120567.0</v>
       </c>
       <c r="I255">
-        <v>-77085</v>
+        <v>-77085.0</v>
       </c>
       <c r="J255" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K255" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="256" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="256" ht="14.25" customHeight="1">
       <c r="A256" t="s">
         <v>671</v>
       </c>
@@ -11359,19 +11346,19 @@
         <v>673</v>
       </c>
       <c r="H256">
-        <v>-1205983221</v>
+        <v>-1.205983221E9</v>
       </c>
       <c r="I256">
-        <v>-7708107917</v>
+        <v>-7.708107917E9</v>
       </c>
       <c r="J256" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K256" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="257" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="257" ht="14.25" customHeight="1">
       <c r="A257" t="s">
         <v>674</v>
       </c>
@@ -11394,19 +11381,19 @@
         <v>676</v>
       </c>
       <c r="H257">
-        <v>-12053839</v>
+        <v>-1.2053839E7</v>
       </c>
       <c r="I257">
-        <v>-77086625</v>
+        <v>-7.7086625E7</v>
       </c>
       <c r="J257" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K257" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="258" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="258" ht="14.25" customHeight="1">
       <c r="A258" t="s">
         <v>677</v>
       </c>
@@ -11429,19 +11416,22 @@
         <v>678</v>
       </c>
       <c r="H258">
-        <v>-1205647228</v>
+        <v>-1.205647228E9</v>
       </c>
       <c r="I258">
-        <v>-7708648469</v>
+        <v>-7.708648469E9</v>
       </c>
       <c r="J258" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K258" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions/>
+  <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
+  <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/flora.xlsx
+++ b/flora.xlsx
@@ -1,12 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\User\Documents\bioConservaPY\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB522EC4-9503-4EB1-88DD-89CBD49329D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -2053,59 +2062,68 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
-    <font/>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -2261,7 +2279,7 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln cap="flat" cmpd="sng" w="9525" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -2270,13 +2288,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln cap="flat" cmpd="sng" w="25400" algn="ctr">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln cap="flat" cmpd="sng" w="38100" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -2286,7 +2304,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" rotWithShape="0" dir="5400000" dist="20000">
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -2295,7 +2313,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" rotWithShape="0" dir="5400000" dist="23000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -2304,7 +2322,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" rotWithShape="0" dir="5400000" dist="23000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -2314,12 +2332,12 @@
             <a:camera prst="orthographicFront">
               <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
+            <a:lightRig rig="threePt" dir="t">
               <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
-            <a:bevelT h="25400" w="63500"/>
+            <a:bevelT w="63500" h="25400"/>
           </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
@@ -2350,7 +2368,7 @@
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
-            <a:fillToRect b="180000" l="50000" r="50000" t="-80000"/>
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
@@ -2369,7 +2387,7 @@
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
-            <a:fillToRect b="50000" l="50000" r="50000" t="50000"/>
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
@@ -2381,25 +2399,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K258"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="50.71"/>
-    <col customWidth="1" min="2" max="2" width="13.29"/>
-    <col customWidth="1" min="3" max="3" width="13.43"/>
-    <col customWidth="1" min="4" max="4" width="12.71"/>
-    <col customWidth="1" min="5" max="5" width="15.0"/>
-    <col customWidth="1" min="6" max="6" width="18.43"/>
-    <col customWidth="1" min="7" max="7" width="26.71"/>
-    <col customWidth="1" min="8" max="9" width="11.71"/>
-    <col customWidth="1" min="10" max="10" width="7.0"/>
-    <col customWidth="1" min="11" max="11" width="27.0"/>
+    <col min="1" max="1" width="50.6640625" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" customWidth="1"/>
+    <col min="3" max="3" width="13.44140625" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="6" max="6" width="18.44140625" customWidth="1"/>
+    <col min="7" max="7" width="26.6640625" customWidth="1"/>
+    <col min="8" max="9" width="11.6640625" customWidth="1"/>
+    <col min="10" max="10" width="7" customWidth="1"/>
+    <col min="11" max="11" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1">
+    <row r="1" spans="1:11" ht="14.25" customHeight="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2434,7 +2450,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" ht="14.25" customHeight="1">
+    <row r="2" spans="1:11" ht="14.25" customHeight="1">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -2457,10 +2473,10 @@
         <v>17</v>
       </c>
       <c r="H2">
-        <v>-1.2054126E7</v>
+        <v>-12054126</v>
       </c>
       <c r="I2">
-        <v>-7.7084847E7</v>
+        <v>-77084847</v>
       </c>
       <c r="J2" t="s">
         <v>18</v>
@@ -2469,7 +2485,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" ht="14.25" customHeight="1">
+    <row r="3" spans="1:11" ht="14.25" customHeight="1">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -2492,10 +2508,10 @@
         <v>21</v>
       </c>
       <c r="H3">
-        <v>-1.205694058E9</v>
+        <v>-1205694058</v>
       </c>
       <c r="I3">
-        <v>-7.708641878E9</v>
+        <v>-7708641878</v>
       </c>
       <c r="J3" t="s">
         <v>18</v>
@@ -2504,7 +2520,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" ht="14.25" customHeight="1">
+    <row r="4" spans="1:11" ht="14.25" customHeight="1">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -2527,10 +2543,10 @@
         <v>21</v>
       </c>
       <c r="H4">
-        <v>-1.2060857E7</v>
+        <v>-12060857</v>
       </c>
       <c r="I4">
-        <v>-7.7084882E7</v>
+        <v>-77084882</v>
       </c>
       <c r="J4" t="s">
         <v>18</v>
@@ -2539,7 +2555,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" ht="14.25" customHeight="1">
+    <row r="5" spans="1:11" ht="14.25" customHeight="1">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -2562,10 +2578,10 @@
         <v>24</v>
       </c>
       <c r="H5">
-        <v>-1.2059189E7</v>
+        <v>-12059189</v>
       </c>
       <c r="I5">
-        <v>-7.70833987E8</v>
+        <v>-770833987</v>
       </c>
       <c r="J5" t="s">
         <v>18</v>
@@ -2574,7 +2590,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" ht="14.25" customHeight="1">
+    <row r="6" spans="1:11" ht="14.25" customHeight="1">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -2597,10 +2613,10 @@
         <v>30</v>
       </c>
       <c r="H6">
-        <v>-1.2058464E7</v>
+        <v>-12058464</v>
       </c>
       <c r="I6">
-        <v>-7.7079628E7</v>
+        <v>-77079628</v>
       </c>
       <c r="J6" t="s">
         <v>18</v>
@@ -2609,7 +2625,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" ht="14.25" customHeight="1">
+    <row r="7" spans="1:11" ht="14.25" customHeight="1">
       <c r="A7" t="s">
         <v>32</v>
       </c>
@@ -2632,10 +2648,10 @@
         <v>34</v>
       </c>
       <c r="H7">
-        <v>-1.2059339E7</v>
+        <v>-12059339</v>
       </c>
       <c r="I7">
-        <v>-7.7087202E7</v>
+        <v>-77087202</v>
       </c>
       <c r="J7" t="s">
         <v>18</v>
@@ -2644,7 +2660,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" ht="14.25" customHeight="1">
+    <row r="8" spans="1:11" ht="14.25" customHeight="1">
       <c r="A8" t="s">
         <v>35</v>
       </c>
@@ -2667,10 +2683,10 @@
         <v>36</v>
       </c>
       <c r="H8">
-        <v>-1.205614319E9</v>
+        <v>-1205614319</v>
       </c>
       <c r="I8">
-        <v>-7.708652797E9</v>
+        <v>-7708652797</v>
       </c>
       <c r="J8" t="s">
         <v>18</v>
@@ -2679,7 +2695,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" ht="14.25" customHeight="1">
+    <row r="9" spans="1:11" ht="14.25" customHeight="1">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -2702,10 +2718,10 @@
         <v>37</v>
       </c>
       <c r="H9">
-        <v>-1.2057781E7</v>
+        <v>-12057781</v>
       </c>
       <c r="I9">
-        <v>-7.7080035E7</v>
+        <v>-77080035</v>
       </c>
       <c r="J9" t="s">
         <v>18</v>
@@ -2714,7 +2730,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" ht="14.25" customHeight="1">
+    <row r="10" spans="1:11" ht="14.25" customHeight="1">
       <c r="A10" t="s">
         <v>38</v>
       </c>
@@ -2737,10 +2753,10 @@
         <v>39</v>
       </c>
       <c r="H10">
-        <v>-1.2058044E7</v>
+        <v>-12058044</v>
       </c>
       <c r="I10">
-        <v>-7708053.0</v>
+        <v>-7708053</v>
       </c>
       <c r="J10" t="s">
         <v>18</v>
@@ -2749,7 +2765,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" ht="14.25" customHeight="1">
+    <row r="11" spans="1:11" ht="14.25" customHeight="1">
       <c r="A11" t="s">
         <v>40</v>
       </c>
@@ -2772,10 +2788,10 @@
         <v>44</v>
       </c>
       <c r="H11">
-        <v>-1.205744928E9</v>
+        <v>-1205744928</v>
       </c>
       <c r="I11">
-        <v>-7.708568678E9</v>
+        <v>-7708568678</v>
       </c>
       <c r="J11" t="s">
         <v>18</v>
@@ -2784,7 +2800,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" ht="14.25" customHeight="1">
+    <row r="12" spans="1:11" ht="14.25" customHeight="1">
       <c r="A12" t="s">
         <v>45</v>
       </c>
@@ -2807,10 +2823,10 @@
         <v>48</v>
       </c>
       <c r="H12">
-        <v>-1.2059866E7</v>
+        <v>-12059866</v>
       </c>
       <c r="I12">
-        <v>-7.7081176E7</v>
+        <v>-77081176</v>
       </c>
       <c r="J12" t="s">
         <v>18</v>
@@ -2819,7 +2835,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" ht="14.25" customHeight="1">
+    <row r="13" spans="1:11" ht="14.25" customHeight="1">
       <c r="A13" t="s">
         <v>49</v>
       </c>
@@ -2842,10 +2858,10 @@
         <v>50</v>
       </c>
       <c r="H13">
-        <v>-1.205744058E9</v>
+        <v>-1205744058</v>
       </c>
       <c r="I13">
-        <v>-7.708600328E9</v>
+        <v>-7708600328</v>
       </c>
       <c r="J13" t="s">
         <v>18</v>
@@ -2854,7 +2870,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" ht="14.25" customHeight="1">
+    <row r="14" spans="1:11" ht="14.25" customHeight="1">
       <c r="A14" t="s">
         <v>51</v>
       </c>
@@ -2877,10 +2893,10 @@
         <v>52</v>
       </c>
       <c r="H14">
-        <v>-1.20543636E8</v>
+        <v>-120543636</v>
       </c>
       <c r="I14">
-        <v>-7.70844448E8</v>
+        <v>-770844448</v>
       </c>
       <c r="J14" t="s">
         <v>18</v>
@@ -2889,7 +2905,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" ht="14.25" customHeight="1">
+    <row r="15" spans="1:11" ht="14.25" customHeight="1">
       <c r="A15" t="s">
         <v>53</v>
       </c>
@@ -2912,10 +2928,10 @@
         <v>54</v>
       </c>
       <c r="H15">
-        <v>-1.2058254E7</v>
+        <v>-12058254</v>
       </c>
       <c r="I15">
-        <v>-7.7080432E7</v>
+        <v>-77080432</v>
       </c>
       <c r="J15" t="s">
         <v>18</v>
@@ -2924,7 +2940,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" ht="14.25" customHeight="1">
+    <row r="16" spans="1:11" ht="14.25" customHeight="1">
       <c r="A16" t="s">
         <v>55</v>
       </c>
@@ -2947,10 +2963,10 @@
         <v>56</v>
       </c>
       <c r="H16">
-        <v>-1.2060189E7</v>
+        <v>-12060189</v>
       </c>
       <c r="I16">
-        <v>-7.7080977E7</v>
+        <v>-77080977</v>
       </c>
       <c r="J16" t="s">
         <v>18</v>
@@ -2959,7 +2975,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" ht="14.25" customHeight="1">
+    <row r="17" spans="1:11" ht="14.25" customHeight="1">
       <c r="A17" t="s">
         <v>57</v>
       </c>
@@ -2982,10 +2998,10 @@
         <v>61</v>
       </c>
       <c r="H17">
-        <v>-1.205956993E9</v>
+        <v>-1205956993</v>
       </c>
       <c r="I17">
-        <v>-7.708088735E9</v>
+        <v>-7708088735</v>
       </c>
       <c r="J17" t="s">
         <v>62</v>
@@ -2994,7 +3010,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" ht="14.25" customHeight="1">
+    <row r="18" spans="1:11" ht="14.25" customHeight="1">
       <c r="A18" t="s">
         <v>53</v>
       </c>
@@ -3017,10 +3033,10 @@
         <v>66</v>
       </c>
       <c r="H18">
-        <v>-1.2058444E7</v>
+        <v>-12058444</v>
       </c>
       <c r="I18">
-        <v>-7.7080372E7</v>
+        <v>-77080372</v>
       </c>
       <c r="J18" t="s">
         <v>18</v>
@@ -3029,7 +3045,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" ht="14.25" customHeight="1">
+    <row r="19" spans="1:11" ht="14.25" customHeight="1">
       <c r="A19" t="s">
         <v>67</v>
       </c>
@@ -3052,10 +3068,10 @@
         <v>71</v>
       </c>
       <c r="H19">
-        <v>-1.2054729E7</v>
+        <v>-12054729</v>
       </c>
       <c r="I19">
-        <v>-7.7085504E7</v>
+        <v>-77085504</v>
       </c>
       <c r="J19" t="s">
         <v>62</v>
@@ -3064,7 +3080,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" ht="14.25" customHeight="1">
+    <row r="20" spans="1:11" ht="14.25" customHeight="1">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -3087,10 +3103,10 @@
         <v>72</v>
       </c>
       <c r="H20">
-        <v>-1.2058446E7</v>
+        <v>-12058446</v>
       </c>
       <c r="I20">
-        <v>-7.7079712E7</v>
+        <v>-77079712</v>
       </c>
       <c r="J20" t="s">
         <v>62</v>
@@ -3099,7 +3115,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" ht="14.25" customHeight="1">
+    <row r="21" spans="1:11" ht="14.25" customHeight="1">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -3122,10 +3138,10 @@
         <v>74</v>
       </c>
       <c r="H21">
-        <v>-1.2057977E7</v>
+        <v>-12057977</v>
       </c>
       <c r="I21">
-        <v>-7.7079822E7</v>
+        <v>-77079822</v>
       </c>
       <c r="J21" t="s">
         <v>18</v>
@@ -3134,7 +3150,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" ht="14.25" customHeight="1">
+    <row r="22" spans="1:11" ht="14.25" customHeight="1">
       <c r="A22" t="s">
         <v>75</v>
       </c>
@@ -3157,10 +3173,10 @@
         <v>77</v>
       </c>
       <c r="H22">
-        <v>-1.20601022E8</v>
+        <v>-120601022</v>
       </c>
       <c r="I22">
-        <v>-7.70812073E8</v>
+        <v>-770812073</v>
       </c>
       <c r="J22" t="s">
         <v>18</v>
@@ -3169,7 +3185,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="23" ht="14.25" customHeight="1">
+    <row r="23" spans="1:11" ht="14.25" customHeight="1">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -3192,10 +3208,10 @@
         <v>78</v>
       </c>
       <c r="H23">
-        <v>-1.2058392E7</v>
+        <v>-12058392</v>
       </c>
       <c r="I23">
-        <v>-7.7080974E7</v>
+        <v>-77080974</v>
       </c>
       <c r="J23" t="s">
         <v>18</v>
@@ -3204,7 +3220,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" ht="14.25" customHeight="1">
+    <row r="24" spans="1:11" ht="14.25" customHeight="1">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -3227,10 +3243,10 @@
         <v>81</v>
       </c>
       <c r="H24">
-        <v>-1.2058012E7</v>
+        <v>-12058012</v>
       </c>
       <c r="I24">
-        <v>-7.7079983E7</v>
+        <v>-77079983</v>
       </c>
       <c r="J24" t="s">
         <v>18</v>
@@ -3239,7 +3255,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="25" ht="14.25" customHeight="1">
+    <row r="25" spans="1:11" ht="14.25" customHeight="1">
       <c r="A25" t="s">
         <v>82</v>
       </c>
@@ -3262,10 +3278,10 @@
         <v>86</v>
       </c>
       <c r="H25">
-        <v>-1.2059339E7</v>
+        <v>-12059339</v>
       </c>
       <c r="I25">
-        <v>-7.7087202E7</v>
+        <v>-77087202</v>
       </c>
       <c r="J25" t="s">
         <v>62</v>
@@ -3274,7 +3290,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="26" ht="14.25" customHeight="1">
+    <row r="26" spans="1:11" ht="14.25" customHeight="1">
       <c r="A26" t="s">
         <v>87</v>
       </c>
@@ -3297,10 +3313,10 @@
         <v>88</v>
       </c>
       <c r="H26">
-        <v>-1.2054079E7</v>
+        <v>-12054079</v>
       </c>
       <c r="I26">
-        <v>-7.7085772E7</v>
+        <v>-77085772</v>
       </c>
       <c r="J26" t="s">
         <v>62</v>
@@ -3309,7 +3325,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" ht="14.25" customHeight="1">
+    <row r="27" spans="1:11" ht="14.25" customHeight="1">
       <c r="A27" t="s">
         <v>89</v>
       </c>
@@ -3332,10 +3348,10 @@
         <v>90</v>
       </c>
       <c r="H27">
-        <v>-1.2060689E7</v>
+        <v>-12060689</v>
       </c>
       <c r="I27">
-        <v>-7.7082967E7</v>
+        <v>-77082967</v>
       </c>
       <c r="J27" t="s">
         <v>62</v>
@@ -3344,7 +3360,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" ht="14.25" customHeight="1">
+    <row r="28" spans="1:11" ht="14.25" customHeight="1">
       <c r="A28" t="s">
         <v>91</v>
       </c>
@@ -3367,10 +3383,10 @@
         <v>92</v>
       </c>
       <c r="H28">
-        <v>-1.2060636E7</v>
+        <v>-12060636</v>
       </c>
       <c r="I28">
-        <v>-7.7082914E7</v>
+        <v>-77082914</v>
       </c>
       <c r="J28" t="s">
         <v>62</v>
@@ -3379,7 +3395,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" ht="14.25" customHeight="1">
+    <row r="29" spans="1:11" ht="14.25" customHeight="1">
       <c r="A29" t="s">
         <v>93</v>
       </c>
@@ -3402,10 +3418,10 @@
         <v>99</v>
       </c>
       <c r="H29">
-        <v>-1.205938467E9</v>
+        <v>-1205938467</v>
       </c>
       <c r="I29">
-        <v>-7.708157858E9</v>
+        <v>-7708157858</v>
       </c>
       <c r="J29" t="s">
         <v>18</v>
@@ -3414,7 +3430,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="30" ht="14.25" customHeight="1">
+    <row r="30" spans="1:11" ht="14.25" customHeight="1">
       <c r="A30" t="s">
         <v>100</v>
       </c>
@@ -3437,10 +3453,10 @@
         <v>104</v>
       </c>
       <c r="H30">
-        <v>-1.20603064E8</v>
+        <v>-120603064</v>
       </c>
       <c r="I30">
-        <v>-7.70811865E8</v>
+        <v>-770811865</v>
       </c>
       <c r="J30" t="s">
         <v>18</v>
@@ -3449,7 +3465,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="31" ht="14.25" customHeight="1">
+    <row r="31" spans="1:11" ht="14.25" customHeight="1">
       <c r="A31" t="s">
         <v>105</v>
       </c>
@@ -3472,10 +3488,10 @@
         <v>107</v>
       </c>
       <c r="H31">
-        <v>-1.2060747E7</v>
+        <v>-12060747</v>
       </c>
       <c r="I31">
-        <v>-7708427.0</v>
+        <v>-7708427</v>
       </c>
       <c r="J31" t="s">
         <v>18</v>
@@ -3484,7 +3500,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="32" ht="14.25" customHeight="1">
+    <row r="32" spans="1:11" ht="14.25" customHeight="1">
       <c r="A32" t="s">
         <v>108</v>
       </c>
@@ -3507,10 +3523,10 @@
         <v>112</v>
       </c>
       <c r="H32">
-        <v>-1.2054079E7</v>
+        <v>-12054079</v>
       </c>
       <c r="I32">
-        <v>-7.7085772E7</v>
+        <v>-77085772</v>
       </c>
       <c r="J32" t="s">
         <v>18</v>
@@ -3519,7 +3535,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="33" ht="14.25" customHeight="1">
+    <row r="33" spans="1:11" ht="14.25" customHeight="1">
       <c r="A33" t="s">
         <v>113</v>
       </c>
@@ -3542,10 +3558,10 @@
         <v>115</v>
       </c>
       <c r="H33">
-        <v>-1.2055022E7</v>
+        <v>-12055022</v>
       </c>
       <c r="I33">
-        <v>-7.7085872E7</v>
+        <v>-77085872</v>
       </c>
       <c r="J33" t="s">
         <v>18</v>
@@ -3554,7 +3570,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="34" ht="14.25" customHeight="1">
+    <row r="34" spans="1:11" ht="14.25" customHeight="1">
       <c r="A34" t="s">
         <v>116</v>
       </c>
@@ -3577,10 +3593,10 @@
         <v>118</v>
       </c>
       <c r="H34">
-        <v>-1.206006375E9</v>
+        <v>-1206006375</v>
       </c>
       <c r="I34">
-        <v>-7.708105692E9</v>
+        <v>-7708105692</v>
       </c>
       <c r="J34" t="s">
         <v>18</v>
@@ -3589,7 +3605,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="35" ht="14.25" customHeight="1">
+    <row r="35" spans="1:11" ht="14.25" customHeight="1">
       <c r="A35" t="s">
         <v>119</v>
       </c>
@@ -3612,10 +3628,10 @@
         <v>121</v>
       </c>
       <c r="H35">
-        <v>-1205555.0</v>
+        <v>-1205555</v>
       </c>
       <c r="I35">
-        <v>-7.7082396E7</v>
+        <v>-77082396</v>
       </c>
       <c r="J35" t="s">
         <v>18</v>
@@ -3624,7 +3640,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="36" ht="14.25" customHeight="1">
+    <row r="36" spans="1:11" ht="14.25" customHeight="1">
       <c r="A36" t="s">
         <v>122</v>
       </c>
@@ -3647,10 +3663,10 @@
         <v>121</v>
       </c>
       <c r="H36">
-        <v>-1.2054731E7</v>
+        <v>-12054731</v>
       </c>
       <c r="I36">
-        <v>-7.7085502E7</v>
+        <v>-77085502</v>
       </c>
       <c r="J36" t="s">
         <v>18</v>
@@ -3659,7 +3675,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="37" ht="14.25" customHeight="1">
+    <row r="37" spans="1:11" ht="14.25" customHeight="1">
       <c r="A37" t="s">
         <v>25</v>
       </c>
@@ -3682,10 +3698,10 @@
         <v>125</v>
       </c>
       <c r="H37">
-        <v>-1.2058223E7</v>
+        <v>-12058223</v>
       </c>
       <c r="I37">
-        <v>-7.7079791E7</v>
+        <v>-77079791</v>
       </c>
       <c r="J37" t="s">
         <v>62</v>
@@ -3694,7 +3710,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="38" ht="14.25" customHeight="1">
+    <row r="38" spans="1:11" ht="14.25" customHeight="1">
       <c r="A38" t="s">
         <v>126</v>
       </c>
@@ -3717,10 +3733,10 @@
         <v>128</v>
       </c>
       <c r="H38">
-        <v>-1.20596026E8</v>
+        <v>-120596026</v>
       </c>
       <c r="I38">
-        <v>-7.708200161E9</v>
+        <v>-7708200161</v>
       </c>
       <c r="J38" t="s">
         <v>62</v>
@@ -3729,7 +3745,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="39" ht="14.25" customHeight="1">
+    <row r="39" spans="1:11" ht="14.25" customHeight="1">
       <c r="A39" t="s">
         <v>129</v>
       </c>
@@ -3752,10 +3768,10 @@
         <v>130</v>
       </c>
       <c r="H39">
-        <v>-1.2055507E7</v>
+        <v>-12055507</v>
       </c>
       <c r="I39">
-        <v>-7.7086982E7</v>
+        <v>-77086982</v>
       </c>
       <c r="J39" t="s">
         <v>62</v>
@@ -3764,7 +3780,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="40" ht="14.25" customHeight="1">
+    <row r="40" spans="1:11" ht="14.25" customHeight="1">
       <c r="A40" t="s">
         <v>131</v>
       </c>
@@ -3787,10 +3803,10 @@
         <v>132</v>
       </c>
       <c r="H40">
-        <v>-1.2059339E7</v>
+        <v>-12059339</v>
       </c>
       <c r="I40">
-        <v>-7.7087202E7</v>
+        <v>-77087202</v>
       </c>
       <c r="J40" t="s">
         <v>62</v>
@@ -3799,7 +3815,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="41" ht="14.25" customHeight="1">
+    <row r="41" spans="1:11" ht="14.25" customHeight="1">
       <c r="A41" t="s">
         <v>25</v>
       </c>
@@ -3822,10 +3838,10 @@
         <v>136</v>
       </c>
       <c r="H41">
-        <v>-1.2058293E7</v>
+        <v>-12058293</v>
       </c>
       <c r="I41">
-        <v>-7.7079951E7</v>
+        <v>-77079951</v>
       </c>
       <c r="J41" t="s">
         <v>18</v>
@@ -3834,7 +3850,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="42" ht="14.25" customHeight="1">
+    <row r="42" spans="1:11" ht="14.25" customHeight="1">
       <c r="A42" t="s">
         <v>137</v>
       </c>
@@ -3857,10 +3873,10 @@
         <v>141</v>
       </c>
       <c r="H42">
-        <v>-1.2056378E7</v>
+        <v>-12056378</v>
       </c>
       <c r="I42">
-        <v>-7.7082083E7</v>
+        <v>-77082083</v>
       </c>
       <c r="J42" t="s">
         <v>62</v>
@@ -3869,7 +3885,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="43" ht="14.25" customHeight="1">
+    <row r="43" spans="1:11" ht="14.25" customHeight="1">
       <c r="A43" t="s">
         <v>143</v>
       </c>
@@ -3892,10 +3908,10 @@
         <v>144</v>
       </c>
       <c r="H43">
-        <v>-1.2056669E7</v>
+        <v>-12056669</v>
       </c>
       <c r="I43">
-        <v>-7.7085002E7</v>
+        <v>-77085002</v>
       </c>
       <c r="J43" t="s">
         <v>62</v>
@@ -3904,7 +3920,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="44" ht="14.25" customHeight="1">
+    <row r="44" spans="1:11" ht="14.25" customHeight="1">
       <c r="A44" t="s">
         <v>23</v>
       </c>
@@ -3927,10 +3943,10 @@
         <v>145</v>
       </c>
       <c r="H44">
-        <v>-1.20582519E8</v>
+        <v>-120582519</v>
       </c>
       <c r="I44">
-        <v>-7.70854067E8</v>
+        <v>-770854067</v>
       </c>
       <c r="J44" t="s">
         <v>62</v>
@@ -3939,7 +3955,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="45" ht="14.25" customHeight="1">
+    <row r="45" spans="1:11" ht="14.25" customHeight="1">
       <c r="A45" t="s">
         <v>146</v>
       </c>
@@ -3962,10 +3978,10 @@
         <v>150</v>
       </c>
       <c r="H45">
-        <v>-1.2059339E7</v>
+        <v>-12059339</v>
       </c>
       <c r="I45">
-        <v>-7.7087202E7</v>
+        <v>-77087202</v>
       </c>
       <c r="J45" t="s">
         <v>62</v>
@@ -3974,7 +3990,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="46" ht="14.25" customHeight="1">
+    <row r="46" spans="1:11" ht="14.25" customHeight="1">
       <c r="A46" t="s">
         <v>151</v>
       </c>
@@ -3997,10 +4013,10 @@
         <v>155</v>
       </c>
       <c r="H46">
-        <v>-1.2053123E7</v>
+        <v>-12053123</v>
       </c>
       <c r="I46">
-        <v>-7.7087656E7</v>
+        <v>-77087656</v>
       </c>
       <c r="J46" t="s">
         <v>62</v>
@@ -4009,7 +4025,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="47" ht="14.25" customHeight="1">
+    <row r="47" spans="1:11" ht="14.25" customHeight="1">
       <c r="A47" t="s">
         <v>137</v>
       </c>
@@ -4032,10 +4048,10 @@
         <v>158</v>
       </c>
       <c r="H47">
-        <v>-1.2056669E7</v>
+        <v>-12056669</v>
       </c>
       <c r="I47">
-        <v>-7.7082056E7</v>
+        <v>-77082056</v>
       </c>
       <c r="J47" t="s">
         <v>62</v>
@@ -4044,7 +4060,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="48" ht="14.25" customHeight="1">
+    <row r="48" spans="1:11" ht="14.25" customHeight="1">
       <c r="A48" t="s">
         <v>25</v>
       </c>
@@ -4067,10 +4083,10 @@
         <v>162</v>
       </c>
       <c r="H48">
-        <v>-1.2058495E7</v>
+        <v>-12058495</v>
       </c>
       <c r="I48">
-        <v>-7.7079711E7</v>
+        <v>-77079711</v>
       </c>
       <c r="J48" t="s">
         <v>18</v>
@@ -4079,7 +4095,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="49" ht="14.25" customHeight="1">
+    <row r="49" spans="1:11" ht="14.25" customHeight="1">
       <c r="A49" t="s">
         <v>163</v>
       </c>
@@ -4102,10 +4118,10 @@
         <v>162</v>
       </c>
       <c r="H49">
-        <v>-1.2058495E7</v>
+        <v>-12058495</v>
       </c>
       <c r="I49">
-        <v>-7.7079711E7</v>
+        <v>-77079711</v>
       </c>
       <c r="J49" t="s">
         <v>18</v>
@@ -4114,7 +4130,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="50" ht="14.25" customHeight="1">
+    <row r="50" spans="1:11" ht="14.25" customHeight="1">
       <c r="A50" t="s">
         <v>164</v>
       </c>
@@ -4137,10 +4153,10 @@
         <v>168</v>
       </c>
       <c r="H50">
-        <v>-1.2059164E7</v>
+        <v>-12059164</v>
       </c>
       <c r="I50">
-        <v>-7.7082569E7</v>
+        <v>-77082569</v>
       </c>
       <c r="J50" t="s">
         <v>62</v>
@@ -4149,7 +4165,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="51" ht="14.25" customHeight="1">
+    <row r="51" spans="1:11" ht="14.25" customHeight="1">
       <c r="A51" t="s">
         <v>169</v>
       </c>
@@ -4172,10 +4188,10 @@
         <v>173</v>
       </c>
       <c r="H51">
-        <v>-1.2054729E7</v>
+        <v>-12054729</v>
       </c>
       <c r="I51">
-        <v>-7.7085504E7</v>
+        <v>-77085504</v>
       </c>
       <c r="J51" t="s">
         <v>18</v>
@@ -4184,7 +4200,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="52" ht="14.25" customHeight="1">
+    <row r="52" spans="1:11" ht="14.25" customHeight="1">
       <c r="A52" t="s">
         <v>25</v>
       </c>
@@ -4207,10 +4223,10 @@
         <v>175</v>
       </c>
       <c r="H52">
-        <v>-1.2058372E7</v>
+        <v>-12058372</v>
       </c>
       <c r="I52">
-        <v>-7.7079835E7</v>
+        <v>-77079835</v>
       </c>
       <c r="J52" t="s">
         <v>62</v>
@@ -4219,7 +4235,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="53" ht="14.25" customHeight="1">
+    <row r="53" spans="1:11" ht="14.25" customHeight="1">
       <c r="A53" t="s">
         <v>163</v>
       </c>
@@ -4242,10 +4258,10 @@
         <v>175</v>
       </c>
       <c r="H53">
-        <v>-1.2058372E7</v>
+        <v>-12058372</v>
       </c>
       <c r="I53">
-        <v>-7.7079835E7</v>
+        <v>-77079835</v>
       </c>
       <c r="J53" t="s">
         <v>62</v>
@@ -4254,7 +4270,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="54" ht="14.25" customHeight="1">
+    <row r="54" spans="1:11" ht="14.25" customHeight="1">
       <c r="A54" t="s">
         <v>176</v>
       </c>
@@ -4277,10 +4293,10 @@
         <v>178</v>
       </c>
       <c r="H54">
-        <v>-1.2059876E7</v>
+        <v>-12059876</v>
       </c>
       <c r="I54">
-        <v>-7.7080387E7</v>
+        <v>-77080387</v>
       </c>
       <c r="J54" t="s">
         <v>18</v>
@@ -4289,7 +4305,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="55" ht="14.25" customHeight="1">
+    <row r="55" spans="1:11" ht="14.25" customHeight="1">
       <c r="A55" t="s">
         <v>179</v>
       </c>
@@ -4312,10 +4328,10 @@
         <v>181</v>
       </c>
       <c r="H55">
-        <v>-1.2059676E7</v>
+        <v>-12059676</v>
       </c>
       <c r="I55">
-        <v>-7.7079776E7</v>
+        <v>-77079776</v>
       </c>
       <c r="J55" t="s">
         <v>18</v>
@@ -4324,7 +4340,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="56" ht="14.25" customHeight="1">
+    <row r="56" spans="1:11" ht="14.25" customHeight="1">
       <c r="A56" t="s">
         <v>38</v>
       </c>
@@ -4347,10 +4363,10 @@
         <v>184</v>
       </c>
       <c r="H56">
-        <v>-1.2058044E7</v>
+        <v>-12058044</v>
       </c>
       <c r="I56">
-        <v>-7.708196112E9</v>
+        <v>-7708196112</v>
       </c>
       <c r="J56" t="s">
         <v>62</v>
@@ -4359,7 +4375,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="57" ht="14.25" customHeight="1">
+    <row r="57" spans="1:11" ht="14.25" customHeight="1">
       <c r="A57" t="s">
         <v>53</v>
       </c>
@@ -4382,10 +4398,10 @@
         <v>186</v>
       </c>
       <c r="H57">
-        <v>-1.2058455E7</v>
+        <v>-12058455</v>
       </c>
       <c r="I57">
-        <v>-7.7080218E7</v>
+        <v>-77080218</v>
       </c>
       <c r="J57" t="s">
         <v>18</v>
@@ -4394,7 +4410,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="58" ht="14.25" customHeight="1">
+    <row r="58" spans="1:11" ht="14.25" customHeight="1">
       <c r="A58" t="s">
         <v>187</v>
       </c>
@@ -4417,10 +4433,10 @@
         <v>191</v>
       </c>
       <c r="H58">
-        <v>-1.205636519E9</v>
+        <v>-1205636519</v>
       </c>
       <c r="I58">
-        <v>-7.708688828E9</v>
+        <v>-7708688828</v>
       </c>
       <c r="J58" t="s">
         <v>18</v>
@@ -4429,7 +4445,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="59" ht="14.25" customHeight="1">
+    <row r="59" spans="1:11" ht="14.25" customHeight="1">
       <c r="A59" t="s">
         <v>53</v>
       </c>
@@ -4452,10 +4468,10 @@
         <v>195</v>
       </c>
       <c r="H59">
-        <v>-1.2058392E7</v>
+        <v>-12058392</v>
       </c>
       <c r="I59">
-        <v>-7.7080974E7</v>
+        <v>-77080974</v>
       </c>
       <c r="J59" t="s">
         <v>18</v>
@@ -4464,7 +4480,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="60" ht="14.25" customHeight="1">
+    <row r="60" spans="1:11" ht="14.25" customHeight="1">
       <c r="A60" t="s">
         <v>196</v>
       </c>
@@ -4487,10 +4503,10 @@
         <v>199</v>
       </c>
       <c r="H60">
-        <v>-1.205982207E9</v>
+        <v>-1205982207</v>
       </c>
       <c r="I60">
-        <v>-7.708130564E9</v>
+        <v>-7708130564</v>
       </c>
       <c r="J60" t="s">
         <v>18</v>
@@ -4499,7 +4515,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="61" ht="14.25" customHeight="1">
+    <row r="61" spans="1:11" ht="14.25" customHeight="1">
       <c r="A61" t="s">
         <v>200</v>
       </c>
@@ -4522,10 +4538,10 @@
         <v>201</v>
       </c>
       <c r="H61">
-        <v>-1.2059339E7</v>
+        <v>-12059339</v>
       </c>
       <c r="I61">
-        <v>-7.7087202E7</v>
+        <v>-77087202</v>
       </c>
       <c r="J61" t="s">
         <v>18</v>
@@ -4534,7 +4550,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="62" ht="14.25" customHeight="1">
+    <row r="62" spans="1:11" ht="14.25" customHeight="1">
       <c r="A62" t="s">
         <v>53</v>
       </c>
@@ -4557,10 +4573,10 @@
         <v>202</v>
       </c>
       <c r="H62">
-        <v>-1.2058258E7</v>
+        <v>-12058258</v>
       </c>
       <c r="I62">
-        <v>-7.7080569E7</v>
+        <v>-77080569</v>
       </c>
       <c r="J62" t="s">
         <v>18</v>
@@ -4569,7 +4585,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="63" ht="14.25" customHeight="1">
+    <row r="63" spans="1:11" ht="14.25" customHeight="1">
       <c r="A63" t="s">
         <v>25</v>
       </c>
@@ -4592,10 +4608,10 @@
         <v>204</v>
       </c>
       <c r="H63">
-        <v>-1.2058487E7</v>
+        <v>-12058487</v>
       </c>
       <c r="I63">
-        <v>-7.7079881E7</v>
+        <v>-77079881</v>
       </c>
       <c r="J63" t="s">
         <v>18</v>
@@ -4604,7 +4620,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="64" ht="14.25" customHeight="1">
+    <row r="64" spans="1:11" ht="14.25" customHeight="1">
       <c r="A64" t="s">
         <v>163</v>
       </c>
@@ -4627,10 +4643,10 @@
         <v>204</v>
       </c>
       <c r="H64">
-        <v>-1.2058487E7</v>
+        <v>-12058487</v>
       </c>
       <c r="I64">
-        <v>-7.7079881E7</v>
+        <v>-77079881</v>
       </c>
       <c r="J64" t="s">
         <v>18</v>
@@ -4639,7 +4655,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="65" ht="14.25" customHeight="1">
+    <row r="65" spans="1:11" ht="14.25" customHeight="1">
       <c r="A65" t="s">
         <v>25</v>
       </c>
@@ -4662,10 +4678,10 @@
         <v>206</v>
       </c>
       <c r="H65">
-        <v>-1.2058078E7</v>
+        <v>-12058078</v>
       </c>
       <c r="I65">
-        <v>-7.7079772E7</v>
+        <v>-77079772</v>
       </c>
       <c r="J65" t="s">
         <v>18</v>
@@ -4674,7 +4690,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="66" ht="14.25" customHeight="1">
+    <row r="66" spans="1:11" ht="14.25" customHeight="1">
       <c r="A66" t="s">
         <v>137</v>
       </c>
@@ -4697,10 +4713,10 @@
         <v>208</v>
       </c>
       <c r="H66">
-        <v>-1.2056444E7</v>
+        <v>-12056444</v>
       </c>
       <c r="I66">
-        <v>-7.7081023E7</v>
+        <v>-77081023</v>
       </c>
       <c r="J66" t="s">
         <v>18</v>
@@ -4709,7 +4725,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="67" ht="14.25" customHeight="1">
+    <row r="67" spans="1:11" ht="14.25" customHeight="1">
       <c r="A67" t="s">
         <v>209</v>
       </c>
@@ -4732,10 +4748,10 @@
         <v>213</v>
       </c>
       <c r="H67">
-        <v>-1.2060774E7</v>
+        <v>-12060774</v>
       </c>
       <c r="I67">
-        <v>-7.7084292E7</v>
+        <v>-77084292</v>
       </c>
       <c r="J67" t="s">
         <v>18</v>
@@ -4744,7 +4760,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="68" ht="14.25" customHeight="1">
+    <row r="68" spans="1:11" ht="14.25" customHeight="1">
       <c r="A68" t="s">
         <v>214</v>
       </c>
@@ -4767,10 +4783,10 @@
         <v>217</v>
       </c>
       <c r="H68">
-        <v>-1.205973372E9</v>
+        <v>-1205973372</v>
       </c>
       <c r="I68">
-        <v>-7.708081745E9</v>
+        <v>-7708081745</v>
       </c>
       <c r="J68" t="s">
         <v>18</v>
@@ -4779,7 +4795,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="69" ht="14.25" customHeight="1">
+    <row r="69" spans="1:11" ht="14.25" customHeight="1">
       <c r="A69" t="s">
         <v>218</v>
       </c>
@@ -4802,10 +4818,10 @@
         <v>220</v>
       </c>
       <c r="H69">
-        <v>-120577.0</v>
+        <v>-120577</v>
       </c>
       <c r="I69">
-        <v>-7.70816994E8</v>
+        <v>-770816994</v>
       </c>
       <c r="J69" t="s">
         <v>18</v>
@@ -4814,7 +4830,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="70" ht="14.25" customHeight="1">
+    <row r="70" spans="1:11" ht="14.25" customHeight="1">
       <c r="A70" t="s">
         <v>221</v>
       </c>
@@ -4837,10 +4853,10 @@
         <v>227</v>
       </c>
       <c r="H70">
-        <v>-1.20551446E8</v>
+        <v>-120551446</v>
       </c>
       <c r="I70">
-        <v>-7.7082736E7</v>
+        <v>-77082736</v>
       </c>
       <c r="J70" t="s">
         <v>18</v>
@@ -4849,7 +4865,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="71" ht="14.25" customHeight="1">
+    <row r="71" spans="1:11" ht="14.25" customHeight="1">
       <c r="A71" t="s">
         <v>23</v>
       </c>
@@ -4872,10 +4888,10 @@
         <v>230</v>
       </c>
       <c r="H71">
-        <v>-1.20551446E8</v>
+        <v>-120551446</v>
       </c>
       <c r="I71">
-        <v>-7708471.0</v>
+        <v>-7708471</v>
       </c>
       <c r="J71" t="s">
         <v>18</v>
@@ -4884,7 +4900,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="72" ht="14.25" customHeight="1">
+    <row r="72" spans="1:11" ht="14.25" customHeight="1">
       <c r="A72" t="s">
         <v>231</v>
       </c>
@@ -4907,10 +4923,10 @@
         <v>233</v>
       </c>
       <c r="H72">
-        <v>-1.205957777E9</v>
+        <v>-1205957777</v>
       </c>
       <c r="I72">
-        <v>-7.70808874E8</v>
+        <v>-770808874</v>
       </c>
       <c r="J72" t="s">
         <v>18</v>
@@ -4919,7 +4935,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="73" ht="14.25" customHeight="1">
+    <row r="73" spans="1:11" ht="14.25" customHeight="1">
       <c r="A73" t="s">
         <v>234</v>
       </c>
@@ -4942,10 +4958,10 @@
         <v>236</v>
       </c>
       <c r="H73">
-        <v>-1.2055507E7</v>
+        <v>-12055507</v>
       </c>
       <c r="I73">
-        <v>-7.7086982E7</v>
+        <v>-77086982</v>
       </c>
       <c r="J73" t="s">
         <v>18</v>
@@ -4954,7 +4970,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="74" ht="14.25" customHeight="1">
+    <row r="74" spans="1:11" ht="14.25" customHeight="1">
       <c r="A74" t="s">
         <v>25</v>
       </c>
@@ -4977,10 +4993,10 @@
         <v>237</v>
       </c>
       <c r="H74">
-        <v>-1.2058386E7</v>
+        <v>-12058386</v>
       </c>
       <c r="I74">
-        <v>-7.7079987E7</v>
+        <v>-77079987</v>
       </c>
       <c r="J74" t="s">
         <v>18</v>
@@ -4989,7 +5005,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="75" ht="14.25" customHeight="1">
+    <row r="75" spans="1:11" ht="14.25" customHeight="1">
       <c r="A75" t="s">
         <v>53</v>
       </c>
@@ -5012,10 +5028,10 @@
         <v>240</v>
       </c>
       <c r="H75">
-        <v>-1.2058352E7</v>
+        <v>-12058352</v>
       </c>
       <c r="I75">
-        <v>-7.7080834E7</v>
+        <v>-77080834</v>
       </c>
       <c r="J75" t="s">
         <v>18</v>
@@ -5024,7 +5040,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="76" ht="14.25" customHeight="1">
+    <row r="76" spans="1:11" ht="14.25" customHeight="1">
       <c r="A76" t="s">
         <v>241</v>
       </c>
@@ -5047,10 +5063,10 @@
         <v>242</v>
       </c>
       <c r="H76">
-        <v>-120567.0</v>
+        <v>-120567</v>
       </c>
       <c r="I76">
-        <v>-77085.0</v>
+        <v>-77085</v>
       </c>
       <c r="J76" t="s">
         <v>18</v>
@@ -5059,7 +5075,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="77" ht="14.25" customHeight="1">
+    <row r="77" spans="1:11" ht="14.25" customHeight="1">
       <c r="A77" t="s">
         <v>243</v>
       </c>
@@ -5082,10 +5098,10 @@
         <v>244</v>
       </c>
       <c r="H77">
-        <v>-1.2059236E7</v>
+        <v>-12059236</v>
       </c>
       <c r="I77">
-        <v>-7.7081608E7</v>
+        <v>-77081608</v>
       </c>
       <c r="J77" t="s">
         <v>18</v>
@@ -5094,7 +5110,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="78" ht="14.25" customHeight="1">
+    <row r="78" spans="1:11" ht="14.25" customHeight="1">
       <c r="A78" t="s">
         <v>245</v>
       </c>
@@ -5117,10 +5133,10 @@
         <v>247</v>
       </c>
       <c r="H78">
-        <v>-1.205791189E9</v>
+        <v>-1205791189</v>
       </c>
       <c r="I78">
-        <v>-7.708579389E9</v>
+        <v>-7708579389</v>
       </c>
       <c r="J78" t="s">
         <v>18</v>
@@ -5129,7 +5145,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="79" ht="14.25" customHeight="1">
+    <row r="79" spans="1:11" ht="14.25" customHeight="1">
       <c r="A79" t="s">
         <v>248</v>
       </c>
@@ -5152,10 +5168,10 @@
         <v>250</v>
       </c>
       <c r="H79">
-        <v>-1.2053856E7</v>
+        <v>-12053856</v>
       </c>
       <c r="I79">
-        <v>-7.7086632E7</v>
+        <v>-77086632</v>
       </c>
       <c r="J79" t="s">
         <v>18</v>
@@ -5164,7 +5180,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="80" ht="14.25" customHeight="1">
+    <row r="80" spans="1:11" ht="14.25" customHeight="1">
       <c r="A80" t="s">
         <v>251</v>
       </c>
@@ -5187,10 +5203,10 @@
         <v>253</v>
       </c>
       <c r="H80">
-        <v>-1205922.0</v>
+        <v>-1205922</v>
       </c>
       <c r="I80">
-        <v>-7.7079594E7</v>
+        <v>-77079594</v>
       </c>
       <c r="J80" t="s">
         <v>62</v>
@@ -5199,7 +5215,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="81" ht="14.25" customHeight="1">
+    <row r="81" spans="1:11" ht="14.25" customHeight="1">
       <c r="A81" t="s">
         <v>254</v>
       </c>
@@ -5222,10 +5238,10 @@
         <v>255</v>
       </c>
       <c r="H81">
-        <v>-1.205974253E9</v>
+        <v>-1205974253</v>
       </c>
       <c r="I81">
-        <v>-7.708080566E9</v>
+        <v>-7708080566</v>
       </c>
       <c r="J81" t="s">
         <v>62</v>
@@ -5234,7 +5250,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="82" ht="14.25" customHeight="1">
+    <row r="82" spans="1:11" ht="14.25" customHeight="1">
       <c r="A82" t="s">
         <v>25</v>
       </c>
@@ -5257,10 +5273,10 @@
         <v>256</v>
       </c>
       <c r="H82">
-        <v>-1.2058576E7</v>
+        <v>-12058576</v>
       </c>
       <c r="I82">
-        <v>-7.7079769E7</v>
+        <v>-77079769</v>
       </c>
       <c r="J82" t="s">
         <v>62</v>
@@ -5269,7 +5285,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="83" ht="14.25" customHeight="1">
+    <row r="83" spans="1:11" ht="14.25" customHeight="1">
       <c r="A83" t="s">
         <v>163</v>
       </c>
@@ -5292,10 +5308,10 @@
         <v>256</v>
       </c>
       <c r="H83">
-        <v>-1.2058576E7</v>
+        <v>-12058576</v>
       </c>
       <c r="I83">
-        <v>-7.7079769E7</v>
+        <v>-77079769</v>
       </c>
       <c r="J83" t="s">
         <v>62</v>
@@ -5304,7 +5320,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="84" ht="14.25" customHeight="1">
+    <row r="84" spans="1:11" ht="14.25" customHeight="1">
       <c r="A84" t="s">
         <v>25</v>
       </c>
@@ -5327,10 +5343,10 @@
         <v>259</v>
       </c>
       <c r="H84">
-        <v>-1.2058012E7</v>
+        <v>-12058012</v>
       </c>
       <c r="I84">
-        <v>-7.7079983E7</v>
+        <v>-77079983</v>
       </c>
       <c r="J84" t="s">
         <v>18</v>
@@ -5339,7 +5355,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="85" ht="14.25" customHeight="1">
+    <row r="85" spans="1:11" ht="14.25" customHeight="1">
       <c r="A85" t="s">
         <v>163</v>
       </c>
@@ -5362,10 +5378,10 @@
         <v>259</v>
       </c>
       <c r="H85">
-        <v>-1.2058012E7</v>
+        <v>-12058012</v>
       </c>
       <c r="I85">
-        <v>-7.7079983E7</v>
+        <v>-77079983</v>
       </c>
       <c r="J85" t="s">
         <v>18</v>
@@ -5374,7 +5390,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="86" ht="14.25" customHeight="1">
+    <row r="86" spans="1:11" ht="14.25" customHeight="1">
       <c r="A86" t="s">
         <v>260</v>
       </c>
@@ -5397,10 +5413,10 @@
         <v>262</v>
       </c>
       <c r="H86">
-        <v>-1.2055613E7</v>
+        <v>-12055613</v>
       </c>
       <c r="I86">
-        <v>-7.7087195E7</v>
+        <v>-77087195</v>
       </c>
       <c r="J86" t="s">
         <v>18</v>
@@ -5409,7 +5425,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="87" ht="14.25" customHeight="1">
+    <row r="87" spans="1:11" ht="14.25" customHeight="1">
       <c r="A87" t="s">
         <v>263</v>
       </c>
@@ -5432,10 +5448,10 @@
         <v>265</v>
       </c>
       <c r="H87">
-        <v>-1.2056613E7</v>
+        <v>-12056613</v>
       </c>
       <c r="I87">
-        <v>-7.7086961E7</v>
+        <v>-77086961</v>
       </c>
       <c r="J87" t="s">
         <v>18</v>
@@ -5444,7 +5460,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="88" ht="14.25" customHeight="1">
+    <row r="88" spans="1:11" ht="14.25" customHeight="1">
       <c r="A88" t="s">
         <v>53</v>
       </c>
@@ -5467,10 +5483,10 @@
         <v>267</v>
       </c>
       <c r="H88">
-        <v>-1.2058254E7</v>
+        <v>-12058254</v>
       </c>
       <c r="I88">
-        <v>-7.7080432E7</v>
+        <v>-77080432</v>
       </c>
       <c r="J88" t="s">
         <v>18</v>
@@ -5479,7 +5495,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="89" ht="14.25" customHeight="1">
+    <row r="89" spans="1:11" ht="14.25" customHeight="1">
       <c r="A89" t="s">
         <v>268</v>
       </c>
@@ -5502,10 +5518,10 @@
         <v>269</v>
       </c>
       <c r="H89">
-        <v>-1.2059274E7</v>
+        <v>-12059274</v>
       </c>
       <c r="I89">
-        <v>-770808.0</v>
+        <v>-770808</v>
       </c>
       <c r="J89" t="s">
         <v>18</v>
@@ -5514,7 +5530,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="90" ht="14.25" customHeight="1">
+    <row r="90" spans="1:11" ht="14.25" customHeight="1">
       <c r="A90" t="s">
         <v>53</v>
       </c>
@@ -5537,10 +5553,10 @@
         <v>270</v>
       </c>
       <c r="H90">
-        <v>-1.2058254E7</v>
+        <v>-12058254</v>
       </c>
       <c r="I90">
-        <v>-7.7080432E7</v>
+        <v>-77080432</v>
       </c>
       <c r="J90" t="s">
         <v>18</v>
@@ -5549,7 +5565,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="91" ht="14.25" customHeight="1">
+    <row r="91" spans="1:11" ht="14.25" customHeight="1">
       <c r="A91" t="s">
         <v>271</v>
       </c>
@@ -5572,10 +5588,10 @@
         <v>272</v>
       </c>
       <c r="H91">
-        <v>-1.205671728E9</v>
+        <v>-1205671728</v>
       </c>
       <c r="I91">
-        <v>-7.708682219E9</v>
+        <v>-7708682219</v>
       </c>
       <c r="J91" t="s">
         <v>18</v>
@@ -5584,7 +5600,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="92" ht="14.25" customHeight="1">
+    <row r="92" spans="1:11" ht="14.25" customHeight="1">
       <c r="A92" t="s">
         <v>273</v>
       </c>
@@ -5607,10 +5623,10 @@
         <v>275</v>
       </c>
       <c r="H92">
-        <v>-1.2054019E7</v>
+        <v>-12054019</v>
       </c>
       <c r="I92">
-        <v>-7.7085599E7</v>
+        <v>-77085599</v>
       </c>
       <c r="J92" t="s">
         <v>18</v>
@@ -5619,7 +5635,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="93" ht="14.25" customHeight="1">
+    <row r="93" spans="1:11" ht="14.25" customHeight="1">
       <c r="A93" t="s">
         <v>53</v>
       </c>
@@ -5642,10 +5658,10 @@
         <v>276</v>
       </c>
       <c r="H93">
-        <v>-1.2058552E7</v>
+        <v>-12058552</v>
       </c>
       <c r="I93">
-        <v>-7.708092E7</v>
+        <v>-77080920</v>
       </c>
       <c r="J93" t="s">
         <v>18</v>
@@ -5654,7 +5670,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="94" ht="14.25" customHeight="1">
+    <row r="94" spans="1:11" ht="14.25" customHeight="1">
       <c r="A94" t="s">
         <v>38</v>
       </c>
@@ -5677,10 +5693,10 @@
         <v>278</v>
       </c>
       <c r="H94">
-        <v>-1.205796644E9</v>
+        <v>-1205796644</v>
       </c>
       <c r="I94">
-        <v>-7.708147904E9</v>
+        <v>-7708147904</v>
       </c>
       <c r="J94" t="s">
         <v>18</v>
@@ -5689,7 +5705,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="95" ht="14.25" customHeight="1">
+    <row r="95" spans="1:11" ht="14.25" customHeight="1">
       <c r="A95" t="s">
         <v>25</v>
       </c>
@@ -5712,10 +5728,10 @@
         <v>279</v>
       </c>
       <c r="H95">
-        <v>-1.2057968E7</v>
+        <v>-12057968</v>
       </c>
       <c r="I95">
-        <v>-7.7079862E7</v>
+        <v>-77079862</v>
       </c>
       <c r="J95" t="s">
         <v>18</v>
@@ -5724,7 +5740,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="96" ht="14.25" customHeight="1">
+    <row r="96" spans="1:11" ht="14.25" customHeight="1">
       <c r="A96" t="s">
         <v>280</v>
       </c>
@@ -5747,10 +5763,10 @@
         <v>282</v>
       </c>
       <c r="H96">
-        <v>-1.2059339E7</v>
+        <v>-12059339</v>
       </c>
       <c r="I96">
-        <v>-7.7087202E7</v>
+        <v>-77087202</v>
       </c>
       <c r="J96" t="s">
         <v>62</v>
@@ -5759,7 +5775,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="97" ht="14.25" customHeight="1">
+    <row r="97" spans="1:11" ht="14.25" customHeight="1">
       <c r="A97" t="s">
         <v>53</v>
       </c>
@@ -5782,10 +5798,10 @@
         <v>284</v>
       </c>
       <c r="H97">
-        <v>-1.2058455E7</v>
+        <v>-12058455</v>
       </c>
       <c r="I97">
-        <v>-7.7080218E7</v>
+        <v>-77080218</v>
       </c>
       <c r="J97" t="s">
         <v>18</v>
@@ -5794,7 +5810,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="98" ht="14.25" customHeight="1">
+    <row r="98" spans="1:11" ht="14.25" customHeight="1">
       <c r="A98" t="s">
         <v>25</v>
       </c>
@@ -5817,10 +5833,10 @@
         <v>286</v>
       </c>
       <c r="H98">
-        <v>-1.2058223E7</v>
+        <v>-12058223</v>
       </c>
       <c r="I98">
-        <v>-7.7079791E7</v>
+        <v>-77079791</v>
       </c>
       <c r="J98" t="s">
         <v>18</v>
@@ -5829,7 +5845,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="99" ht="14.25" customHeight="1">
+    <row r="99" spans="1:11" ht="14.25" customHeight="1">
       <c r="A99" t="s">
         <v>287</v>
       </c>
@@ -5852,10 +5868,10 @@
         <v>289</v>
       </c>
       <c r="H99">
-        <v>-1.205992081E9</v>
+        <v>-1205992081</v>
       </c>
       <c r="I99">
-        <v>-7.708127214E9</v>
+        <v>-7708127214</v>
       </c>
       <c r="J99" t="s">
         <v>18</v>
@@ -5864,7 +5880,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="100" ht="14.25" customHeight="1">
+    <row r="100" spans="1:11" ht="14.25" customHeight="1">
       <c r="A100" t="s">
         <v>290</v>
       </c>
@@ -5887,10 +5903,10 @@
         <v>292</v>
       </c>
       <c r="H100">
-        <v>-1.2054729E7</v>
+        <v>-12054729</v>
       </c>
       <c r="I100">
-        <v>-7.7085504E7</v>
+        <v>-77085504</v>
       </c>
       <c r="J100" t="s">
         <v>18</v>
@@ -5899,7 +5915,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="101" ht="14.25" customHeight="1">
+    <row r="101" spans="1:11" ht="14.25" customHeight="1">
       <c r="A101" t="s">
         <v>293</v>
       </c>
@@ -5922,10 +5938,10 @@
         <v>295</v>
       </c>
       <c r="H101">
-        <v>-1.2055623E7</v>
+        <v>-12055623</v>
       </c>
       <c r="I101">
-        <v>-7.7087197E7</v>
+        <v>-77087197</v>
       </c>
       <c r="J101" t="s">
         <v>18</v>
@@ -5934,7 +5950,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="102" ht="14.25" customHeight="1">
+    <row r="102" spans="1:11" ht="14.25" customHeight="1">
       <c r="A102" t="s">
         <v>25</v>
       </c>
@@ -5957,10 +5973,10 @@
         <v>296</v>
       </c>
       <c r="H102">
-        <v>-1.2058521E7</v>
+        <v>-12058521</v>
       </c>
       <c r="I102">
-        <v>-7.7079742E7</v>
+        <v>-77079742</v>
       </c>
       <c r="J102" t="s">
         <v>18</v>
@@ -5969,7 +5985,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="103" ht="14.25" customHeight="1">
+    <row r="103" spans="1:11" ht="14.25" customHeight="1">
       <c r="A103" t="s">
         <v>297</v>
       </c>
@@ -5992,10 +6008,10 @@
         <v>299</v>
       </c>
       <c r="H103">
-        <v>-1.205393778E9</v>
+        <v>-1205393778</v>
       </c>
       <c r="I103">
-        <v>-7.708729878E9</v>
+        <v>-7708729878</v>
       </c>
       <c r="J103" t="s">
         <v>18</v>
@@ -6004,7 +6020,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="104" ht="14.25" customHeight="1">
+    <row r="104" spans="1:11" ht="14.25" customHeight="1">
       <c r="A104" t="s">
         <v>53</v>
       </c>
@@ -6027,10 +6043,10 @@
         <v>300</v>
       </c>
       <c r="H104">
-        <v>-1.2058258E7</v>
+        <v>-12058258</v>
       </c>
       <c r="I104">
-        <v>-7.7080569E7</v>
+        <v>-77080569</v>
       </c>
       <c r="J104" t="s">
         <v>18</v>
@@ -6039,7 +6055,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="105" ht="14.25" customHeight="1">
+    <row r="105" spans="1:11" ht="14.25" customHeight="1">
       <c r="A105" t="s">
         <v>25</v>
       </c>
@@ -6062,10 +6078,10 @@
         <v>302</v>
       </c>
       <c r="H105">
-        <v>-1.2058521E7</v>
+        <v>-12058521</v>
       </c>
       <c r="I105">
-        <v>-7.7079742E7</v>
+        <v>-77079742</v>
       </c>
       <c r="J105" t="s">
         <v>18</v>
@@ -6074,7 +6090,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="106" ht="14.25" customHeight="1">
+    <row r="106" spans="1:11" ht="14.25" customHeight="1">
       <c r="A106" t="s">
         <v>303</v>
       </c>
@@ -6097,10 +6113,10 @@
         <v>304</v>
       </c>
       <c r="H106">
-        <v>-1.205940176E9</v>
+        <v>-1205940176</v>
       </c>
       <c r="I106">
-        <v>-7.708161868E9</v>
+        <v>-7708161868</v>
       </c>
       <c r="J106" t="s">
         <v>18</v>
@@ -6109,7 +6125,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="107" ht="14.25" customHeight="1">
+    <row r="107" spans="1:11" ht="14.25" customHeight="1">
       <c r="A107" t="s">
         <v>305</v>
       </c>
@@ -6132,10 +6148,10 @@
         <v>307</v>
       </c>
       <c r="H107">
-        <v>-1.205744058E9</v>
+        <v>-1205744058</v>
       </c>
       <c r="I107">
-        <v>-7.708600328E9</v>
+        <v>-7708600328</v>
       </c>
       <c r="J107" t="s">
         <v>18</v>
@@ -6144,7 +6160,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="108" ht="14.25" customHeight="1">
+    <row r="108" spans="1:11" ht="14.25" customHeight="1">
       <c r="A108" t="s">
         <v>308</v>
       </c>
@@ -6167,10 +6183,10 @@
         <v>310</v>
       </c>
       <c r="H108">
-        <v>-1.2060812E7</v>
+        <v>-12060812</v>
       </c>
       <c r="I108">
-        <v>-7.7084473E7</v>
+        <v>-77084473</v>
       </c>
       <c r="J108" t="s">
         <v>18</v>
@@ -6179,7 +6195,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="109" ht="14.25" customHeight="1">
+    <row r="109" spans="1:11" ht="14.25" customHeight="1">
       <c r="A109" t="s">
         <v>311</v>
       </c>
@@ -6202,10 +6218,10 @@
         <v>312</v>
       </c>
       <c r="H109">
-        <v>-1.205791189E9</v>
+        <v>-1205791189</v>
       </c>
       <c r="I109">
-        <v>-7.708579389E9</v>
+        <v>-7708579389</v>
       </c>
       <c r="J109" t="s">
         <v>18</v>
@@ -6214,7 +6230,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="110" ht="14.25" customHeight="1">
+    <row r="110" spans="1:11" ht="14.25" customHeight="1">
       <c r="A110" t="s">
         <v>53</v>
       </c>
@@ -6237,10 +6253,10 @@
         <v>313</v>
       </c>
       <c r="H110">
-        <v>-1.2058455E7</v>
+        <v>-12058455</v>
       </c>
       <c r="I110">
-        <v>-7.7080218E7</v>
+        <v>-77080218</v>
       </c>
       <c r="J110" t="s">
         <v>18</v>
@@ -6249,7 +6265,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="111" ht="14.25" customHeight="1">
+    <row r="111" spans="1:11" ht="14.25" customHeight="1">
       <c r="A111" t="s">
         <v>314</v>
       </c>
@@ -6272,10 +6288,10 @@
         <v>315</v>
       </c>
       <c r="H111">
-        <v>-1.2059857E7</v>
+        <v>-12059857</v>
       </c>
       <c r="I111">
-        <v>-7.7081168E7</v>
+        <v>-77081168</v>
       </c>
       <c r="J111" t="s">
         <v>18</v>
@@ -6284,7 +6300,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="112" ht="14.25" customHeight="1">
+    <row r="112" spans="1:11" ht="14.25" customHeight="1">
       <c r="A112" t="s">
         <v>25</v>
       </c>
@@ -6307,10 +6323,10 @@
         <v>316</v>
       </c>
       <c r="H112">
-        <v>-1.2058446E7</v>
+        <v>-12058446</v>
       </c>
       <c r="I112">
-        <v>-7.7079712E7</v>
+        <v>-77079712</v>
       </c>
       <c r="J112" t="s">
         <v>18</v>
@@ -6319,7 +6335,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="113" ht="14.25" customHeight="1">
+    <row r="113" spans="1:11" ht="14.25" customHeight="1">
       <c r="A113" t="s">
         <v>25</v>
       </c>
@@ -6342,10 +6358,10 @@
         <v>317</v>
       </c>
       <c r="H113">
-        <v>-1.2058357E7</v>
+        <v>-12058357</v>
       </c>
       <c r="I113">
-        <v>-7.7079686E7</v>
+        <v>-77079686</v>
       </c>
       <c r="J113" t="s">
         <v>18</v>
@@ -6354,7 +6370,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="114" ht="14.25" customHeight="1">
+    <row r="114" spans="1:11" ht="14.25" customHeight="1">
       <c r="A114" t="s">
         <v>53</v>
       </c>
@@ -6377,10 +6393,10 @@
         <v>318</v>
       </c>
       <c r="H114">
-        <v>-1.2058378E7</v>
+        <v>-12058378</v>
       </c>
       <c r="I114">
-        <v>-7.7080139E7</v>
+        <v>-77080139</v>
       </c>
       <c r="J114" t="s">
         <v>18</v>
@@ -6389,7 +6405,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="115" ht="14.25" customHeight="1">
+    <row r="115" spans="1:11" ht="14.25" customHeight="1">
       <c r="A115" t="s">
         <v>319</v>
       </c>
@@ -6412,10 +6428,10 @@
         <v>320</v>
       </c>
       <c r="H115">
-        <v>-1.2059204E7</v>
+        <v>-12059204</v>
       </c>
       <c r="I115">
-        <v>-7.7079622E7</v>
+        <v>-77079622</v>
       </c>
       <c r="J115" t="s">
         <v>18</v>
@@ -6424,7 +6440,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="116" ht="14.25" customHeight="1">
+    <row r="116" spans="1:11" ht="14.25" customHeight="1">
       <c r="A116" t="s">
         <v>321</v>
       </c>
@@ -6447,10 +6463,10 @@
         <v>323</v>
       </c>
       <c r="H116">
-        <v>-1.20599869E8</v>
+        <v>-120599869</v>
       </c>
       <c r="I116">
-        <v>-7.708184206E9</v>
+        <v>-7708184206</v>
       </c>
       <c r="J116" t="s">
         <v>18</v>
@@ -6459,7 +6475,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="117" ht="14.25" customHeight="1">
+    <row r="117" spans="1:11" ht="14.25" customHeight="1">
       <c r="A117" t="s">
         <v>324</v>
       </c>
@@ -6482,10 +6498,10 @@
         <v>325</v>
       </c>
       <c r="H117">
-        <v>-1.205704639E9</v>
+        <v>-1205704639</v>
       </c>
       <c r="I117">
-        <v>-7.708647347E9</v>
+        <v>-7708647347</v>
       </c>
       <c r="J117" t="s">
         <v>18</v>
@@ -6494,7 +6510,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="118" ht="14.25" customHeight="1">
+    <row r="118" spans="1:11" ht="14.25" customHeight="1">
       <c r="A118" t="s">
         <v>326</v>
       </c>
@@ -6517,10 +6533,10 @@
         <v>327</v>
       </c>
       <c r="H118">
-        <v>-1.2057855E7</v>
+        <v>-12057855</v>
       </c>
       <c r="I118">
-        <v>-7.7080801E7</v>
+        <v>-77080801</v>
       </c>
       <c r="J118" t="s">
         <v>18</v>
@@ -6529,7 +6545,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="119" ht="14.25" customHeight="1">
+    <row r="119" spans="1:11" ht="14.25" customHeight="1">
       <c r="A119" t="s">
         <v>38</v>
       </c>
@@ -6552,10 +6568,10 @@
         <v>328</v>
       </c>
       <c r="H119">
-        <v>-1.2058044E7</v>
+        <v>-12058044</v>
       </c>
       <c r="I119">
-        <v>-7708053.0</v>
+        <v>-7708053</v>
       </c>
       <c r="J119" t="s">
         <v>18</v>
@@ -6564,7 +6580,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="120" ht="14.25" customHeight="1">
+    <row r="120" spans="1:11" ht="14.25" customHeight="1">
       <c r="A120" t="s">
         <v>53</v>
       </c>
@@ -6587,10 +6603,10 @@
         <v>329</v>
       </c>
       <c r="H120">
-        <v>-1.2058552E7</v>
+        <v>-12058552</v>
       </c>
       <c r="I120">
-        <v>-7.708092E7</v>
+        <v>-77080920</v>
       </c>
       <c r="J120" t="s">
         <v>18</v>
@@ -6599,7 +6615,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="121" ht="14.25" customHeight="1">
+    <row r="121" spans="1:11" ht="14.25" customHeight="1">
       <c r="A121" t="s">
         <v>330</v>
       </c>
@@ -6622,10 +6638,10 @@
         <v>331</v>
       </c>
       <c r="H121">
-        <v>-1.2059274E7</v>
+        <v>-12059274</v>
       </c>
       <c r="I121">
-        <v>-770808.0</v>
+        <v>-770808</v>
       </c>
       <c r="J121" t="s">
         <v>18</v>
@@ -6634,7 +6650,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="122" ht="14.25" customHeight="1">
+    <row r="122" spans="1:11" ht="14.25" customHeight="1">
       <c r="A122" t="s">
         <v>332</v>
       </c>
@@ -6657,10 +6673,10 @@
         <v>336</v>
       </c>
       <c r="H122">
-        <v>-1.2055491E7</v>
+        <v>-12055491</v>
       </c>
       <c r="I122">
-        <v>-7.7087924E7</v>
+        <v>-77087924</v>
       </c>
       <c r="J122" t="s">
         <v>18</v>
@@ -6669,7 +6685,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="123" ht="14.25" customHeight="1">
+    <row r="123" spans="1:11" ht="14.25" customHeight="1">
       <c r="A123" t="s">
         <v>337</v>
       </c>
@@ -6692,10 +6708,10 @@
         <v>340</v>
       </c>
       <c r="H123">
-        <v>-1.2053839E7</v>
+        <v>-12053839</v>
       </c>
       <c r="I123">
-        <v>-7.7086625E7</v>
+        <v>-77086625</v>
       </c>
       <c r="J123" t="s">
         <v>18</v>
@@ -6704,7 +6720,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="124" ht="14.25" customHeight="1">
+    <row r="124" spans="1:11" ht="14.25" customHeight="1">
       <c r="A124" t="s">
         <v>341</v>
       </c>
@@ -6727,10 +6743,10 @@
         <v>343</v>
       </c>
       <c r="H124">
-        <v>-1205651.0</v>
+        <v>-1205651</v>
       </c>
       <c r="I124">
-        <v>-7.7087056E7</v>
+        <v>-77087056</v>
       </c>
       <c r="J124" t="s">
         <v>18</v>
@@ -6739,7 +6755,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="125" ht="14.25" customHeight="1">
+    <row r="125" spans="1:11" ht="14.25" customHeight="1">
       <c r="A125" t="s">
         <v>344</v>
       </c>
@@ -6762,10 +6778,10 @@
         <v>348</v>
       </c>
       <c r="H125">
-        <v>-1.20560768E8</v>
+        <v>-120560768</v>
       </c>
       <c r="I125">
-        <v>-7.70822742E8</v>
+        <v>-770822742</v>
       </c>
       <c r="J125" t="s">
         <v>18</v>
@@ -6774,7 +6790,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="126" ht="14.25" customHeight="1">
+    <row r="126" spans="1:11" ht="14.25" customHeight="1">
       <c r="A126" t="s">
         <v>38</v>
       </c>
@@ -6797,10 +6813,10 @@
         <v>349</v>
       </c>
       <c r="H126">
-        <v>-1.205792004E9</v>
+        <v>-1205792004</v>
       </c>
       <c r="I126">
-        <v>-7.708145421E9</v>
+        <v>-7708145421</v>
       </c>
       <c r="J126" t="s">
         <v>18</v>
@@ -6809,7 +6825,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="127" ht="14.25" customHeight="1">
+    <row r="127" spans="1:11" ht="14.25" customHeight="1">
       <c r="A127" t="s">
         <v>137</v>
       </c>
@@ -6832,10 +6848,10 @@
         <v>351</v>
       </c>
       <c r="H127">
-        <v>-1.2056342E7</v>
+        <v>-12056342</v>
       </c>
       <c r="I127">
-        <v>-7.7080938E7</v>
+        <v>-77080938</v>
       </c>
       <c r="J127" t="s">
         <v>18</v>
@@ -6844,7 +6860,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="128" ht="14.25" customHeight="1">
+    <row r="128" spans="1:11" ht="14.25" customHeight="1">
       <c r="A128" t="s">
         <v>352</v>
       </c>
@@ -6867,10 +6883,10 @@
         <v>354</v>
       </c>
       <c r="H128">
-        <v>-1.2059581E7</v>
+        <v>-12059581</v>
       </c>
       <c r="I128">
-        <v>-7.7080704E7</v>
+        <v>-77080704</v>
       </c>
       <c r="J128" t="s">
         <v>18</v>
@@ -6879,7 +6895,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="129" ht="14.25" customHeight="1">
+    <row r="129" spans="1:11" ht="14.25" customHeight="1">
       <c r="A129" t="s">
         <v>355</v>
       </c>
@@ -6902,10 +6918,10 @@
         <v>356</v>
       </c>
       <c r="H129">
-        <v>-1.2057104E7</v>
+        <v>-12057104</v>
       </c>
       <c r="I129">
-        <v>-7.7086707E7</v>
+        <v>-77086707</v>
       </c>
       <c r="J129" t="s">
         <v>18</v>
@@ -6914,7 +6930,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="130" ht="14.25" customHeight="1">
+    <row r="130" spans="1:11" ht="14.25" customHeight="1">
       <c r="A130" t="s">
         <v>53</v>
       </c>
@@ -6937,10 +6953,10 @@
         <v>360</v>
       </c>
       <c r="H130">
-        <v>-1.2058392E7</v>
+        <v>-12058392</v>
       </c>
       <c r="I130">
-        <v>-7.7080974E7</v>
+        <v>-77080974</v>
       </c>
       <c r="J130" t="s">
         <v>62</v>
@@ -6949,7 +6965,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="131" ht="14.25" customHeight="1">
+    <row r="131" spans="1:11" ht="14.25" customHeight="1">
       <c r="A131" t="s">
         <v>361</v>
       </c>
@@ -6972,10 +6988,10 @@
         <v>364</v>
       </c>
       <c r="H131">
-        <v>-1.205735758E9</v>
+        <v>-1205735758</v>
       </c>
       <c r="I131">
-        <v>-7.708610558E9</v>
+        <v>-7708610558</v>
       </c>
       <c r="J131" t="s">
         <v>18</v>
@@ -6984,7 +7000,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="132" ht="14.25" customHeight="1">
+    <row r="132" spans="1:11" ht="14.25" customHeight="1">
       <c r="A132" t="s">
         <v>25</v>
       </c>
@@ -7007,10 +7023,10 @@
         <v>365</v>
       </c>
       <c r="H132">
-        <v>-1.2058555E7</v>
+        <v>-12058555</v>
       </c>
       <c r="I132">
-        <v>-7.7079716E7</v>
+        <v>-77079716</v>
       </c>
       <c r="J132" t="s">
         <v>18</v>
@@ -7019,7 +7035,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="133" ht="14.25" customHeight="1">
+    <row r="133" spans="1:11" ht="14.25" customHeight="1">
       <c r="A133" t="s">
         <v>25</v>
       </c>
@@ -7042,10 +7058,10 @@
         <v>366</v>
       </c>
       <c r="H133">
-        <v>-1.2058503E7</v>
+        <v>-12058503</v>
       </c>
       <c r="I133">
-        <v>-7.7079896E7</v>
+        <v>-77079896</v>
       </c>
       <c r="J133" t="s">
         <v>18</v>
@@ -7054,7 +7070,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="134" ht="14.25" customHeight="1">
+    <row r="134" spans="1:11" ht="14.25" customHeight="1">
       <c r="A134" t="s">
         <v>51</v>
       </c>
@@ -7077,10 +7093,10 @@
         <v>367</v>
       </c>
       <c r="H134">
-        <v>-1.20543072E8</v>
+        <v>-120543072</v>
       </c>
       <c r="I134">
-        <v>-7.70845118E8</v>
+        <v>-770845118</v>
       </c>
       <c r="J134" t="s">
         <v>18</v>
@@ -7089,7 +7105,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="135" ht="14.25" customHeight="1">
+    <row r="135" spans="1:11" ht="14.25" customHeight="1">
       <c r="A135" t="s">
         <v>368</v>
       </c>
@@ -7112,10 +7128,10 @@
         <v>369</v>
       </c>
       <c r="H135">
-        <v>-1.2055931E7</v>
+        <v>-12055931</v>
       </c>
       <c r="I135">
-        <v>-7.7082624E7</v>
+        <v>-77082624</v>
       </c>
       <c r="J135" t="s">
         <v>18</v>
@@ -7124,7 +7140,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="136" ht="14.25" customHeight="1">
+    <row r="136" spans="1:11" ht="14.25" customHeight="1">
       <c r="A136" t="s">
         <v>25</v>
       </c>
@@ -7147,10 +7163,10 @@
         <v>371</v>
       </c>
       <c r="H136">
-        <v>-1.2058558E7</v>
+        <v>-12058558</v>
       </c>
       <c r="I136">
-        <v>-7.7079863E7</v>
+        <v>-77079863</v>
       </c>
       <c r="J136" t="s">
         <v>62</v>
@@ -7159,7 +7175,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="137" ht="14.25" customHeight="1">
+    <row r="137" spans="1:11" ht="14.25" customHeight="1">
       <c r="A137" t="s">
         <v>372</v>
       </c>
@@ -7182,10 +7198,10 @@
         <v>373</v>
       </c>
       <c r="H137">
-        <v>-1205732.0</v>
+        <v>-1205732</v>
       </c>
       <c r="I137">
-        <v>-7708635.0</v>
+        <v>-7708635</v>
       </c>
       <c r="J137" t="s">
         <v>62</v>
@@ -7194,7 +7210,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="138" ht="14.25" customHeight="1">
+    <row r="138" spans="1:11" ht="14.25" customHeight="1">
       <c r="A138" t="s">
         <v>23</v>
       </c>
@@ -7217,10 +7233,10 @@
         <v>376</v>
       </c>
       <c r="H138">
-        <v>-1.20547328E8</v>
+        <v>-120547328</v>
       </c>
       <c r="I138">
-        <v>-7.70851167E8</v>
+        <v>-770851167</v>
       </c>
       <c r="J138" t="s">
         <v>18</v>
@@ -7229,7 +7245,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="139" ht="14.25" customHeight="1">
+    <row r="139" spans="1:11" ht="14.25" customHeight="1">
       <c r="A139" t="s">
         <v>25</v>
       </c>
@@ -7252,10 +7268,10 @@
         <v>379</v>
       </c>
       <c r="H139">
-        <v>-1.2057859E7</v>
+        <v>-12057859</v>
       </c>
       <c r="I139">
-        <v>-7.7079771E7</v>
+        <v>-77079771</v>
       </c>
       <c r="J139" t="s">
         <v>18</v>
@@ -7264,7 +7280,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="140" ht="14.25" customHeight="1">
+    <row r="140" spans="1:11" ht="14.25" customHeight="1">
       <c r="A140" t="s">
         <v>380</v>
       </c>
@@ -7287,10 +7303,10 @@
         <v>382</v>
       </c>
       <c r="H140">
-        <v>-1.2059856E7</v>
+        <v>-12059856</v>
       </c>
       <c r="I140">
-        <v>-7.7081167E7</v>
+        <v>-77081167</v>
       </c>
       <c r="J140" t="s">
         <v>18</v>
@@ -7299,7 +7315,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="141" ht="14.25" customHeight="1">
+    <row r="141" spans="1:11" ht="14.25" customHeight="1">
       <c r="A141" t="s">
         <v>383</v>
       </c>
@@ -7322,10 +7338,10 @@
         <v>385</v>
       </c>
       <c r="H141">
-        <v>-1.2059339E7</v>
+        <v>-12059339</v>
       </c>
       <c r="I141">
-        <v>-7.7087202E7</v>
+        <v>-77087202</v>
       </c>
       <c r="J141" t="s">
         <v>18</v>
@@ -7334,7 +7350,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="142" ht="14.25" customHeight="1">
+    <row r="142" spans="1:11" ht="14.25" customHeight="1">
       <c r="A142" t="s">
         <v>344</v>
       </c>
@@ -7357,10 +7373,10 @@
         <v>387</v>
       </c>
       <c r="H142">
-        <v>-1.2056708E7</v>
+        <v>-12056708</v>
       </c>
       <c r="I142">
-        <v>-7.70815916E8</v>
+        <v>-770815916</v>
       </c>
       <c r="J142" t="s">
         <v>18</v>
@@ -7369,7 +7385,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="143" ht="14.25" customHeight="1">
+    <row r="143" spans="1:11" ht="14.25" customHeight="1">
       <c r="A143" t="s">
         <v>388</v>
       </c>
@@ -7392,10 +7408,10 @@
         <v>392</v>
       </c>
       <c r="H143">
-        <v>-1.2054079E7</v>
+        <v>-12054079</v>
       </c>
       <c r="I143">
-        <v>-7.7085772E7</v>
+        <v>-77085772</v>
       </c>
       <c r="J143" t="s">
         <v>62</v>
@@ -7404,7 +7420,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="144" ht="14.25" customHeight="1">
+    <row r="144" spans="1:11" ht="14.25" customHeight="1">
       <c r="A144" t="s">
         <v>394</v>
       </c>
@@ -7427,10 +7443,10 @@
         <v>397</v>
       </c>
       <c r="H144">
-        <v>-1.2060274E7</v>
+        <v>-12060274</v>
       </c>
       <c r="I144">
-        <v>-7.7084485E7</v>
+        <v>-77084485</v>
       </c>
       <c r="J144" t="s">
         <v>18</v>
@@ -7439,7 +7455,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="145" ht="14.25" customHeight="1">
+    <row r="145" spans="1:11" ht="14.25" customHeight="1">
       <c r="A145" t="s">
         <v>398</v>
       </c>
@@ -7462,10 +7478,10 @@
         <v>400</v>
       </c>
       <c r="H145">
-        <v>-1.2060527E7</v>
+        <v>-12060527</v>
       </c>
       <c r="I145">
-        <v>-7.7084247E7</v>
+        <v>-77084247</v>
       </c>
       <c r="J145" t="s">
         <v>18</v>
@@ -7474,7 +7490,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="146" ht="14.25" customHeight="1">
+    <row r="146" spans="1:11" ht="14.25" customHeight="1">
       <c r="A146" t="s">
         <v>401</v>
       </c>
@@ -7497,10 +7513,10 @@
         <v>403</v>
       </c>
       <c r="H146">
-        <v>-1.2053551E7</v>
+        <v>-12053551</v>
       </c>
       <c r="I146">
-        <v>-7.7086277E7</v>
+        <v>-77086277</v>
       </c>
       <c r="J146" t="s">
         <v>18</v>
@@ -7509,7 +7525,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="147" ht="14.25" customHeight="1">
+    <row r="147" spans="1:11" ht="14.25" customHeight="1">
       <c r="A147" t="s">
         <v>404</v>
       </c>
@@ -7532,10 +7548,10 @@
         <v>406</v>
       </c>
       <c r="H147">
-        <v>-1.2054729E7</v>
+        <v>-12054729</v>
       </c>
       <c r="I147">
-        <v>-7.7085504E7</v>
+        <v>-77085504</v>
       </c>
       <c r="J147" t="s">
         <v>18</v>
@@ -7544,7 +7560,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="148" ht="14.25" customHeight="1">
+    <row r="148" spans="1:11" ht="14.25" customHeight="1">
       <c r="A148" t="s">
         <v>151</v>
       </c>
@@ -7567,10 +7583,10 @@
         <v>407</v>
       </c>
       <c r="H148">
-        <v>-1.2053413E7</v>
+        <v>-12053413</v>
       </c>
       <c r="I148">
-        <v>-7.7086877E7</v>
+        <v>-77086877</v>
       </c>
       <c r="J148" t="s">
         <v>18</v>
@@ -7579,7 +7595,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="149" ht="14.25" customHeight="1">
+    <row r="149" spans="1:11" ht="14.25" customHeight="1">
       <c r="A149" t="s">
         <v>53</v>
       </c>
@@ -7602,10 +7618,10 @@
         <v>408</v>
       </c>
       <c r="H149">
-        <v>-1.2058444E7</v>
+        <v>-12058444</v>
       </c>
       <c r="I149">
-        <v>-7.7080372E7</v>
+        <v>-77080372</v>
       </c>
       <c r="J149" t="s">
         <v>18</v>
@@ -7614,7 +7630,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="150" ht="14.25" customHeight="1">
+    <row r="150" spans="1:11" ht="14.25" customHeight="1">
       <c r="A150" t="s">
         <v>53</v>
       </c>
@@ -7637,10 +7653,10 @@
         <v>411</v>
       </c>
       <c r="H150">
-        <v>-1.2058455E7</v>
+        <v>-12058455</v>
       </c>
       <c r="I150">
-        <v>-7.7080218E7</v>
+        <v>-77080218</v>
       </c>
       <c r="J150" t="s">
         <v>18</v>
@@ -7649,7 +7665,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="151" ht="14.25" customHeight="1">
+    <row r="151" spans="1:11" ht="14.25" customHeight="1">
       <c r="A151" t="s">
         <v>25</v>
       </c>
@@ -7672,10 +7688,10 @@
         <v>413</v>
       </c>
       <c r="H151">
-        <v>-1.205821E7</v>
+        <v>-12058210</v>
       </c>
       <c r="I151">
-        <v>-7.7079859E7</v>
+        <v>-77079859</v>
       </c>
       <c r="J151" t="s">
         <v>18</v>
@@ -7684,7 +7700,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="152" ht="14.25" customHeight="1">
+    <row r="152" spans="1:11" ht="14.25" customHeight="1">
       <c r="A152" t="s">
         <v>414</v>
       </c>
@@ -7707,10 +7723,10 @@
         <v>416</v>
       </c>
       <c r="H152">
-        <v>-1.2059274E7</v>
+        <v>-12059274</v>
       </c>
       <c r="I152">
-        <v>-770808.0</v>
+        <v>-770808</v>
       </c>
       <c r="J152" t="s">
         <v>18</v>
@@ -7719,7 +7735,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="153" ht="14.25" customHeight="1">
+    <row r="153" spans="1:11" ht="14.25" customHeight="1">
       <c r="A153" t="s">
         <v>417</v>
       </c>
@@ -7742,10 +7758,10 @@
         <v>419</v>
       </c>
       <c r="H153">
-        <v>-1205732.0</v>
+        <v>-1205732</v>
       </c>
       <c r="I153">
-        <v>-7708635.0</v>
+        <v>-7708635</v>
       </c>
       <c r="J153" t="s">
         <v>62</v>
@@ -7754,7 +7770,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="154" ht="14.25" customHeight="1">
+    <row r="154" spans="1:11" ht="14.25" customHeight="1">
       <c r="A154" t="s">
         <v>420</v>
       </c>
@@ -7777,10 +7793,10 @@
         <v>423</v>
       </c>
       <c r="H154">
-        <v>-1.2059642E7</v>
+        <v>-12059642</v>
       </c>
       <c r="I154">
-        <v>-7.7080672E7</v>
+        <v>-77080672</v>
       </c>
       <c r="J154" t="s">
         <v>18</v>
@@ -7789,7 +7805,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="155" ht="14.25" customHeight="1">
+    <row r="155" spans="1:11" ht="14.25" customHeight="1">
       <c r="A155" t="s">
         <v>424</v>
       </c>
@@ -7812,10 +7828,10 @@
         <v>426</v>
       </c>
       <c r="H155">
-        <v>-1.206028675E9</v>
+        <v>-1206028675</v>
       </c>
       <c r="I155">
-        <v>-7.70813027E8</v>
+        <v>-770813027</v>
       </c>
       <c r="J155" t="s">
         <v>18</v>
@@ -7824,7 +7840,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="156" ht="14.25" customHeight="1">
+    <row r="156" spans="1:11" ht="14.25" customHeight="1">
       <c r="A156" t="s">
         <v>53</v>
       </c>
@@ -7847,10 +7863,10 @@
         <v>428</v>
       </c>
       <c r="H156">
-        <v>-1.2058378E7</v>
+        <v>-12058378</v>
       </c>
       <c r="I156">
-        <v>-7.7080139E7</v>
+        <v>-77080139</v>
       </c>
       <c r="J156" t="s">
         <v>18</v>
@@ -7859,7 +7875,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="157" ht="14.25" customHeight="1">
+    <row r="157" spans="1:11" ht="14.25" customHeight="1">
       <c r="A157" t="s">
         <v>429</v>
       </c>
@@ -7882,10 +7898,10 @@
         <v>431</v>
       </c>
       <c r="H157">
-        <v>-1.206024726E9</v>
+        <v>-1206024726</v>
       </c>
       <c r="I157">
-        <v>-7.708256338E9</v>
+        <v>-7708256338</v>
       </c>
       <c r="J157" t="s">
         <v>18</v>
@@ -7894,7 +7910,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="158" ht="14.25" customHeight="1">
+    <row r="158" spans="1:11" ht="14.25" customHeight="1">
       <c r="A158" t="s">
         <v>25</v>
       </c>
@@ -7917,10 +7933,10 @@
         <v>432</v>
       </c>
       <c r="H158">
-        <v>-1.2058012E7</v>
+        <v>-12058012</v>
       </c>
       <c r="I158">
-        <v>-7.7079983E7</v>
+        <v>-77079983</v>
       </c>
       <c r="J158" t="s">
         <v>18</v>
@@ -7929,7 +7945,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="159" ht="14.25" customHeight="1">
+    <row r="159" spans="1:11" ht="14.25" customHeight="1">
       <c r="A159" t="s">
         <v>433</v>
       </c>
@@ -7952,10 +7968,10 @@
         <v>434</v>
       </c>
       <c r="H159">
-        <v>-1.2059274E7</v>
+        <v>-12059274</v>
       </c>
       <c r="I159">
-        <v>-770808.0</v>
+        <v>-770808</v>
       </c>
       <c r="J159" t="s">
         <v>18</v>
@@ -7964,7 +7980,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="160" ht="14.25" customHeight="1">
+    <row r="160" spans="1:11" ht="14.25" customHeight="1">
       <c r="A160" t="s">
         <v>435</v>
       </c>
@@ -7987,10 +8003,10 @@
         <v>438</v>
       </c>
       <c r="H160">
-        <v>-1.20604022E8</v>
+        <v>-120604022</v>
       </c>
       <c r="I160">
-        <v>-7.70818246E8</v>
+        <v>-770818246</v>
       </c>
       <c r="J160" t="s">
         <v>18</v>
@@ -7999,7 +8015,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="161" ht="14.25" customHeight="1">
+    <row r="161" spans="1:11" ht="14.25" customHeight="1">
       <c r="A161" t="s">
         <v>439</v>
       </c>
@@ -8022,10 +8038,10 @@
         <v>441</v>
       </c>
       <c r="H161">
-        <v>-1.2059274E7</v>
+        <v>-12059274</v>
       </c>
       <c r="I161">
-        <v>-770808.0</v>
+        <v>-770808</v>
       </c>
       <c r="J161" t="s">
         <v>18</v>
@@ -8034,7 +8050,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="162" ht="14.25" customHeight="1">
+    <row r="162" spans="1:11" ht="14.25" customHeight="1">
       <c r="A162" t="s">
         <v>442</v>
       </c>
@@ -8057,10 +8073,10 @@
         <v>444</v>
       </c>
       <c r="H162">
-        <v>-1.2054079E7</v>
+        <v>-12054079</v>
       </c>
       <c r="I162">
-        <v>-7.7085772E7</v>
+        <v>-77085772</v>
       </c>
       <c r="J162" t="s">
         <v>62</v>
@@ -8069,7 +8085,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="163" ht="14.25" customHeight="1">
+    <row r="163" spans="1:11" ht="14.25" customHeight="1">
       <c r="A163" t="s">
         <v>445</v>
       </c>
@@ -8092,10 +8108,10 @@
         <v>448</v>
       </c>
       <c r="H163">
-        <v>-1.2060315E7</v>
+        <v>-12060315</v>
       </c>
       <c r="I163">
-        <v>-7.7084368E7</v>
+        <v>-77084368</v>
       </c>
       <c r="J163" t="s">
         <v>62</v>
@@ -8104,7 +8120,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="164" ht="14.25" customHeight="1">
+    <row r="164" spans="1:11" ht="14.25" customHeight="1">
       <c r="A164" t="s">
         <v>53</v>
       </c>
@@ -8127,10 +8143,10 @@
         <v>450</v>
       </c>
       <c r="H164">
-        <v>-1.2058378E7</v>
+        <v>-12058378</v>
       </c>
       <c r="I164">
-        <v>-7.7080139E7</v>
+        <v>-77080139</v>
       </c>
       <c r="J164" t="s">
         <v>18</v>
@@ -8139,7 +8155,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="165" ht="14.25" customHeight="1">
+    <row r="165" spans="1:11" ht="14.25" customHeight="1">
       <c r="A165" t="s">
         <v>344</v>
       </c>
@@ -8162,10 +8178,10 @@
         <v>451</v>
       </c>
       <c r="H165">
-        <v>-1.20565319E8</v>
+        <v>-120565319</v>
       </c>
       <c r="I165">
-        <v>-7.70820465E8</v>
+        <v>-770820465</v>
       </c>
       <c r="J165" t="s">
         <v>18</v>
@@ -8174,7 +8190,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="166" ht="14.25" customHeight="1">
+    <row r="166" spans="1:11" ht="14.25" customHeight="1">
       <c r="A166" t="s">
         <v>452</v>
       </c>
@@ -8197,10 +8213,10 @@
         <v>455</v>
       </c>
       <c r="H166">
-        <v>-1.2059218E7</v>
+        <v>-12059218</v>
       </c>
       <c r="I166">
-        <v>-7.7079587E7</v>
+        <v>-77079587</v>
       </c>
       <c r="J166" t="s">
         <v>18</v>
@@ -8209,7 +8225,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="167" ht="14.25" customHeight="1">
+    <row r="167" spans="1:11" ht="14.25" customHeight="1">
       <c r="A167" t="s">
         <v>456</v>
       </c>
@@ -8232,10 +8248,10 @@
         <v>457</v>
       </c>
       <c r="H167">
-        <v>-1.2058299E7</v>
+        <v>-12058299</v>
       </c>
       <c r="I167">
-        <v>-7.7080642E7</v>
+        <v>-77080642</v>
       </c>
       <c r="J167" t="s">
         <v>18</v>
@@ -8244,7 +8260,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="168" ht="14.25" customHeight="1">
+    <row r="168" spans="1:11" ht="14.25" customHeight="1">
       <c r="A168" t="s">
         <v>151</v>
       </c>
@@ -8267,10 +8283,10 @@
         <v>460</v>
       </c>
       <c r="H168">
-        <v>-1.2053404E7</v>
+        <v>-12053404</v>
       </c>
       <c r="I168">
-        <v>-7.7087545E7</v>
+        <v>-77087545</v>
       </c>
       <c r="J168" t="s">
         <v>18</v>
@@ -8279,7 +8295,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="169" ht="14.25" customHeight="1">
+    <row r="169" spans="1:11" ht="14.25" customHeight="1">
       <c r="A169" t="s">
         <v>23</v>
       </c>
@@ -8302,10 +8318,10 @@
         <v>462</v>
       </c>
       <c r="H169">
-        <v>-1.20545941E8</v>
+        <v>-120545941</v>
       </c>
       <c r="I169">
-        <v>-7.70850302E8</v>
+        <v>-770850302</v>
       </c>
       <c r="J169" t="s">
         <v>18</v>
@@ -8314,7 +8330,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="170" ht="14.25" customHeight="1">
+    <row r="170" spans="1:11" ht="14.25" customHeight="1">
       <c r="A170" t="s">
         <v>463</v>
       </c>
@@ -8337,10 +8353,10 @@
         <v>465</v>
       </c>
       <c r="H170">
-        <v>-1.2056773E7</v>
+        <v>-12056773</v>
       </c>
       <c r="I170">
-        <v>-7.7086538E7</v>
+        <v>-77086538</v>
       </c>
       <c r="J170" t="s">
         <v>62</v>
@@ -8349,7 +8365,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="171" ht="14.25" customHeight="1">
+    <row r="171" spans="1:11" ht="14.25" customHeight="1">
       <c r="A171" t="s">
         <v>466</v>
       </c>
@@ -8372,10 +8388,10 @@
         <v>468</v>
       </c>
       <c r="H171">
-        <v>-1.205790019E9</v>
+        <v>-1205790019</v>
       </c>
       <c r="I171">
-        <v>-7.708584828E9</v>
+        <v>-7708584828</v>
       </c>
       <c r="J171" t="s">
         <v>18</v>
@@ -8384,7 +8400,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="172" ht="14.25" customHeight="1">
+    <row r="172" spans="1:11" ht="14.25" customHeight="1">
       <c r="A172" t="s">
         <v>137</v>
       </c>
@@ -8407,10 +8423,10 @@
         <v>471</v>
       </c>
       <c r="H172">
-        <v>-1.2056269E7</v>
+        <v>-12056269</v>
       </c>
       <c r="I172">
-        <v>-7.7081025E7</v>
+        <v>-77081025</v>
       </c>
       <c r="J172" t="s">
         <v>18</v>
@@ -8419,7 +8435,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="173" ht="14.25" customHeight="1">
+    <row r="173" spans="1:11" ht="14.25" customHeight="1">
       <c r="A173" t="s">
         <v>472</v>
       </c>
@@ -8442,10 +8458,10 @@
         <v>474</v>
       </c>
       <c r="H173">
-        <v>-1205623.0</v>
+        <v>-1205623</v>
       </c>
       <c r="I173">
-        <v>-7708746.0</v>
+        <v>-7708746</v>
       </c>
       <c r="J173" t="s">
         <v>62</v>
@@ -8454,7 +8470,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="174" ht="14.25" customHeight="1">
+    <row r="174" spans="1:11" ht="14.25" customHeight="1">
       <c r="A174" t="s">
         <v>475</v>
       </c>
@@ -8477,10 +8493,10 @@
         <v>477</v>
       </c>
       <c r="H174">
-        <v>-1.2060636E7</v>
+        <v>-12060636</v>
       </c>
       <c r="I174">
-        <v>-7.7082914E7</v>
+        <v>-77082914</v>
       </c>
       <c r="J174" t="s">
         <v>18</v>
@@ -8489,7 +8505,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="175" ht="14.25" customHeight="1">
+    <row r="175" spans="1:11" ht="14.25" customHeight="1">
       <c r="A175" t="s">
         <v>478</v>
       </c>
@@ -8512,10 +8528,10 @@
         <v>482</v>
       </c>
       <c r="H175" s="1">
-        <v>-1205513.0</v>
+        <v>-1205913</v>
       </c>
       <c r="I175">
-        <v>-7.7080643E7</v>
+        <v>-77080643</v>
       </c>
       <c r="J175" t="s">
         <v>18</v>
@@ -8524,7 +8540,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="176" ht="14.25" customHeight="1">
+    <row r="176" spans="1:11" ht="14.25" customHeight="1">
       <c r="A176" t="s">
         <v>53</v>
       </c>
@@ -8547,10 +8563,10 @@
         <v>483</v>
       </c>
       <c r="H176">
-        <v>-1.20583E7</v>
+        <v>-12058300</v>
       </c>
       <c r="I176">
-        <v>-7.7080643E7</v>
+        <v>-77080643</v>
       </c>
       <c r="J176" t="s">
         <v>18</v>
@@ -8559,7 +8575,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="177" ht="14.25" customHeight="1">
+    <row r="177" spans="1:11" ht="14.25" customHeight="1">
       <c r="A177" t="s">
         <v>25</v>
       </c>
@@ -8582,10 +8598,10 @@
         <v>484</v>
       </c>
       <c r="H177">
-        <v>-1.2058558E7</v>
+        <v>-12058558</v>
       </c>
       <c r="I177">
-        <v>-7.7079863E7</v>
+        <v>-77079863</v>
       </c>
       <c r="J177" t="s">
         <v>18</v>
@@ -8594,7 +8610,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="178" ht="14.25" customHeight="1">
+    <row r="178" spans="1:11" ht="14.25" customHeight="1">
       <c r="A178" t="s">
         <v>485</v>
       </c>
@@ -8617,10 +8633,10 @@
         <v>487</v>
       </c>
       <c r="H178">
-        <v>-1.205645147E9</v>
+        <v>-1205645147</v>
       </c>
       <c r="I178">
-        <v>-7.708684178E9</v>
+        <v>-7708684178</v>
       </c>
       <c r="J178" t="s">
         <v>18</v>
@@ -8629,7 +8645,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="179" ht="14.25" customHeight="1">
+    <row r="179" spans="1:11" ht="14.25" customHeight="1">
       <c r="A179" t="s">
         <v>25</v>
       </c>
@@ -8652,10 +8668,10 @@
         <v>489</v>
       </c>
       <c r="H179">
-        <v>-1.2058459E7</v>
+        <v>-12058459</v>
       </c>
       <c r="I179">
-        <v>-7.7079841E7</v>
+        <v>-77079841</v>
       </c>
       <c r="J179" t="s">
         <v>18</v>
@@ -8664,7 +8680,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="180" ht="14.25" customHeight="1">
+    <row r="180" spans="1:11" ht="14.25" customHeight="1">
       <c r="A180" t="s">
         <v>25</v>
       </c>
@@ -8687,10 +8703,10 @@
         <v>490</v>
       </c>
       <c r="H180">
-        <v>-1.2058576E7</v>
+        <v>-12058576</v>
       </c>
       <c r="I180">
-        <v>-7.7079769E7</v>
+        <v>-77079769</v>
       </c>
       <c r="J180" t="s">
         <v>18</v>
@@ -8699,7 +8715,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="181" ht="14.25" customHeight="1">
+    <row r="181" spans="1:11" ht="14.25" customHeight="1">
       <c r="A181" t="s">
         <v>491</v>
       </c>
@@ -8722,10 +8738,10 @@
         <v>493</v>
       </c>
       <c r="H181">
-        <v>-1.2060574E7</v>
+        <v>-12060574</v>
       </c>
       <c r="I181">
-        <v>-7.7082192E7</v>
+        <v>-77082192</v>
       </c>
       <c r="J181" t="s">
         <v>18</v>
@@ -8734,7 +8750,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="182" ht="14.25" customHeight="1">
+    <row r="182" spans="1:11" ht="14.25" customHeight="1">
       <c r="A182" t="s">
         <v>137</v>
       </c>
@@ -8757,10 +8773,10 @@
         <v>494</v>
       </c>
       <c r="H182">
-        <v>-1.2056327E7</v>
+        <v>-12056327</v>
       </c>
       <c r="I182">
-        <v>-7.7080965E7</v>
+        <v>-77080965</v>
       </c>
       <c r="J182" t="s">
         <v>18</v>
@@ -8769,7 +8785,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="183" ht="14.25" customHeight="1">
+    <row r="183" spans="1:11" ht="14.25" customHeight="1">
       <c r="A183" t="s">
         <v>53</v>
       </c>
@@ -8792,10 +8808,10 @@
         <v>495</v>
       </c>
       <c r="H183">
-        <v>-1.2058444E7</v>
+        <v>-12058444</v>
       </c>
       <c r="I183">
-        <v>-7.7080372E7</v>
+        <v>-77080372</v>
       </c>
       <c r="J183" t="s">
         <v>18</v>
@@ -8804,7 +8820,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="184" ht="14.25" customHeight="1">
+    <row r="184" spans="1:11" ht="14.25" customHeight="1">
       <c r="A184" t="s">
         <v>496</v>
       </c>
@@ -8827,10 +8843,10 @@
         <v>502</v>
       </c>
       <c r="H184">
-        <v>-1.205712839E9</v>
+        <v>-1205712839</v>
       </c>
       <c r="I184">
-        <v>-7.708622389E9</v>
+        <v>-7708622389</v>
       </c>
       <c r="J184" t="s">
         <v>62</v>
@@ -8839,7 +8855,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="185" ht="14.25" customHeight="1">
+    <row r="185" spans="1:11" ht="14.25" customHeight="1">
       <c r="A185" t="s">
         <v>503</v>
       </c>
@@ -8862,10 +8878,10 @@
         <v>504</v>
       </c>
       <c r="H185">
-        <v>-1.2059339E7</v>
+        <v>-12059339</v>
       </c>
       <c r="I185">
-        <v>-7.7087202E7</v>
+        <v>-77087202</v>
       </c>
       <c r="J185" t="s">
         <v>62</v>
@@ -8874,7 +8890,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="186" ht="14.25" customHeight="1">
+    <row r="186" spans="1:11" ht="14.25" customHeight="1">
       <c r="A186" t="s">
         <v>53</v>
       </c>
@@ -8897,10 +8913,10 @@
         <v>508</v>
       </c>
       <c r="H186">
-        <v>-1.2058254E7</v>
+        <v>-12058254</v>
       </c>
       <c r="I186">
-        <v>-7.7080432E7</v>
+        <v>-77080432</v>
       </c>
       <c r="J186" t="s">
         <v>18</v>
@@ -8909,7 +8925,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="187" ht="14.25" customHeight="1">
+    <row r="187" spans="1:11" ht="14.25" customHeight="1">
       <c r="A187" t="s">
         <v>53</v>
       </c>
@@ -8932,10 +8948,10 @@
         <v>509</v>
       </c>
       <c r="H187">
-        <v>-1.2058552E7</v>
+        <v>-12058552</v>
       </c>
       <c r="I187">
-        <v>-7.708092E7</v>
+        <v>-77080920</v>
       </c>
       <c r="J187" t="s">
         <v>18</v>
@@ -8944,7 +8960,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="188" ht="14.25" customHeight="1">
+    <row r="188" spans="1:11" ht="14.25" customHeight="1">
       <c r="A188" t="s">
         <v>510</v>
       </c>
@@ -8967,10 +8983,10 @@
         <v>512</v>
       </c>
       <c r="H188">
-        <v>-1.2058944E7</v>
+        <v>-12058944</v>
       </c>
       <c r="I188">
-        <v>-7.7079397E7</v>
+        <v>-77079767</v>
       </c>
       <c r="J188" t="s">
         <v>18</v>
@@ -8979,7 +8995,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="189" ht="14.25" customHeight="1">
+    <row r="189" spans="1:11" ht="14.25" customHeight="1">
       <c r="A189" t="s">
         <v>513</v>
       </c>
@@ -9002,10 +9018,10 @@
         <v>514</v>
       </c>
       <c r="H189">
-        <v>-1.2054729E7</v>
+        <v>-12054729</v>
       </c>
       <c r="I189">
-        <v>-7.7085504E7</v>
+        <v>-77085504</v>
       </c>
       <c r="J189" t="s">
         <v>18</v>
@@ -9014,7 +9030,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="190" ht="14.25" customHeight="1">
+    <row r="190" spans="1:11" ht="14.25" customHeight="1">
       <c r="A190" t="s">
         <v>515</v>
       </c>
@@ -9037,10 +9053,10 @@
         <v>516</v>
       </c>
       <c r="H190">
-        <v>-1.20596026E8</v>
+        <v>-120596026</v>
       </c>
       <c r="I190">
-        <v>-7.708201627E9</v>
+        <v>-7708201627</v>
       </c>
       <c r="J190" t="s">
         <v>18</v>
@@ -9049,7 +9065,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="191" ht="14.25" customHeight="1">
+    <row r="191" spans="1:11" ht="14.25" customHeight="1">
       <c r="A191" t="s">
         <v>25</v>
       </c>
@@ -9072,10 +9088,10 @@
         <v>518</v>
       </c>
       <c r="H191">
-        <v>-1.2058446E7</v>
+        <v>-12058446</v>
       </c>
       <c r="I191">
-        <v>-7.7079712E7</v>
+        <v>-77079712</v>
       </c>
       <c r="J191" t="s">
         <v>62</v>
@@ -9084,7 +9100,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="192" ht="14.25" customHeight="1">
+    <row r="192" spans="1:11" ht="14.25" customHeight="1">
       <c r="A192" t="s">
         <v>519</v>
       </c>
@@ -9107,10 +9123,10 @@
         <v>522</v>
       </c>
       <c r="H192">
-        <v>-1.2053929E7</v>
+        <v>-12053929</v>
       </c>
       <c r="I192">
-        <v>-7.7086401E7</v>
+        <v>-77086401</v>
       </c>
       <c r="J192" t="s">
         <v>18</v>
@@ -9119,7 +9135,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="193" ht="14.25" customHeight="1">
+    <row r="193" spans="1:11" ht="14.25" customHeight="1">
       <c r="A193" t="s">
         <v>523</v>
       </c>
@@ -9142,10 +9158,10 @@
         <v>525</v>
       </c>
       <c r="H193">
-        <v>-1.2059411E7</v>
+        <v>-12059411</v>
       </c>
       <c r="I193">
-        <v>-7.7080058E7</v>
+        <v>-77080058</v>
       </c>
       <c r="J193" t="s">
         <v>18</v>
@@ -9154,7 +9170,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="194" ht="14.25" customHeight="1">
+    <row r="194" spans="1:11" ht="14.25" customHeight="1">
       <c r="A194" t="s">
         <v>526</v>
       </c>
@@ -9177,10 +9193,10 @@
         <v>525</v>
       </c>
       <c r="H194">
-        <v>-1.2060887E7</v>
+        <v>-12060887</v>
       </c>
       <c r="I194">
-        <v>-7.7084615E7</v>
+        <v>-77084615</v>
       </c>
       <c r="J194" t="s">
         <v>18</v>
@@ -9189,7 +9205,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="195" ht="14.25" customHeight="1">
+    <row r="195" spans="1:11" ht="14.25" customHeight="1">
       <c r="A195" t="s">
         <v>53</v>
       </c>
@@ -9212,10 +9228,10 @@
         <v>527</v>
       </c>
       <c r="H195">
-        <v>-1.20583E7</v>
+        <v>-12058300</v>
       </c>
       <c r="I195">
-        <v>-7.7080643E7</v>
+        <v>-77080643</v>
       </c>
       <c r="J195" t="s">
         <v>18</v>
@@ -9224,7 +9240,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="196" ht="14.25" customHeight="1">
+    <row r="196" spans="1:11" ht="14.25" customHeight="1">
       <c r="A196" t="s">
         <v>528</v>
       </c>
@@ -9247,10 +9263,10 @@
         <v>532</v>
       </c>
       <c r="H196">
-        <v>-1.2056669E7</v>
+        <v>-12056669</v>
       </c>
       <c r="I196">
-        <v>-7.7085002E7</v>
+        <v>-77085002</v>
       </c>
       <c r="J196" t="s">
         <v>18</v>
@@ -9259,7 +9275,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="197" ht="14.25" customHeight="1">
+    <row r="197" spans="1:11" ht="14.25" customHeight="1">
       <c r="A197" t="s">
         <v>533</v>
       </c>
@@ -9282,10 +9298,10 @@
         <v>536</v>
       </c>
       <c r="H197">
-        <v>-1.2057323E7</v>
+        <v>-12057323</v>
       </c>
       <c r="I197">
-        <v>-7.7085923E7</v>
+        <v>-77085923</v>
       </c>
       <c r="J197" t="s">
         <v>18</v>
@@ -9294,7 +9310,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="198" ht="14.25" customHeight="1">
+    <row r="198" spans="1:11" ht="14.25" customHeight="1">
       <c r="A198" t="s">
         <v>53</v>
       </c>
@@ -9317,10 +9333,10 @@
         <v>537</v>
       </c>
       <c r="H198">
-        <v>-1.2058444E7</v>
+        <v>-12058444</v>
       </c>
       <c r="I198">
-        <v>-7.7080372E7</v>
+        <v>-77080372</v>
       </c>
       <c r="J198" t="s">
         <v>18</v>
@@ -9329,7 +9345,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="199" ht="14.25" customHeight="1">
+    <row r="199" spans="1:11" ht="14.25" customHeight="1">
       <c r="A199" t="s">
         <v>53</v>
       </c>
@@ -9352,10 +9368,10 @@
         <v>538</v>
       </c>
       <c r="H199">
-        <v>-1.2058378E7</v>
+        <v>-12058378</v>
       </c>
       <c r="I199">
-        <v>-7.7080139E7</v>
+        <v>-77080139</v>
       </c>
       <c r="J199" t="s">
         <v>18</v>
@@ -9364,7 +9380,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="200" ht="14.25" customHeight="1">
+    <row r="200" spans="1:11" ht="14.25" customHeight="1">
       <c r="A200" t="s">
         <v>539</v>
       </c>
@@ -9387,10 +9403,10 @@
         <v>541</v>
       </c>
       <c r="H200">
-        <v>-1.20573215E8</v>
+        <v>-120573215</v>
       </c>
       <c r="I200">
-        <v>-7.708623939E9</v>
+        <v>-7708623939</v>
       </c>
       <c r="J200" t="s">
         <v>18</v>
@@ -9399,7 +9415,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="201" ht="14.25" customHeight="1">
+    <row r="201" spans="1:11" ht="14.25" customHeight="1">
       <c r="A201" t="s">
         <v>25</v>
       </c>
@@ -9422,10 +9438,10 @@
         <v>543</v>
       </c>
       <c r="H201">
-        <v>-1.2058555E7</v>
+        <v>-12058555</v>
       </c>
       <c r="I201">
-        <v>-7.7079716E7</v>
+        <v>-77079716</v>
       </c>
       <c r="J201" t="s">
         <v>18</v>
@@ -9434,7 +9450,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="202" ht="14.25" customHeight="1">
+    <row r="202" spans="1:11" ht="14.25" customHeight="1">
       <c r="A202" t="s">
         <v>544</v>
       </c>
@@ -9457,10 +9473,10 @@
         <v>546</v>
       </c>
       <c r="H202">
-        <v>-1.2060606E7</v>
+        <v>-12060606</v>
       </c>
       <c r="I202">
-        <v>-7.7082258E7</v>
+        <v>-77082258</v>
       </c>
       <c r="J202" t="s">
         <v>18</v>
@@ -9469,7 +9485,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="203" ht="14.25" customHeight="1">
+    <row r="203" spans="1:11" ht="14.25" customHeight="1">
       <c r="A203" t="s">
         <v>53</v>
       </c>
@@ -9492,10 +9508,10 @@
         <v>549</v>
       </c>
       <c r="H203">
-        <v>-1.2058455E7</v>
+        <v>-12058455</v>
       </c>
       <c r="I203">
-        <v>-7.7080218E7</v>
+        <v>-77080218</v>
       </c>
       <c r="J203" t="s">
         <v>18</v>
@@ -9504,7 +9520,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="204" ht="14.25" customHeight="1">
+    <row r="204" spans="1:11" ht="14.25" customHeight="1">
       <c r="A204" t="s">
         <v>550</v>
       </c>
@@ -9527,10 +9543,10 @@
         <v>554</v>
       </c>
       <c r="H204">
-        <v>-1.2053551E7</v>
-      </c>
-      <c r="I204" s="2">
-        <v>-7.7084238E7</v>
+        <v>-12053551</v>
+      </c>
+      <c r="I204" s="1">
+        <v>-77084238</v>
       </c>
       <c r="J204" t="s">
         <v>62</v>
@@ -9539,7 +9555,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="205" ht="14.25" customHeight="1">
+    <row r="205" spans="1:11" ht="14.25" customHeight="1">
       <c r="A205" t="s">
         <v>555</v>
       </c>
@@ -9562,10 +9578,10 @@
         <v>557</v>
       </c>
       <c r="H205">
-        <v>-1.2053551E7</v>
+        <v>-12053551</v>
       </c>
       <c r="I205">
-        <v>-7.7086277E7</v>
+        <v>-77085277</v>
       </c>
       <c r="J205" t="s">
         <v>62</v>
@@ -9574,7 +9590,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="206" ht="14.25" customHeight="1">
+    <row r="206" spans="1:11" ht="14.25" customHeight="1">
       <c r="A206" t="s">
         <v>558</v>
       </c>
@@ -9597,10 +9613,10 @@
         <v>560</v>
       </c>
       <c r="H206">
-        <v>-1.2059274E7</v>
+        <v>-12059274</v>
       </c>
       <c r="I206">
-        <v>-770808.0</v>
+        <v>-770808</v>
       </c>
       <c r="J206" t="s">
         <v>62</v>
@@ -9609,7 +9625,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="207" ht="14.25" customHeight="1">
+    <row r="207" spans="1:11" ht="14.25" customHeight="1">
       <c r="A207" t="s">
         <v>561</v>
       </c>
@@ -9632,10 +9648,10 @@
         <v>564</v>
       </c>
       <c r="H207">
-        <v>-1.20602174E8</v>
+        <v>-120602174</v>
       </c>
       <c r="I207">
-        <v>-7.708176537E9</v>
+        <v>-7708176537</v>
       </c>
       <c r="J207" t="s">
         <v>18</v>
@@ -9644,7 +9660,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="208" ht="14.25" customHeight="1">
+    <row r="208" spans="1:11" ht="14.25" customHeight="1">
       <c r="A208" t="s">
         <v>565</v>
       </c>
@@ -9667,10 +9683,10 @@
         <v>567</v>
       </c>
       <c r="H208">
-        <v>-1.2057333E7</v>
+        <v>-12057333</v>
       </c>
       <c r="I208" s="1">
-        <v>-7.7085238E7</v>
+        <v>-77085238</v>
       </c>
       <c r="J208" t="s">
         <v>18</v>
@@ -9679,7 +9695,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="209" ht="14.25" customHeight="1">
+    <row r="209" spans="1:11" ht="14.25" customHeight="1">
       <c r="A209" t="s">
         <v>568</v>
       </c>
@@ -9702,10 +9718,10 @@
         <v>570</v>
       </c>
       <c r="H209">
-        <v>-1.2057333E7</v>
+        <v>-12057333</v>
       </c>
       <c r="I209">
-        <v>-7.7085928E7</v>
+        <v>-77085928</v>
       </c>
       <c r="J209" t="s">
         <v>18</v>
@@ -9714,7 +9730,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="210" ht="14.25" customHeight="1">
+    <row r="210" spans="1:11" ht="14.25" customHeight="1">
       <c r="A210" t="s">
         <v>25</v>
       </c>
@@ -9737,10 +9753,10 @@
         <v>571</v>
       </c>
       <c r="H210">
-        <v>-1.2057968E7</v>
+        <v>-12057968</v>
       </c>
       <c r="I210">
-        <v>-7.7079862E7</v>
+        <v>-77079862</v>
       </c>
       <c r="J210" t="s">
         <v>18</v>
@@ -9749,7 +9765,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="211" ht="14.25" customHeight="1">
+    <row r="211" spans="1:11" ht="14.25" customHeight="1">
       <c r="A211" t="s">
         <v>572</v>
       </c>
@@ -9772,10 +9788,10 @@
         <v>573</v>
       </c>
       <c r="H211">
-        <v>-1.2059106E7</v>
+        <v>-12059106</v>
       </c>
       <c r="I211">
-        <v>-7.7079643E7</v>
+        <v>-77079643</v>
       </c>
       <c r="J211" t="s">
         <v>18</v>
@@ -9784,7 +9800,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="212" ht="14.25" customHeight="1">
+    <row r="212" spans="1:11" ht="14.25" customHeight="1">
       <c r="A212" t="s">
         <v>574</v>
       </c>
@@ -9807,10 +9823,10 @@
         <v>575</v>
       </c>
       <c r="H212">
-        <v>-1.2059106E7</v>
+        <v>-12059106</v>
       </c>
       <c r="I212">
-        <v>-7.7079643E7</v>
+        <v>-77079643</v>
       </c>
       <c r="J212" t="s">
         <v>18</v>
@@ -9819,7 +9835,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="213" ht="14.25" customHeight="1">
+    <row r="213" spans="1:11" ht="14.25" customHeight="1">
       <c r="A213" t="s">
         <v>23</v>
       </c>
@@ -9842,10 +9858,10 @@
         <v>576</v>
       </c>
       <c r="H213">
-        <v>-1.20554125E8</v>
+        <v>-120554125</v>
       </c>
       <c r="I213">
-        <v>-7.70829659E8</v>
+        <v>-770829659</v>
       </c>
       <c r="J213" t="s">
         <v>18</v>
@@ -9854,7 +9870,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="214" ht="14.25" customHeight="1">
+    <row r="214" spans="1:11" ht="14.25" customHeight="1">
       <c r="A214" t="s">
         <v>577</v>
       </c>
@@ -9877,10 +9893,10 @@
         <v>578</v>
       </c>
       <c r="H214">
-        <v>-1.2054729E7</v>
+        <v>-12054729</v>
       </c>
       <c r="I214">
-        <v>-7.7085504E7</v>
+        <v>-77085504</v>
       </c>
       <c r="J214" t="s">
         <v>18</v>
@@ -9889,7 +9905,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="215" ht="14.25" customHeight="1">
+    <row r="215" spans="1:11" ht="14.25" customHeight="1">
       <c r="A215" t="s">
         <v>23</v>
       </c>
@@ -9912,10 +9928,10 @@
         <v>579</v>
       </c>
       <c r="H215">
-        <v>-1.20544912E8</v>
+        <v>-120544912</v>
       </c>
       <c r="I215">
-        <v>-7.70845148E8</v>
+        <v>-770845148</v>
       </c>
       <c r="J215" t="s">
         <v>18</v>
@@ -9924,7 +9940,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="216" ht="14.25" customHeight="1">
+    <row r="216" spans="1:11" ht="14.25" customHeight="1">
       <c r="A216" t="s">
         <v>137</v>
       </c>
@@ -9947,10 +9963,10 @@
         <v>580</v>
       </c>
       <c r="H216">
-        <v>-1.2056125E7</v>
+        <v>-12056125</v>
       </c>
       <c r="I216">
-        <v>-7.7081382E7</v>
+        <v>-77081382</v>
       </c>
       <c r="J216" t="s">
         <v>18</v>
@@ -9959,7 +9975,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="217" ht="14.25" customHeight="1">
+    <row r="217" spans="1:11" ht="14.25" customHeight="1">
       <c r="A217" t="s">
         <v>25</v>
       </c>
@@ -9982,10 +9998,10 @@
         <v>582</v>
       </c>
       <c r="H217">
-        <v>-1.2058414E7</v>
+        <v>-12058414</v>
       </c>
       <c r="I217">
-        <v>-7.7079889E7</v>
+        <v>-77079889</v>
       </c>
       <c r="J217" t="s">
         <v>18</v>
@@ -9994,7 +10010,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="218" ht="14.25" customHeight="1">
+    <row r="218" spans="1:11" ht="14.25" customHeight="1">
       <c r="A218" t="s">
         <v>38</v>
       </c>
@@ -10017,10 +10033,10 @@
         <v>584</v>
       </c>
       <c r="H218">
-        <v>-120567.0</v>
+        <v>-120567</v>
       </c>
       <c r="I218">
-        <v>-77082.0</v>
+        <v>-77082</v>
       </c>
       <c r="J218" t="s">
         <v>18</v>
@@ -10029,7 +10045,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="219" ht="14.25" customHeight="1">
+    <row r="219" spans="1:11" ht="14.25" customHeight="1">
       <c r="A219" t="s">
         <v>585</v>
       </c>
@@ -10052,10 +10068,10 @@
         <v>587</v>
       </c>
       <c r="H219">
-        <v>-1.2054804E7</v>
+        <v>-12054804</v>
       </c>
       <c r="I219">
-        <v>-7.7085347E7</v>
+        <v>-77085347</v>
       </c>
       <c r="J219" t="s">
         <v>18</v>
@@ -10064,7 +10080,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="220" ht="14.25" customHeight="1">
+    <row r="220" spans="1:11" ht="14.25" customHeight="1">
       <c r="A220" t="s">
         <v>588</v>
       </c>
@@ -10087,10 +10103,10 @@
         <v>591</v>
       </c>
       <c r="H220">
-        <v>-1.205955986E9</v>
+        <v>-1205955986</v>
       </c>
       <c r="I220">
-        <v>-7.708088826E9</v>
+        <v>-7708088826</v>
       </c>
       <c r="J220" t="s">
         <v>18</v>
@@ -10099,7 +10115,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="221" ht="14.25" customHeight="1">
+    <row r="221" spans="1:11" ht="14.25" customHeight="1">
       <c r="A221" t="s">
         <v>137</v>
       </c>
@@ -10122,10 +10138,10 @@
         <v>593</v>
       </c>
       <c r="H221">
-        <v>-1.2056545E7</v>
+        <v>-12056545</v>
       </c>
       <c r="I221">
-        <v>-7708216.0</v>
+        <v>-7708216</v>
       </c>
       <c r="J221" t="s">
         <v>18</v>
@@ -10134,7 +10150,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="222" ht="14.25" customHeight="1">
+    <row r="222" spans="1:11" ht="14.25" customHeight="1">
       <c r="A222" t="s">
         <v>38</v>
       </c>
@@ -10157,10 +10173,10 @@
         <v>594</v>
       </c>
       <c r="H222">
-        <v>-1.205697598E9</v>
+        <v>-1205697598</v>
       </c>
       <c r="I222">
-        <v>-7.708196071E9</v>
+        <v>-7708196071</v>
       </c>
       <c r="J222" t="s">
         <v>18</v>
@@ -10169,7 +10185,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="223" ht="14.25" customHeight="1">
+    <row r="223" spans="1:11" ht="14.25" customHeight="1">
       <c r="A223" t="s">
         <v>25</v>
       </c>
@@ -10192,10 +10208,10 @@
         <v>596</v>
       </c>
       <c r="H223">
-        <v>-1.2058534E7</v>
+        <v>-12058534</v>
       </c>
       <c r="I223">
-        <v>-7.7079864E7</v>
+        <v>-77079864</v>
       </c>
       <c r="J223" t="s">
         <v>62</v>
@@ -10204,7 +10220,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="224" ht="14.25" customHeight="1">
+    <row r="224" spans="1:11" ht="14.25" customHeight="1">
       <c r="A224" t="s">
         <v>25</v>
       </c>
@@ -10227,10 +10243,10 @@
         <v>597</v>
       </c>
       <c r="H224">
-        <v>-1.2057977E7</v>
+        <v>-12057977</v>
       </c>
       <c r="I224">
-        <v>-7.7079822E7</v>
+        <v>-77079822</v>
       </c>
       <c r="J224" t="s">
         <v>18</v>
@@ -10239,7 +10255,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="225" ht="14.25" customHeight="1">
+    <row r="225" spans="1:11" ht="14.25" customHeight="1">
       <c r="A225" t="s">
         <v>53</v>
       </c>
@@ -10262,10 +10278,10 @@
         <v>599</v>
       </c>
       <c r="H225">
-        <v>-1.2058599E7</v>
+        <v>-12058599</v>
       </c>
       <c r="I225">
-        <v>-7.7081083E7</v>
+        <v>-77081083</v>
       </c>
       <c r="J225" t="s">
         <v>18</v>
@@ -10274,7 +10290,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="226" ht="14.25" customHeight="1">
+    <row r="226" spans="1:11" ht="14.25" customHeight="1">
       <c r="A226" t="s">
         <v>25</v>
       </c>
@@ -10297,10 +10313,10 @@
         <v>601</v>
       </c>
       <c r="H226">
-        <v>-1.2058558E7</v>
+        <v>-12058558</v>
       </c>
       <c r="I226">
-        <v>-7.7079863E7</v>
+        <v>-77079863</v>
       </c>
       <c r="J226" t="s">
         <v>18</v>
@@ -10309,7 +10325,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="227" ht="14.25" customHeight="1">
+    <row r="227" spans="1:11" ht="14.25" customHeight="1">
       <c r="A227" t="s">
         <v>25</v>
       </c>
@@ -10332,10 +10348,10 @@
         <v>602</v>
       </c>
       <c r="H227">
-        <v>-1.2058558E7</v>
+        <v>-12058558</v>
       </c>
       <c r="I227">
-        <v>-7.7079863E7</v>
+        <v>-77079863</v>
       </c>
       <c r="J227" t="s">
         <v>18</v>
@@ -10344,7 +10360,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="228" ht="14.25" customHeight="1">
+    <row r="228" spans="1:11" ht="14.25" customHeight="1">
       <c r="A228" t="s">
         <v>25</v>
       </c>
@@ -10367,10 +10383,10 @@
         <v>604</v>
       </c>
       <c r="H228">
-        <v>-1.2058396E7</v>
+        <v>-12058396</v>
       </c>
       <c r="I228">
-        <v>-7.7079838E7</v>
+        <v>-77079838</v>
       </c>
       <c r="J228" t="s">
         <v>18</v>
@@ -10379,7 +10395,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="229" ht="14.25" customHeight="1">
+    <row r="229" spans="1:11" ht="14.25" customHeight="1">
       <c r="A229" t="s">
         <v>25</v>
       </c>
@@ -10402,10 +10418,10 @@
         <v>605</v>
       </c>
       <c r="H229">
-        <v>-1.2058487E7</v>
+        <v>-12058487</v>
       </c>
       <c r="I229">
-        <v>-7.7079881E7</v>
+        <v>-77079881</v>
       </c>
       <c r="J229" t="s">
         <v>18</v>
@@ -10414,7 +10430,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="230" ht="14.25" customHeight="1">
+    <row r="230" spans="1:11" ht="14.25" customHeight="1">
       <c r="A230" t="s">
         <v>11</v>
       </c>
@@ -10437,10 +10453,10 @@
         <v>607</v>
       </c>
       <c r="H230">
-        <v>-1.2054099E7</v>
+        <v>-12054099</v>
       </c>
       <c r="I230">
-        <v>-7.7085121E7</v>
+        <v>-77085121</v>
       </c>
       <c r="J230" t="s">
         <v>18</v>
@@ -10449,7 +10465,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="231" ht="14.25" customHeight="1">
+    <row r="231" spans="1:11" ht="14.25" customHeight="1">
       <c r="A231" t="s">
         <v>608</v>
       </c>
@@ -10472,10 +10488,10 @@
         <v>610</v>
       </c>
       <c r="H231">
-        <v>-1.2059066E7</v>
+        <v>-12059066</v>
       </c>
       <c r="I231">
-        <v>-7.7079712E7</v>
+        <v>-77079712</v>
       </c>
       <c r="J231" t="s">
         <v>18</v>
@@ -10484,7 +10500,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="232" ht="14.25" customHeight="1">
+    <row r="232" spans="1:11" ht="14.25" customHeight="1">
       <c r="A232" t="s">
         <v>25</v>
       </c>
@@ -10507,10 +10523,10 @@
         <v>611</v>
       </c>
       <c r="H232">
-        <v>-1.2058446E7</v>
+        <v>-12058446</v>
       </c>
       <c r="I232">
-        <v>-7.7079712E7</v>
+        <v>-77079712</v>
       </c>
       <c r="J232" t="s">
         <v>18</v>
@@ -10519,7 +10535,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="233" ht="14.25" customHeight="1">
+    <row r="233" spans="1:11" ht="14.25" customHeight="1">
       <c r="A233" t="s">
         <v>53</v>
       </c>
@@ -10542,10 +10558,10 @@
         <v>612</v>
       </c>
       <c r="H233">
-        <v>-1.2058378E7</v>
+        <v>-12058378</v>
       </c>
       <c r="I233">
-        <v>-7.7080139E7</v>
+        <v>-77080139</v>
       </c>
       <c r="J233" t="s">
         <v>18</v>
@@ -10554,7 +10570,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="234" ht="14.25" customHeight="1">
+    <row r="234" spans="1:11" ht="14.25" customHeight="1">
       <c r="A234" t="s">
         <v>218</v>
       </c>
@@ -10577,10 +10593,10 @@
         <v>615</v>
       </c>
       <c r="H234">
-        <v>-1.2057683E7</v>
+        <v>-12057683</v>
       </c>
       <c r="I234">
-        <v>-7.7081691E7</v>
+        <v>-77081691</v>
       </c>
       <c r="J234" t="s">
         <v>18</v>
@@ -10589,7 +10605,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="235" ht="14.25" customHeight="1">
+    <row r="235" spans="1:11" ht="14.25" customHeight="1">
       <c r="A235" t="s">
         <v>616</v>
       </c>
@@ -10612,10 +10628,10 @@
         <v>617</v>
       </c>
       <c r="H235">
-        <v>-1.205956104E9</v>
+        <v>-1205956104</v>
       </c>
       <c r="I235">
-        <v>-7.708225469E9</v>
+        <v>-7708225469</v>
       </c>
       <c r="J235" t="s">
         <v>18</v>
@@ -10624,7 +10640,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="236" ht="14.25" customHeight="1">
+    <row r="236" spans="1:11" ht="14.25" customHeight="1">
       <c r="A236" t="s">
         <v>618</v>
       </c>
@@ -10647,10 +10663,10 @@
         <v>620</v>
       </c>
       <c r="H236">
-        <v>-1.2060321E7</v>
+        <v>-12060321</v>
       </c>
       <c r="I236">
-        <v>-7.7082444E7</v>
+        <v>-77082444</v>
       </c>
       <c r="J236" t="s">
         <v>18</v>
@@ -10659,7 +10675,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="237" ht="14.25" customHeight="1">
+    <row r="237" spans="1:11" ht="14.25" customHeight="1">
       <c r="A237" t="s">
         <v>621</v>
       </c>
@@ -10682,10 +10698,10 @@
         <v>623</v>
       </c>
       <c r="H237">
-        <v>-1.2060478E7</v>
+        <v>-12060478</v>
       </c>
       <c r="I237">
-        <v>-7.7081862E7</v>
+        <v>-77081862</v>
       </c>
       <c r="J237" t="s">
         <v>18</v>
@@ -10694,7 +10710,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="238" ht="14.25" customHeight="1">
+    <row r="238" spans="1:11" ht="14.25" customHeight="1">
       <c r="A238" t="s">
         <v>624</v>
       </c>
@@ -10717,10 +10733,10 @@
         <v>626</v>
       </c>
       <c r="H238">
-        <v>-1.2057692E7</v>
+        <v>-12057692</v>
       </c>
       <c r="I238">
-        <v>-7.7079914E7</v>
+        <v>-77079914</v>
       </c>
       <c r="J238" t="s">
         <v>18</v>
@@ -10729,7 +10745,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="239" ht="14.25" customHeight="1">
+    <row r="239" spans="1:11" ht="14.25" customHeight="1">
       <c r="A239" t="s">
         <v>627</v>
       </c>
@@ -10752,10 +10768,10 @@
         <v>628</v>
       </c>
       <c r="H239">
-        <v>-1.2055621E7</v>
+        <v>-12055621</v>
       </c>
       <c r="I239">
-        <v>-7.7087168E7</v>
+        <v>-77087168</v>
       </c>
       <c r="J239" t="s">
         <v>18</v>
@@ -10764,7 +10780,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="240" ht="14.25" customHeight="1">
+    <row r="240" spans="1:11" ht="14.25" customHeight="1">
       <c r="A240" t="s">
         <v>629</v>
       </c>
@@ -10787,10 +10803,10 @@
         <v>631</v>
       </c>
       <c r="H240">
-        <v>-1.20598789E8</v>
+        <v>-120598789</v>
       </c>
       <c r="I240">
-        <v>-7.70812378E8</v>
+        <v>-770812378</v>
       </c>
       <c r="J240" t="s">
         <v>62</v>
@@ -10799,7 +10815,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="241" ht="14.25" customHeight="1">
+    <row r="241" spans="1:11" ht="14.25" customHeight="1">
       <c r="A241" t="s">
         <v>632</v>
       </c>
@@ -10822,10 +10838,10 @@
         <v>634</v>
       </c>
       <c r="H241">
-        <v>-1.205794058E9</v>
+        <v>-1205794058</v>
       </c>
       <c r="I241">
-        <v>-7.708585978E9</v>
+        <v>-7708585978</v>
       </c>
       <c r="J241" t="s">
         <v>62</v>
@@ -10834,7 +10850,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="242" ht="14.25" customHeight="1">
+    <row r="242" spans="1:11" ht="14.25" customHeight="1">
       <c r="A242" t="s">
         <v>635</v>
       </c>
@@ -10857,10 +10873,10 @@
         <v>637</v>
       </c>
       <c r="H242">
-        <v>-1.2054079E7</v>
+        <v>-12054079</v>
       </c>
       <c r="I242">
-        <v>-7.7085772E7</v>
+        <v>-77085772</v>
       </c>
       <c r="J242" t="s">
         <v>62</v>
@@ -10869,7 +10885,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="243" ht="14.25" customHeight="1">
+    <row r="243" spans="1:11" ht="14.25" customHeight="1">
       <c r="A243" t="s">
         <v>638</v>
       </c>
@@ -10892,10 +10908,10 @@
         <v>640</v>
       </c>
       <c r="H243">
-        <v>-1205486.0</v>
+        <v>-1205486</v>
       </c>
       <c r="I243">
-        <v>-7.7085772E7</v>
+        <v>-77085772</v>
       </c>
       <c r="J243" t="s">
         <v>18</v>
@@ -10904,7 +10920,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="244" ht="14.25" customHeight="1">
+    <row r="244" spans="1:11" ht="14.25" customHeight="1">
       <c r="A244" t="s">
         <v>641</v>
       </c>
@@ -10927,10 +10943,10 @@
         <v>643</v>
       </c>
       <c r="H244">
-        <v>-1205574.0</v>
+        <v>-1205574</v>
       </c>
       <c r="I244">
-        <v>-7708559.0</v>
+        <v>-7708559</v>
       </c>
       <c r="J244" t="s">
         <v>18</v>
@@ -10939,7 +10955,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="245" ht="14.25" customHeight="1">
+    <row r="245" spans="1:11" ht="14.25" customHeight="1">
       <c r="A245" t="s">
         <v>644</v>
       </c>
@@ -10962,10 +10978,10 @@
         <v>648</v>
       </c>
       <c r="H245">
-        <v>-1.20601022E8</v>
+        <v>-120601022</v>
       </c>
       <c r="I245">
-        <v>-7.70812073E8</v>
+        <v>-770812073</v>
       </c>
       <c r="J245" t="s">
         <v>18</v>
@@ -10974,7 +10990,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="246" ht="14.25" customHeight="1">
+    <row r="246" spans="1:11" ht="14.25" customHeight="1">
       <c r="A246" t="s">
         <v>25</v>
       </c>
@@ -10997,10 +11013,10 @@
         <v>649</v>
       </c>
       <c r="H246">
-        <v>-1.205828E7</v>
+        <v>-12058280</v>
       </c>
       <c r="I246">
-        <v>-7.7079939E7</v>
+        <v>-77079939</v>
       </c>
       <c r="J246" t="s">
         <v>18</v>
@@ -11009,7 +11025,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="247" ht="14.25" customHeight="1">
+    <row r="247" spans="1:11" ht="14.25" customHeight="1">
       <c r="A247" t="s">
         <v>53</v>
       </c>
@@ -11032,10 +11048,10 @@
         <v>650</v>
       </c>
       <c r="H247">
-        <v>-1.2058308E7</v>
+        <v>-12058308</v>
       </c>
       <c r="I247">
-        <v>-7.7080516E7</v>
+        <v>-77080516</v>
       </c>
       <c r="J247" t="s">
         <v>18</v>
@@ -11044,7 +11060,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="248" ht="14.25" customHeight="1">
+    <row r="248" spans="1:11" ht="14.25" customHeight="1">
       <c r="A248" t="s">
         <v>651</v>
       </c>
@@ -11067,10 +11083,10 @@
         <v>654</v>
       </c>
       <c r="H248">
-        <v>-1.20603143E8</v>
+        <v>-120603143</v>
       </c>
       <c r="I248">
-        <v>-7.70814323E8</v>
+        <v>-770814323</v>
       </c>
       <c r="J248" t="s">
         <v>18</v>
@@ -11079,7 +11095,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="249" ht="14.25" customHeight="1">
+    <row r="249" spans="1:11" ht="14.25" customHeight="1">
       <c r="A249" t="s">
         <v>25</v>
       </c>
@@ -11102,10 +11118,10 @@
         <v>656</v>
       </c>
       <c r="H249">
-        <v>-1.2058379E7</v>
+        <v>-12058379</v>
       </c>
       <c r="I249">
-        <v>-7.7079694E7</v>
+        <v>-77079694</v>
       </c>
       <c r="J249" t="s">
         <v>62</v>
@@ -11114,7 +11130,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="250" ht="14.25" customHeight="1">
+    <row r="250" spans="1:11" ht="14.25" customHeight="1">
       <c r="A250" t="s">
         <v>25</v>
       </c>
@@ -11137,10 +11153,10 @@
         <v>657</v>
       </c>
       <c r="H250">
-        <v>-1.2058576E7</v>
+        <v>-12058576</v>
       </c>
       <c r="I250">
-        <v>-7.7079769E7</v>
+        <v>-77079769</v>
       </c>
       <c r="J250" t="s">
         <v>18</v>
@@ -11149,7 +11165,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="251" ht="14.25" customHeight="1">
+    <row r="251" spans="1:11" ht="14.25" customHeight="1">
       <c r="A251" t="s">
         <v>658</v>
       </c>
@@ -11172,10 +11188,10 @@
         <v>662</v>
       </c>
       <c r="H251">
-        <v>-1.2054079E7</v>
+        <v>-12054079</v>
       </c>
       <c r="I251">
-        <v>-7.7085772E7</v>
+        <v>-77085772</v>
       </c>
       <c r="J251" t="s">
         <v>18</v>
@@ -11184,7 +11200,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="252" ht="14.25" customHeight="1">
+    <row r="252" spans="1:11" ht="14.25" customHeight="1">
       <c r="A252" t="s">
         <v>25</v>
       </c>
@@ -11207,10 +11223,10 @@
         <v>664</v>
       </c>
       <c r="H252">
-        <v>-1.2058225E7</v>
+        <v>-12058225</v>
       </c>
       <c r="I252">
-        <v>-7.7079769E7</v>
+        <v>-77079769</v>
       </c>
       <c r="J252" t="s">
         <v>62</v>
@@ -11219,7 +11235,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="253" ht="14.25" customHeight="1">
+    <row r="253" spans="1:11" ht="14.25" customHeight="1">
       <c r="A253" t="s">
         <v>665</v>
       </c>
@@ -11242,10 +11258,10 @@
         <v>666</v>
       </c>
       <c r="H253">
-        <v>-1.205524619E9</v>
+        <v>-1205524619</v>
       </c>
       <c r="I253">
-        <v>-7.708674081E9</v>
+        <v>-7708674081</v>
       </c>
       <c r="J253" t="s">
         <v>62</v>
@@ -11254,7 +11270,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="254" ht="14.25" customHeight="1">
+    <row r="254" spans="1:11" ht="14.25" customHeight="1">
       <c r="A254" t="s">
         <v>667</v>
       </c>
@@ -11277,10 +11293,10 @@
         <v>669</v>
       </c>
       <c r="H254">
-        <v>-1.20597677E8</v>
+        <v>-120597677</v>
       </c>
       <c r="I254">
-        <v>-7.7081146E7</v>
+        <v>-77081146</v>
       </c>
       <c r="J254" t="s">
         <v>18</v>
@@ -11289,7 +11305,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="255" ht="14.25" customHeight="1">
+    <row r="255" spans="1:11" ht="14.25" customHeight="1">
       <c r="A255" t="s">
         <v>670</v>
       </c>
@@ -11312,10 +11328,10 @@
         <v>669</v>
       </c>
       <c r="H255">
-        <v>-120567.0</v>
+        <v>-120567</v>
       </c>
       <c r="I255">
-        <v>-77085.0</v>
+        <v>-77085</v>
       </c>
       <c r="J255" t="s">
         <v>18</v>
@@ -11324,7 +11340,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="256" ht="14.25" customHeight="1">
+    <row r="256" spans="1:11" ht="14.25" customHeight="1">
       <c r="A256" t="s">
         <v>671</v>
       </c>
@@ -11347,10 +11363,10 @@
         <v>673</v>
       </c>
       <c r="H256">
-        <v>-1.205983221E9</v>
+        <v>-1205983221</v>
       </c>
       <c r="I256">
-        <v>-7.708107917E9</v>
+        <v>-7708107917</v>
       </c>
       <c r="J256" t="s">
         <v>18</v>
@@ -11359,7 +11375,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="257" ht="14.25" customHeight="1">
+    <row r="257" spans="1:11" ht="14.25" customHeight="1">
       <c r="A257" t="s">
         <v>674</v>
       </c>
@@ -11382,10 +11398,10 @@
         <v>676</v>
       </c>
       <c r="H257">
-        <v>-1.2053839E7</v>
+        <v>-12053839</v>
       </c>
       <c r="I257">
-        <v>-7.7086625E7</v>
+        <v>-77086625</v>
       </c>
       <c r="J257" t="s">
         <v>18</v>
@@ -11394,7 +11410,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="258" ht="14.25" customHeight="1">
+    <row r="258" spans="1:11" ht="14.25" customHeight="1">
       <c r="A258" t="s">
         <v>677</v>
       </c>
@@ -11417,10 +11433,10 @@
         <v>678</v>
       </c>
       <c r="H258">
-        <v>-1.205647228E9</v>
+        <v>-1205647228</v>
       </c>
       <c r="I258">
-        <v>-7.708648469E9</v>
+        <v>-7708648469</v>
       </c>
       <c r="J258" t="s">
         <v>18</v>
@@ -11430,9 +11446,7 @@
       </c>
     </row>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/flora.xlsx
+++ b/flora.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\User\Documents\bioConservaPY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB522EC4-9503-4EB1-88DD-89CBD49329D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA6F45F5-876D-4E3B-9E7E-2D96947CC660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9546,7 +9546,7 @@
         <v>-12053551</v>
       </c>
       <c r="I204" s="1">
-        <v>-77084238</v>
+        <v>-77086238</v>
       </c>
       <c r="J204" t="s">
         <v>62</v>
